--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="15960" windowHeight="8652" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="T00" sheetId="1" r:id="rId1"/>
@@ -3085,7 +3085,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14994890" y="10421620"/>
+          <a:off x="14914880" y="10421620"/>
           <a:ext cx="1118870" cy="2019300"/>
         </a:xfrm>
         <a:prstGeom prst="rightBrace">
@@ -3377,7 +3377,7 @@
     <col min="2" max="2" width="9" style="3"/>
     <col min="3" max="3" width="12.1111111111111" style="3" customWidth="1"/>
     <col min="4" max="4" width="12.1759259259259" customWidth="1"/>
-    <col min="5" max="5" width="48.0185185185185" customWidth="1"/>
+    <col min="5" max="5" width="46.8518518518519" customWidth="1"/>
     <col min="6" max="6" width="35.4444444444444" customWidth="1"/>
     <col min="7" max="7" width="31.8888888888889" customWidth="1"/>
     <col min="8" max="8" width="43.6666666666667" customWidth="1"/>

--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15960" windowHeight="8652" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="10620"/>
   </bookViews>
   <sheets>
     <sheet name="T00" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet2" sheetId="7" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">T00!$A$1:$K$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">T00!$A$1:$K$64</definedName>
     <definedName name="ods_akshare_stock_value_em">Takshare!$C$7</definedName>
     <definedName name="ods_akshare_stock_zh_a_gdhs_detail_em">Takshare!$H$7</definedName>
     <definedName name="ods_akshare_stock_cyq_em">Takshare!$M$7</definedName>
@@ -86,6 +86,7 @@
     <definedName name="ods_tushare_stock_board_concept_hist_em">Tushare!$H$51</definedName>
     <definedName name="ods_tushare_stock_board_concept_maps_em">Tushare!$M$51</definedName>
     <definedName name="dwd_shareholder_num_latest">ODS_DWD_DMART!$H$19</definedName>
+    <definedName name="dwd_stock_technical_indicators">ODS_DWD_DMART!$M$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -105,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="708">
   <si>
     <t>序号</t>
   </si>
@@ -531,7 +532,7 @@
     <t>每日17点  T-1</t>
   </si>
   <si>
-    <t>ods_stock_kline_daily_insight
+    <t>ods_stock_kline_daily_ts
 dwd_ashare_stock_base_info</t>
   </si>
   <si>
@@ -539,6 +540,12 @@
   </si>
   <si>
     <t>跌停股票清单</t>
+  </si>
+  <si>
+    <t>dwd_stock_technical_indicators</t>
+  </si>
+  <si>
+    <t>股票技术指标预计算表（均线等）</t>
   </si>
   <si>
     <t>DMART 层</t>
@@ -1482,6 +1489,24 @@
   </si>
   <si>
     <t>XXXXX</t>
+  </si>
+  <si>
+    <t>成交量（手）</t>
+  </si>
+  <si>
+    <t>成交额（千元）</t>
+  </si>
+  <si>
+    <t>today_pct</t>
+  </si>
+  <si>
+    <t>日内涨跌幅（%）</t>
+  </si>
+  <si>
+    <t>is_down</t>
+  </si>
+  <si>
+    <t>是否阴线1:是(close&lt;open), 0:否(close&gt;=open)</t>
   </si>
   <si>
     <t>买token 偶尔跑一次</t>
@@ -1846,16 +1871,118 @@
     <t>昨日收盘价</t>
   </si>
   <si>
+    <t>ma5</t>
+  </si>
+  <si>
+    <t>5日均线</t>
+  </si>
+  <si>
     <t>rate</t>
   </si>
   <si>
     <t>涨幅</t>
   </si>
   <si>
+    <t>ma10</t>
+  </si>
+  <si>
+    <t>10日均线</t>
+  </si>
+  <si>
+    <t>ma20</t>
+  </si>
+  <si>
+    <t>20日均线</t>
+  </si>
+  <si>
+    <t>ma60</t>
+  </si>
+  <si>
+    <t>60日均线</t>
+  </si>
+  <si>
+    <t>ma120</t>
+  </si>
+  <si>
+    <t>120日均线（半年线）</t>
+  </si>
+  <si>
+    <t>ma250</t>
+  </si>
+  <si>
+    <t>250日均线（年线）</t>
+  </si>
+  <si>
+    <t>vol_ma5</t>
+  </si>
+  <si>
+    <t>5日均量</t>
+  </si>
+  <si>
+    <t>vol_ma10</t>
+  </si>
+  <si>
+    <t>10日均量</t>
+  </si>
+  <si>
+    <t>vol_ma20</t>
+  </si>
+  <si>
+    <t>20日均量</t>
+  </si>
+  <si>
+    <t>vol_ma60</t>
+  </si>
+  <si>
+    <t>60日均量</t>
+  </si>
+  <si>
+    <t>vol_ma120</t>
+  </si>
+  <si>
+    <t>120日均量</t>
+  </si>
+  <si>
+    <t>vol_ma250</t>
+  </si>
+  <si>
+    <t>250日均量</t>
+  </si>
+  <si>
+    <t>price_vs_ma5</t>
+  </si>
+  <si>
+    <t>价格/5日均线-1, 单位%</t>
+  </si>
+  <si>
+    <t>price_vs_ma20</t>
+  </si>
+  <si>
+    <t>价格/20日均线-1, 单位%</t>
+  </si>
+  <si>
+    <t>price_vs_ma60</t>
+  </si>
+  <si>
+    <t>价格/60日均线-1, 单位%</t>
+  </si>
+  <si>
+    <t>volume_vs_ma5</t>
+  </si>
+  <si>
+    <t>成交量/5日均量-1, 单位%</t>
+  </si>
+  <si>
     <t>对</t>
   </si>
   <si>
     <t>打上创业、主板、科创、北证等的标识，才能计算其是否满足涨停，因为其涨跌停限制不一样</t>
+  </si>
+  <si>
+    <t>volume_vs_ma20</t>
+  </si>
+  <si>
+    <t>成交量/20日均量-1, 单位%</t>
   </si>
   <si>
     <t>北证的数据呢？ 能不能找到北证的stock_code</t>
@@ -3370,7 +3497,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" style="15"/>
@@ -4524,58 +4651,71 @@
         <v>138</v>
       </c>
     </row>
-    <row r="59" ht="19.95" customHeight="1"/>
+    <row r="59" ht="42" customHeight="1" spans="1:8">
+      <c r="E59" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F59" t="s">
+        <v>142</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="H59" s="28" t="s">
+        <v>77</v>
+      </c>
+    </row>
     <row r="60" ht="19.95" customHeight="1"/>
-    <row r="61" ht="19.95" customHeight="1" spans="1:8">
-      <c r="A61" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-    </row>
-    <row r="62" ht="39" customHeight="1" spans="1:8">
-      <c r="B62" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C62" s="3" t="s">
+    <row r="61" ht="19.95" customHeight="1"/>
+    <row r="62" ht="19.95" customHeight="1" spans="1:8">
+      <c r="A62" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="26"/>
+    </row>
+    <row r="63" ht="39" customHeight="1" spans="1:8">
+      <c r="B63" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E62" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="F62" t="s">
+      <c r="E63" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="F63" t="s">
+        <v>146</v>
+      </c>
+      <c r="G63" t="s">
+        <v>147</v>
+      </c>
+      <c r="H63" s="28" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1" spans="1:8">
+      <c r="B64" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G62" t="s">
+      <c r="E64" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F64" t="s">
+        <v>150</v>
+      </c>
+      <c r="G64" t="s">
+        <v>151</v>
+      </c>
+      <c r="H64" t="s">
         <v>145</v>
       </c>
-      <c r="H62" s="28" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="63" ht="30" customHeight="1" spans="1:8">
-      <c r="B63" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F63" t="s">
-        <v>148</v>
-      </c>
-      <c r="G63" t="s">
-        <v>149</v>
-      </c>
-      <c r="H63" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="64" ht="19.95" customHeight="1"/>
+    </row>
     <row r="65" ht="19.95" customHeight="1"/>
     <row r="66" ht="19.95" customHeight="1"/>
     <row r="67" ht="19.95" customHeight="1"/>
@@ -4601,13 +4741,14 @@
     <row r="87" ht="19.95" customHeight="1"/>
     <row r="88" ht="19.95" customHeight="1"/>
     <row r="89" ht="19.95" customHeight="1"/>
+    <row r="90" ht="19.95" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K63" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K64" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A62:H62"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E9" location="ods_akshare_stock_value_em" display="ods_akshare_stock_value_em"/>
@@ -4643,8 +4784,8 @@
     <hyperlink ref="E56" location="dwd_ashare_stock_base_info" display="dwd_ashare_stock_base_info"/>
     <hyperlink ref="E57" location="dwd_stock_ZT_list" display="dwd_stock_zt_list"/>
     <hyperlink ref="E58" location="dwd_stock_DT_list" display="dwd_stock_dt_list"/>
-    <hyperlink ref="E62" location="dmart_stock_zt_details" display="dmart_stock_zt_details"/>
-    <hyperlink ref="E63" location="dmart_stock_zt_details_expanded" display="dmart_stock_zt_details_expanded"/>
+    <hyperlink ref="E63" location="dmart_stock_zt_details" display="dmart_stock_zt_details"/>
+    <hyperlink ref="E64" location="dmart_stock_zt_details_expanded" display="dmart_stock_zt_details_expanded"/>
     <hyperlink ref="H7" location="ods_stock_code_daily_insight" display="ods_stock_code_daily_insight"/>
     <hyperlink ref="K45" location="dwd_stock_a_total_plate" display="dwd_stock_a_total_plate"/>
     <hyperlink ref="E24" location="ods_akshare_stock_board_concept_name_em" display="ods_akshare_stock_board_concept_name_em"/>
@@ -4661,6 +4802,7 @@
     <hyperlink ref="E34" location="ods_tushare_stock_board_concept_hist_em" display="ods_tushare_stock_board_concept_hist_em"/>
     <hyperlink ref="E35" location="ods_tushare_stock_board_concept_maps_em" display="ods_tushare_stock_board_concept_maps_em"/>
     <hyperlink ref="E55" location="dwd_shareholder_num_latest" display="dwd_shareholder_num_latest"/>
+    <hyperlink ref="E59" location="dwd_stock_technical_indicators" display="dwd_stock_technical_indicators"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4709,19 +4851,19 @@
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:13">
@@ -4729,19 +4871,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:13">
@@ -4749,19 +4891,19 @@
         <v>2</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F8" s="3">
         <v>2</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:13">
@@ -4769,10 +4911,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F9" s="3"/>
     </row>
@@ -4781,10 +4923,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F10" s="3"/>
     </row>
@@ -4815,28 +4957,28 @@
         <v>0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>0</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:13">
@@ -4844,28 +4986,28 @@
         <v>1</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K16" s="3">
         <v>1</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:18">
@@ -4873,28 +5015,28 @@
         <v>2</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F17" s="3">
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H17" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K17" s="3">
         <v>2</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M17" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:18">
@@ -4902,28 +5044,28 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C18" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F18" s="3">
         <v>3</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H18" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K18" s="3">
         <v>3</v>
       </c>
       <c r="L18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:18">
@@ -4931,28 +5073,28 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F19" s="3">
         <v>4</v>
       </c>
       <c r="G19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K19" s="3">
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:18">
@@ -4960,28 +5102,28 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C20" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F20" s="3">
         <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K20" s="3">
         <v>5</v>
       </c>
       <c r="L20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M20" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:18">
@@ -4989,28 +5131,28 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C21" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F21" s="3">
         <v>6</v>
       </c>
       <c r="G21" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H21" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K21" s="3">
         <v>6</v>
       </c>
       <c r="L21" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M21" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:18">
@@ -5018,28 +5160,28 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F22" s="3">
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H22" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K22" s="3">
         <v>7</v>
       </c>
       <c r="L22" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M22" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:18">
@@ -5047,19 +5189,19 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F23" s="3">
         <v>8</v>
       </c>
       <c r="G23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:18">
@@ -5095,37 +5237,37 @@
         <v>0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>0</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:18">
@@ -5133,37 +5275,37 @@
         <v>1</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C30" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H30" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K30" s="3">
         <v>1</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M30" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P30" s="3">
         <v>1</v>
       </c>
       <c r="Q30" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="R30" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:18">
@@ -5171,37 +5313,37 @@
         <v>2</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C31" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F31" s="3">
         <v>2</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H31" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K31" s="3">
         <v>2</v>
       </c>
       <c r="L31" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P31" s="3">
         <v>2</v>
       </c>
       <c r="Q31" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="R31" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:18">
@@ -5209,37 +5351,37 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C32" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F32" s="3">
         <v>3</v>
       </c>
       <c r="G32" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K32" s="3">
         <v>3</v>
       </c>
       <c r="L32" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M32" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P32" s="3">
         <v>3</v>
       </c>
       <c r="Q32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="R32" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:18">
@@ -5247,37 +5389,37 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F33" s="3">
         <v>4</v>
       </c>
       <c r="G33" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H33" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K33" s="3">
         <v>4</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M33" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="P33" s="3">
         <v>4</v>
       </c>
       <c r="Q33" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="R33" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:18">
@@ -5285,37 +5427,37 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C34" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F34" s="3">
         <v>5</v>
       </c>
       <c r="G34" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H34" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K34" s="3">
         <v>5</v>
       </c>
       <c r="L34" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M34" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P34" s="3">
         <v>5</v>
       </c>
       <c r="Q34" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="R34" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:18">
@@ -5323,37 +5465,37 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C35" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F35" s="3">
         <v>6</v>
       </c>
       <c r="G35" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H35" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K35" s="3">
         <v>6</v>
       </c>
       <c r="L35" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M35" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P35" s="3">
         <v>6</v>
       </c>
       <c r="Q35" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="R35" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:18">
@@ -5361,37 +5503,37 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C36" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F36" s="3">
         <v>7</v>
       </c>
       <c r="G36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K36" s="3">
         <v>7</v>
       </c>
       <c r="L36" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M36" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P36" s="3">
         <v>7</v>
       </c>
       <c r="Q36" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="R36" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:18">
@@ -5399,37 +5541,37 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C37" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F37" s="3">
         <v>8</v>
       </c>
       <c r="G37" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H37" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K37" s="3">
         <v>8</v>
       </c>
       <c r="L37" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M37" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P37" s="3">
         <v>8</v>
       </c>
       <c r="Q37" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="R37" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:18">
@@ -5437,37 +5579,37 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F38" s="3">
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H38" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K38" s="3">
         <v>9</v>
       </c>
       <c r="L38" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M38" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P38" s="3">
         <v>9</v>
       </c>
       <c r="Q38" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="R38" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:18">
@@ -5475,28 +5617,28 @@
         <v>10</v>
       </c>
       <c r="G39" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H39" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K39" s="3">
         <v>10</v>
       </c>
       <c r="L39" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M39" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P39" s="3">
         <v>10</v>
       </c>
       <c r="Q39" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="R39" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:18">
@@ -5507,19 +5649,19 @@
         <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H40" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P40" s="3">
         <v>11</v>
       </c>
       <c r="Q40" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="R40" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:18">
@@ -5530,10 +5672,10 @@
         <v>12</v>
       </c>
       <c r="G41" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H41" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:18">
@@ -5541,19 +5683,19 @@
         <v>0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F42" s="3">
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:18">
@@ -5561,19 +5703,19 @@
         <v>1</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C43" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F43" s="3">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H43" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:18">
@@ -5581,19 +5723,19 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C44" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F44" s="3">
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H44" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:18">
@@ -5601,19 +5743,19 @@
         <v>3</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F45" s="3">
         <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H45" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:18">
@@ -5621,19 +5763,19 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C46" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F46" s="3">
         <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H46" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:18">
@@ -5641,19 +5783,19 @@
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C47" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F47" s="3">
         <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H47" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:18">
@@ -5661,19 +5803,19 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C48" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F48" s="3">
         <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H48" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:8">
@@ -5681,19 +5823,19 @@
         <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C49" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F49" s="3">
         <v>20</v>
       </c>
       <c r="G49" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H49" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:8">
@@ -5701,10 +5843,10 @@
         <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:8">
@@ -5712,10 +5854,10 @@
         <v>22</v>
       </c>
       <c r="G51" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:8">
@@ -5723,10 +5865,10 @@
         <v>23</v>
       </c>
       <c r="G52" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H52" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:8">
@@ -5737,10 +5879,10 @@
         <v>24</v>
       </c>
       <c r="G53" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H53" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:8">
@@ -5751,10 +5893,10 @@
         <v>25</v>
       </c>
       <c r="G54" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H54" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:8">
@@ -5762,19 +5904,19 @@
         <v>0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F55" s="3">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H55" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:8">
@@ -5782,19 +5924,19 @@
         <v>1</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C56" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F56" s="3">
         <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H56" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:8">
@@ -5802,10 +5944,10 @@
         <v>2</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F57" s="3"/>
     </row>
@@ -5814,10 +5956,10 @@
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C58" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F58" s="3"/>
     </row>
@@ -5826,10 +5968,10 @@
         <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C59" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F59" s="3"/>
     </row>
@@ -5863,7 +6005,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -5922,28 +6064,28 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:14">
@@ -5951,28 +6093,28 @@
         <v>1</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G9" s="3">
         <v>1</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L9" s="3">
         <v>1</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:14">
@@ -5980,28 +6122,28 @@
         <v>2</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G10" s="3">
         <v>2</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L10" s="3">
         <v>2</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:14">
@@ -6009,28 +6151,28 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G11" s="3">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L11" s="3">
         <v>3</v>
       </c>
       <c r="M11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:14">
@@ -6038,28 +6180,28 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D12" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G12" s="3">
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L12" s="3">
         <v>4</v>
       </c>
       <c r="M12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:14">
@@ -6067,28 +6209,28 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D13" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G13" s="3">
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I13" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L13" s="3">
         <v>5</v>
       </c>
       <c r="M13" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:14">
@@ -6096,28 +6238,28 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G14" s="3">
         <v>6</v>
       </c>
       <c r="H14" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I14" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L14" s="3">
         <v>6</v>
       </c>
       <c r="M14" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N14" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:14">
@@ -6125,28 +6267,28 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
         <v>7</v>
       </c>
       <c r="H15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L15" s="3">
         <v>7</v>
       </c>
       <c r="M15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:14">
@@ -6154,28 +6296,28 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D16" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G16" s="3">
         <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I16" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L16" s="3">
         <v>8</v>
       </c>
       <c r="M16" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N16" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:14">
@@ -6183,28 +6325,28 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D17" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G17" s="3">
         <v>9</v>
       </c>
       <c r="H17" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I17" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L17" s="3">
         <v>9</v>
       </c>
       <c r="M17" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N17" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:14">
@@ -6212,28 +6354,28 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D18" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G18" s="3">
         <v>10</v>
       </c>
       <c r="H18" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I18" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L18" s="3">
         <v>10</v>
       </c>
       <c r="M18" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N18" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:14">
@@ -6241,28 +6383,28 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D19" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G19" s="3">
         <v>11</v>
       </c>
       <c r="H19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I19" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L19" s="3">
         <v>11</v>
       </c>
       <c r="M19" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N19" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:14">
@@ -6270,19 +6412,19 @@
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D20" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G20" s="3">
         <v>12</v>
       </c>
       <c r="H20" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I20" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:14">
@@ -6290,19 +6432,19 @@
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D21" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G21" s="3">
         <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I21" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:14">
@@ -6310,19 +6452,19 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D22" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G22" s="3">
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I22" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:14">
@@ -6330,10 +6472,10 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I23" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:14">
@@ -6363,28 +6505,28 @@
         <v>0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:14">
@@ -6392,28 +6534,28 @@
         <v>1</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L29" s="3">
         <v>1</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N29" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:14">
@@ -6421,7 +6563,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D30" t="s">
         <v>0</v>
@@ -6430,7 +6572,7 @@
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I30" t="s">
         <v>0</v>
@@ -6439,10 +6581,10 @@
         <v>2</v>
       </c>
       <c r="M30" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:14">
@@ -6450,28 +6592,28 @@
         <v>3</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G31" s="3">
         <v>3</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L31" s="3">
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N31" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="2:14">
@@ -6479,28 +6621,28 @@
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D32" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G32" s="3">
         <v>4</v>
       </c>
       <c r="H32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I32" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L32" s="3">
         <v>4</v>
       </c>
       <c r="M32" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N32" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:14">
@@ -6508,28 +6650,28 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D33" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G33" s="3">
         <v>5</v>
       </c>
       <c r="H33" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I33" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L33" s="3">
         <v>5</v>
       </c>
       <c r="M33" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N33" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:14">
@@ -6537,28 +6679,28 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D34" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G34" s="3">
         <v>6</v>
       </c>
       <c r="H34" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I34" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L34" s="3">
         <v>6</v>
       </c>
       <c r="M34" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N34" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -6566,28 +6708,28 @@
         <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G35" s="3">
         <v>7</v>
       </c>
       <c r="H35" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I35" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L35" s="3">
         <v>7</v>
       </c>
       <c r="M35" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N35" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -6595,28 +6737,28 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D36" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G36" s="3">
         <v>8</v>
       </c>
       <c r="H36" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I36" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L36" s="3">
         <v>8</v>
       </c>
       <c r="M36" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N36" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:14">
@@ -6624,28 +6766,28 @@
         <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D37" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G37" s="3">
         <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I37" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L37" s="3">
         <v>9</v>
       </c>
       <c r="M37" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N37" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:14">
@@ -6653,19 +6795,19 @@
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D38" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G38" s="3">
         <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I38" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:14">
@@ -6673,19 +6815,19 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D39" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G39" s="3">
         <v>11</v>
       </c>
       <c r="H39" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I39" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:14">
@@ -6693,10 +6835,10 @@
         <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D40" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:14">
@@ -6704,10 +6846,10 @@
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D41" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:14">
@@ -6715,10 +6857,10 @@
         <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D42" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:14">
@@ -6726,10 +6868,10 @@
         <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D43" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:14">
@@ -6737,10 +6879,10 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D44" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:14">
@@ -6748,10 +6890,10 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D45" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:14">
@@ -6759,15 +6901,15 @@
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D46" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:20">
       <c r="B51" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:20">
@@ -6807,37 +6949,37 @@
         <v>0</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L54" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>0</v>
       </c>
       <c r="S54" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:20">
@@ -6845,37 +6987,37 @@
         <v>1</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G55" s="3">
         <v>1</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L55" s="3">
         <v>1</v>
       </c>
       <c r="M55" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N55" s="13" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="R55" s="3">
         <v>1</v>
       </c>
       <c r="S55" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="T55" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="2:20">
@@ -6883,7 +7025,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D56" t="s">
         <v>0</v>
@@ -6892,28 +7034,28 @@
         <v>2</v>
       </c>
       <c r="H56" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I56" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L56" s="3">
         <v>2</v>
       </c>
       <c r="M56" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N56" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="R56" s="3">
         <v>2</v>
       </c>
       <c r="S56" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="T56" s="13" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:20">
@@ -6921,37 +7063,37 @@
         <v>3</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G57" s="3">
         <v>3</v>
       </c>
       <c r="H57" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I57" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L57" s="3">
         <v>3</v>
       </c>
       <c r="M57" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N57" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="R57" s="3">
         <v>3</v>
       </c>
       <c r="S57" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="T57" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:20">
@@ -6959,25 +7101,25 @@
         <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D58" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G58" s="3">
         <v>4</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L58" s="3">
         <v>4</v>
       </c>
       <c r="M58" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N58" t="s">
         <v>0</v>
@@ -6986,10 +7128,10 @@
         <v>4</v>
       </c>
       <c r="S58" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="T58" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:20">
@@ -6997,37 +7139,37 @@
         <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D59" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G59" s="3">
         <v>5</v>
       </c>
       <c r="H59" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I59" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L59" s="3">
         <v>5</v>
       </c>
       <c r="M59" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N59" s="13" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="R59" s="3">
         <v>5</v>
       </c>
       <c r="S59" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="T59" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:20">
@@ -7035,37 +7177,37 @@
         <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D60" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G60" s="3">
         <v>6</v>
       </c>
       <c r="H60" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I60" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L60" s="3">
         <v>6</v>
       </c>
       <c r="M60" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N60" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="R60" s="3">
         <v>6</v>
       </c>
       <c r="S60" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="T60" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:20">
@@ -7073,37 +7215,37 @@
         <v>7</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D61" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G61" s="3">
         <v>7</v>
       </c>
       <c r="H61" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I61" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L61" s="3">
         <v>7</v>
       </c>
       <c r="M61" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N61" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="R61" s="3">
         <v>7</v>
       </c>
       <c r="S61" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="T61" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:20">
@@ -7111,37 +7253,37 @@
         <v>8</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D62" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G62" s="3">
         <v>8</v>
       </c>
       <c r="H62" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I62" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L62" s="3">
         <v>8</v>
       </c>
       <c r="M62" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N62" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="R62" s="3">
         <v>8</v>
       </c>
       <c r="S62" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="T62" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:20">
@@ -7149,37 +7291,37 @@
         <v>9</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D63" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G63" s="3">
         <v>9</v>
       </c>
       <c r="H63" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I63" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L63" s="3">
         <v>9</v>
       </c>
       <c r="M63" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N63" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="R63" s="3">
         <v>9</v>
       </c>
       <c r="S63" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="T63" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:20">
@@ -7187,37 +7329,37 @@
         <v>10</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D64" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G64" s="3">
         <v>10</v>
       </c>
       <c r="H64" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="I64" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L64" s="3">
         <v>10</v>
       </c>
       <c r="M64" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N64" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="R64" s="3">
         <v>10</v>
       </c>
       <c r="S64" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="T64" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:20">
@@ -7225,37 +7367,37 @@
         <v>11</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G65" s="3">
         <v>11</v>
       </c>
       <c r="H65" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="I65" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L65" s="3">
         <v>11</v>
       </c>
       <c r="M65" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N65" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="R65" s="3">
         <v>11</v>
       </c>
       <c r="S65" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="T65" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:20">
@@ -7263,37 +7405,37 @@
         <v>12</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D66" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G66" s="3">
         <v>12</v>
       </c>
       <c r="H66" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I66" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L66" s="3">
         <v>12</v>
       </c>
       <c r="M66" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N66" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="R66" s="3">
         <v>12</v>
       </c>
       <c r="S66" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="T66" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:20">
@@ -7301,28 +7443,28 @@
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D67" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G67" s="3">
         <v>13</v>
       </c>
       <c r="H67" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="I67" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L67" s="3">
         <v>13</v>
       </c>
       <c r="M67" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N67" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:20">
@@ -7330,19 +7472,19 @@
         <v>14</v>
       </c>
       <c r="C68" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D68" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L68" s="3">
         <v>14</v>
       </c>
       <c r="M68" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N68" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:20">
@@ -7350,19 +7492,19 @@
         <v>15</v>
       </c>
       <c r="C69" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D69" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L69" s="3">
         <v>15</v>
       </c>
       <c r="M69" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N69" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="2:20">
@@ -7370,19 +7512,19 @@
         <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D70" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L70" s="3">
         <v>16</v>
       </c>
       <c r="M70" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N70" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:20">
@@ -7390,19 +7532,19 @@
         <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D71" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L71" s="3">
         <v>17</v>
       </c>
       <c r="M71" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N71" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:20">
@@ -7410,19 +7552,19 @@
         <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D72" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L72" s="3">
         <v>18</v>
       </c>
       <c r="M72" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N72" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:20">
@@ -7430,19 +7572,19 @@
         <v>19</v>
       </c>
       <c r="C73" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D73" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L73" s="3">
         <v>19</v>
       </c>
       <c r="M73" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N73" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:20">
@@ -7450,10 +7592,10 @@
         <v>20</v>
       </c>
       <c r="C74" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D74" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:20">
@@ -7461,10 +7603,10 @@
         <v>21</v>
       </c>
       <c r="C75" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D75" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:20">
@@ -7472,10 +7614,10 @@
         <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D76" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:20">
@@ -7483,10 +7625,10 @@
         <v>23</v>
       </c>
       <c r="C77" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D77" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:20">
@@ -7494,15 +7636,15 @@
         <v>24</v>
       </c>
       <c r="C78" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D78" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:9">
       <c r="B82" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:9">
@@ -7526,19 +7668,19 @@
         <v>0</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G85" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:9">
@@ -7546,19 +7688,19 @@
         <v>1</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G86" s="3">
         <v>1</v>
       </c>
       <c r="H86" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:9">
@@ -7566,19 +7708,19 @@
         <v>2</v>
       </c>
       <c r="C87" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D87" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G87" s="3">
         <v>2</v>
       </c>
       <c r="H87" s="14" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I87" s="14" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:9">
@@ -7586,19 +7728,19 @@
         <v>3</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G88" s="3">
         <v>3</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I88" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:9">
@@ -7606,10 +7748,10 @@
         <v>4</v>
       </c>
       <c r="H89" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I89" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:9">
@@ -7617,10 +7759,10 @@
         <v>5</v>
       </c>
       <c r="H90" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I90" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:9">
@@ -7628,10 +7770,10 @@
         <v>6</v>
       </c>
       <c r="H91" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I91" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:9">
@@ -7639,10 +7781,10 @@
         <v>7</v>
       </c>
       <c r="H92" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I92" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:9">
@@ -7650,10 +7792,10 @@
         <v>8</v>
       </c>
       <c r="H93" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I93" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:9">
@@ -7661,10 +7803,10 @@
         <v>9</v>
       </c>
       <c r="H94" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="I94" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -7696,7 +7838,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="12" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -7731,11 +7873,11 @@
         <v>78</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:14">
@@ -7743,11 +7885,11 @@
         <v>77</v>
       </c>
       <c r="H7" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:14">
@@ -7755,28 +7897,28 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:14">
@@ -7784,10 +7926,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G9" s="3">
         <v>1</v>
@@ -7805,10 +7947,10 @@
         <v>2</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G10" s="3">
         <v>2</v>
@@ -7826,10 +7968,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G11" s="3">
         <v>3</v>
@@ -7843,10 +7985,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G12" s="3">
         <v>4</v>
@@ -7860,10 +8002,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G13" s="3">
         <v>5</v>
@@ -7877,10 +8019,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D14" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G14" s="3">
         <v>6</v>
@@ -7894,10 +8036,10 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G15" s="3">
         <v>7</v>
@@ -7911,10 +8053,10 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
-        <v>188</v>
+        <v>457</v>
       </c>
       <c r="G16" s="3">
         <v>8</v>
@@ -7928,10 +8070,10 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D17" t="s">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="G17" s="3">
         <v>9</v>
@@ -7941,6 +8083,15 @@
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:14">
+      <c r="B18" s="3">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>459</v>
+      </c>
+      <c r="D18" t="s">
+        <v>460</v>
+      </c>
       <c r="G18" s="3">
         <v>10</v>
       </c>
@@ -7949,6 +8100,15 @@
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:14">
+      <c r="B19" s="3">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>461</v>
+      </c>
+      <c r="D19" t="s">
+        <v>462</v>
+      </c>
       <c r="G19" s="3">
         <v>11</v>
       </c>
@@ -7978,7 +8138,7 @@
     </row>
     <row r="26" customHeight="1" spans="1:14">
       <c r="A26" s="12" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -8037,28 +8197,28 @@
         <v>0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:14">
@@ -8066,28 +8226,28 @@
         <v>1</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L33" s="3">
         <v>1</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:14">
@@ -8095,28 +8255,28 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D34" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G34" s="3">
         <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I34" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L34" s="3">
         <v>2</v>
       </c>
       <c r="M34" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N34" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -8124,28 +8284,28 @@
         <v>3</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G35" s="3">
         <v>3</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L35" s="3">
         <v>3</v>
       </c>
       <c r="M35" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N35" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -8153,28 +8313,28 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="D36" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="G36" s="3">
         <v>4</v>
       </c>
       <c r="H36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I36" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="L36" s="3">
         <v>4</v>
       </c>
       <c r="M36" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:14">
@@ -8182,28 +8342,28 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D37" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G37" s="3">
         <v>5</v>
       </c>
       <c r="H37" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I37" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="L37" s="3">
         <v>5</v>
       </c>
       <c r="M37" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N37" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:14">
@@ -8211,28 +8371,28 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="D38" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="G38" s="3">
         <v>6</v>
       </c>
       <c r="H38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I38" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="L38" s="3">
         <v>6</v>
       </c>
       <c r="M38" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="N38" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:14">
@@ -8240,28 +8400,28 @@
         <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D39" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="G39" s="3">
         <v>7</v>
       </c>
       <c r="H39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I39" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="L39" s="3">
         <v>7</v>
       </c>
       <c r="M39" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="N39" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:14">
@@ -8269,19 +8429,19 @@
         <v>8</v>
       </c>
       <c r="H40" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I40" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="L40" s="3">
         <v>8</v>
       </c>
       <c r="M40" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="N40" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:14">
@@ -8289,19 +8449,19 @@
         <v>9</v>
       </c>
       <c r="H41" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="I41" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="L41" s="3">
         <v>9</v>
       </c>
       <c r="M41" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="N41" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:14">
@@ -8309,10 +8469,10 @@
         <v>10</v>
       </c>
       <c r="H42" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I42" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="L42" s="3"/>
     </row>
@@ -8321,10 +8481,10 @@
         <v>11</v>
       </c>
       <c r="H43" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I43" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:14">
@@ -8332,10 +8492,10 @@
         <v>12</v>
       </c>
       <c r="H44" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I44" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:14">
@@ -8343,10 +8503,10 @@
         <v>13</v>
       </c>
       <c r="H45" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I45" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:14">
@@ -8354,10 +8514,10 @@
         <v>14</v>
       </c>
       <c r="H46" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="I46" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:14">
@@ -8365,10 +8525,10 @@
         <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="I47" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:15">
@@ -8400,28 +8560,28 @@
         <v>0</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L52" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:15">
@@ -8429,28 +8589,28 @@
         <v>1</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G53" s="3">
         <v>1</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L53" s="3">
         <v>1</v>
       </c>
       <c r="M53" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N53" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O53" s="13"/>
     </row>
@@ -8459,28 +8619,28 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D54" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G54" s="3">
         <v>2</v>
       </c>
       <c r="H54" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I54" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L54" s="3">
         <v>2</v>
       </c>
       <c r="M54" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N54" s="13" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O54" s="13"/>
     </row>
@@ -8489,28 +8649,28 @@
         <v>3</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G55" s="3">
         <v>3</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L55" s="3">
         <v>3</v>
       </c>
       <c r="M55" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N55" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O55" s="13"/>
     </row>
@@ -8519,28 +8679,28 @@
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D56" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="G56" s="3">
         <v>4</v>
       </c>
       <c r="H56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I56" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="L56" s="3">
         <v>4</v>
       </c>
       <c r="M56" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N56" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:15">
@@ -8548,28 +8708,28 @@
         <v>5</v>
       </c>
       <c r="C57" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="D57" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="G57" s="3">
         <v>5</v>
       </c>
       <c r="H57" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I57" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="L57" s="3">
         <v>5</v>
       </c>
       <c r="M57" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N57" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:15">
@@ -8577,19 +8737,19 @@
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D58" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G58" s="3">
         <v>6</v>
       </c>
       <c r="H58" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I58" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:15">
@@ -8597,19 +8757,19 @@
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D59" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="G59" s="3">
         <v>7</v>
       </c>
       <c r="H59" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I59" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:15">
@@ -8617,19 +8777,19 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="D60" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="G60" s="3">
         <v>8</v>
       </c>
       <c r="H60" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I60" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:15">
@@ -8637,19 +8797,19 @@
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D61" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G61" s="3">
         <v>9</v>
       </c>
       <c r="H61" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I61" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:15">
@@ -8657,19 +8817,19 @@
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D62" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G62" s="3">
         <v>10</v>
       </c>
       <c r="H62" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I62" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:15">
@@ -8677,19 +8837,19 @@
         <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D63" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="G63" s="3">
         <v>11</v>
       </c>
       <c r="H63" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="I63" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:15">
@@ -8697,10 +8857,10 @@
         <v>12</v>
       </c>
       <c r="H64" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="I64" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="7:9">
@@ -8708,10 +8868,10 @@
         <v>13</v>
       </c>
       <c r="H65" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I65" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="7:9">
@@ -8719,10 +8879,10 @@
         <v>14</v>
       </c>
       <c r="H66" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="I66" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -8755,7 +8915,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:13">
       <c r="A3" s="12" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -8787,7 +8947,7 @@
     </row>
     <row r="7" customHeight="1" spans="1:13">
       <c r="B7" s="6" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:13">
@@ -8811,19 +8971,19 @@
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:13">
@@ -8831,19 +8991,19 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G11" s="3">
         <v>1</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:13">
@@ -8851,19 +9011,19 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D12" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G12" s="3">
         <v>2</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:13">
@@ -8871,19 +9031,19 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="G13" s="3">
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I13" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:13">
@@ -8891,19 +9051,19 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D14" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="G14" s="3">
         <v>4</v>
       </c>
       <c r="H14" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I14" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:13">
@@ -8911,15 +9071,15 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="D15" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:13">
       <c r="A22" s="12" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -8951,7 +9111,7 @@
     </row>
     <row r="25" customHeight="1" spans="1:13">
       <c r="B25" s="6" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:13">
@@ -8969,10 +9129,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:13">
@@ -8980,10 +9140,10 @@
         <v>1</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:13">
@@ -8991,10 +9151,10 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D30" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:13">
@@ -9002,10 +9162,10 @@
         <v>3</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:13">
@@ -9013,10 +9173,10 @@
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D32" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:4">
@@ -9024,10 +9184,10 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D33" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -9068,10 +9228,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:4">
@@ -9079,10 +9239,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="D7" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:4">
@@ -9090,10 +9250,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:4">
@@ -9101,10 +9261,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="D9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:4">
@@ -9112,10 +9272,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:4">
@@ -9123,10 +9283,10 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="D11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:4">
@@ -9134,10 +9294,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:4">
@@ -9145,10 +9305,10 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D13" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:9">
@@ -9174,19 +9334,19 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:9">
@@ -9194,19 +9354,19 @@
         <v>1</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D21" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="G21" s="3">
         <v>1</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:9">
@@ -9214,19 +9374,19 @@
         <v>2</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3">
         <v>2</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I22" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:9">
@@ -9234,10 +9394,10 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G23" s="3"/>
     </row>
@@ -9246,10 +9406,10 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D24" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G24" s="3"/>
     </row>
@@ -9258,10 +9418,10 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D25" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G25" s="3"/>
     </row>
@@ -9270,10 +9430,10 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G26" s="3"/>
     </row>
@@ -9302,7 +9462,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="9" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -9361,28 +9521,28 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:14">
@@ -9390,28 +9550,28 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="D9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G9" s="3">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="I9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L9" s="3">
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="N9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:14">
@@ -9419,28 +9579,28 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D10" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="G10" s="3">
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="I10" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="L10" s="3">
         <v>2</v>
       </c>
       <c r="M10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N10" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:14">
@@ -9448,28 +9608,28 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D11" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="G11" s="3">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="I11" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="L11" s="3">
         <v>3</v>
       </c>
       <c r="M11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N11" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:14">
@@ -9477,28 +9637,28 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G12" s="3">
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="I12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L12" s="3">
         <v>4</v>
       </c>
       <c r="M12" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="N12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:14">
@@ -9506,28 +9666,28 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="D13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G13" s="3">
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="I13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L13" s="3">
         <v>5</v>
       </c>
       <c r="M13" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="N13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:14">
@@ -9551,19 +9711,19 @@
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:9">
@@ -9571,19 +9731,19 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="D19" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="I19" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:9">
@@ -9591,19 +9751,19 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="D20" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I20" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:9">
@@ -9611,19 +9771,19 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="D21" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="G21" s="3">
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I21" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:9">
@@ -9631,19 +9791,19 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G22" s="3">
         <v>4</v>
       </c>
       <c r="H22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:9">
@@ -9651,19 +9811,19 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G23" s="3">
         <v>5</v>
       </c>
       <c r="H23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:9">
@@ -9681,10 +9841,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:9">
@@ -9692,10 +9852,10 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:9">
@@ -9703,10 +9863,10 @@
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D31" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="2:9">
@@ -9714,10 +9874,10 @@
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D32" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:4">
@@ -9725,10 +9885,10 @@
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="D33" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:4">
@@ -9736,10 +9896,10 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D34" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:4">
@@ -9747,10 +9907,10 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="D35" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:4">
@@ -9758,10 +9918,10 @@
         <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="D36" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:4">
@@ -9769,10 +9929,10 @@
         <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="D37" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:4">
@@ -9780,10 +9940,10 @@
         <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="D38" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:4">
@@ -9791,10 +9951,10 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D39" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:4">
@@ -9802,10 +9962,10 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="D40" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:4">
@@ -9813,10 +9973,10 @@
         <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D41" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>
@@ -9846,7 +10006,7 @@
   <sheetData>
     <row r="2" customHeight="1" spans="1:14">
       <c r="A2" s="4" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -9881,7 +10041,7 @@
     </row>
     <row r="15" customHeight="1" spans="1:14">
       <c r="A15" s="7" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -9945,28 +10105,28 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:14">
@@ -9974,28 +10134,28 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D21" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G21" s="3">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L21" s="3">
         <v>1</v>
       </c>
       <c r="M21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N21" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:14">
@@ -10003,28 +10163,28 @@
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D22" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G22" s="3">
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L22" s="3">
         <v>2</v>
       </c>
       <c r="M22" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N22" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:14">
@@ -10032,28 +10192,28 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D23" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G23" s="3">
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L23" s="3">
         <v>3</v>
       </c>
       <c r="M23" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N23" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:14">
@@ -10061,28 +10221,28 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D24" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="G24" s="3">
         <v>4</v>
       </c>
       <c r="H24" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I24" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L24" s="3">
         <v>4</v>
       </c>
       <c r="M24" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N24" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:14">
@@ -10090,28 +10250,28 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D25" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G25" s="3">
         <v>5</v>
       </c>
       <c r="H25" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I25" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L25" s="3">
         <v>5</v>
       </c>
       <c r="M25" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N25" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:14">
@@ -10119,28 +10279,28 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D26" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G26" s="3">
         <v>6</v>
       </c>
       <c r="H26" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I26" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L26" s="3">
         <v>6</v>
       </c>
       <c r="M26" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="N26" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:14">
@@ -10148,28 +10308,28 @@
         <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D27" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G27" s="3">
         <v>7</v>
       </c>
       <c r="H27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I27" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L27" s="3">
         <v>7</v>
       </c>
       <c r="M27" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="N27" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:14">
@@ -10177,10 +10337,10 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="D28" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:14">
@@ -10188,10 +10348,10 @@
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="D29" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:14">
@@ -10199,10 +10359,10 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="D30" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:14">
@@ -10210,10 +10370,10 @@
         <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="D31" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="H31" s="1"/>
     </row>
@@ -10222,466 +10382,678 @@
         <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="D32" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" customHeight="1" spans="2:9">
+    <row r="33" customHeight="1" spans="2:14">
       <c r="B33" s="3">
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D33" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
-    <row r="34" customHeight="1" spans="2:9">
+    <row r="34" customHeight="1" spans="2:14">
       <c r="B34" s="3">
         <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D34" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="2:9">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="2:14">
       <c r="B35" s="3">
         <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="D35" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="2:9">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="2:14">
       <c r="B36" s="3">
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D36" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="2:9">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="2:14">
       <c r="B37" s="3">
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="D37" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="2:9">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="2:14">
       <c r="C42" s="1" t="s">
         <v>136</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="43" customHeight="1" spans="2:9">
+      <c r="L42" s="3"/>
+      <c r="M42" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="2:14">
       <c r="C43" s="1" t="s">
         <v>135</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="44" customHeight="1" spans="2:9">
+      <c r="L43" s="3"/>
+      <c r="M43" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="2:14">
       <c r="B44" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="2:9">
+        <v>153</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="2:14">
       <c r="B45" s="3">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D45" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I45" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="2:9">
+        <v>155</v>
+      </c>
+      <c r="L45" s="3">
+        <v>1</v>
+      </c>
+      <c r="M45" t="s">
+        <v>154</v>
+      </c>
+      <c r="N45" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="2:14">
       <c r="B46" s="3">
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D46" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G46" s="3">
         <v>2</v>
       </c>
       <c r="H46" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I46" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="2:9">
+        <v>157</v>
+      </c>
+      <c r="L46" s="3">
+        <v>2</v>
+      </c>
+      <c r="M46" t="s">
+        <v>156</v>
+      </c>
+      <c r="N46" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="2:14">
       <c r="B47" s="3">
         <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D47" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G47" s="3">
         <v>3</v>
       </c>
       <c r="H47" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I47" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="2:9">
+        <v>199</v>
+      </c>
+      <c r="L47" s="3">
+        <v>3</v>
+      </c>
+      <c r="M47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N47" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="2:14">
       <c r="B48" s="3">
         <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="D48" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="G48" s="3">
         <v>4</v>
       </c>
       <c r="H48" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="I48" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="2:9">
+        <v>567</v>
+      </c>
+      <c r="L48" s="3">
+        <v>4</v>
+      </c>
+      <c r="M48" t="s">
+        <v>189</v>
+      </c>
+      <c r="N48" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="2:14">
       <c r="B49" s="3">
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G49" s="3">
         <v>5</v>
       </c>
       <c r="H49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I49" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="2:9">
+        <v>174</v>
+      </c>
+      <c r="L49" s="3">
+        <v>5</v>
+      </c>
+      <c r="M49" t="s">
+        <v>568</v>
+      </c>
+      <c r="N49" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="2:14">
       <c r="B50" s="3">
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="D50" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
       </c>
       <c r="H50" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="I50" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="2:9">
+        <v>571</v>
+      </c>
+      <c r="L50" s="3">
+        <v>6</v>
+      </c>
+      <c r="M50" t="s">
+        <v>572</v>
+      </c>
+      <c r="N50" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="2:14">
       <c r="B51" s="3">
         <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="D51" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="G51" s="3">
         <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="I51" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="2:9">
+        <v>544</v>
+      </c>
+      <c r="L51" s="3">
+        <v>7</v>
+      </c>
+      <c r="M51" t="s">
+        <v>574</v>
+      </c>
+      <c r="N51" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="2:14">
       <c r="B52" s="3">
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="D52" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="G52" s="3">
         <v>8</v>
       </c>
       <c r="H52" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="I52" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="2:9">
+        <v>564</v>
+      </c>
+      <c r="L52" s="3">
+        <v>8</v>
+      </c>
+      <c r="M52" t="s">
+        <v>576</v>
+      </c>
+      <c r="N52" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="2:14">
       <c r="B53" s="3">
         <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D53" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="G53" s="3">
         <v>9</v>
       </c>
       <c r="H53" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="I53" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="2:9">
+        <v>546</v>
+      </c>
+      <c r="L53" s="3">
+        <v>9</v>
+      </c>
+      <c r="M53" t="s">
+        <v>578</v>
+      </c>
+      <c r="N53" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="2:14">
       <c r="B54" s="3">
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="D54" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="G54" s="3">
         <v>10</v>
       </c>
       <c r="H54" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="I54" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="2:9">
+        <v>548</v>
+      </c>
+      <c r="L54" s="3">
+        <v>10</v>
+      </c>
+      <c r="M54" t="s">
+        <v>580</v>
+      </c>
+      <c r="N54" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="2:14">
       <c r="B55" s="3">
         <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="D55" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="G55" s="3">
         <v>11</v>
       </c>
       <c r="H55" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="I55" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="2:9">
+        <v>550</v>
+      </c>
+      <c r="L55" s="3">
+        <v>11</v>
+      </c>
+      <c r="M55" t="s">
+        <v>582</v>
+      </c>
+      <c r="N55" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="2:14">
       <c r="B56" s="3">
         <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="D56" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="G56" s="3">
         <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="I56" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="2:9">
+        <v>552</v>
+      </c>
+      <c r="L56" s="3">
+        <v>12</v>
+      </c>
+      <c r="M56" t="s">
+        <v>584</v>
+      </c>
+      <c r="N56" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="2:14">
       <c r="B57" s="3">
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="D57" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="G57" s="3">
         <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="I57" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="2:9">
+        <v>554</v>
+      </c>
+      <c r="L57" s="3">
+        <v>13</v>
+      </c>
+      <c r="M57" t="s">
+        <v>586</v>
+      </c>
+      <c r="N57" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="2:14">
       <c r="B58" s="3">
         <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D58" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G58" s="3">
         <v>14</v>
       </c>
       <c r="H58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I58" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="2:9">
+        <v>324</v>
+      </c>
+      <c r="L58" s="3">
+        <v>14</v>
+      </c>
+      <c r="M58" t="s">
+        <v>588</v>
+      </c>
+      <c r="N58" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="2:14">
       <c r="B59" s="3">
         <v>15</v>
       </c>
       <c r="C59" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="D59" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="G59" s="3">
         <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="I59" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="2:9">
+        <v>556</v>
+      </c>
+      <c r="L59" s="3">
+        <v>15</v>
+      </c>
+      <c r="M59" t="s">
+        <v>590</v>
+      </c>
+      <c r="N59" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="2:14">
       <c r="B60" s="3">
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D60" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="G60" s="3">
         <v>16</v>
       </c>
       <c r="H60" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I60" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="2:9">
+        <v>505</v>
+      </c>
+      <c r="L60" s="3">
+        <v>16</v>
+      </c>
+      <c r="M60" t="s">
+        <v>592</v>
+      </c>
+      <c r="N60" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="2:14">
       <c r="B61" s="3">
         <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="D61" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G61" s="3">
         <v>17</v>
       </c>
       <c r="H61" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="I61" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="1:9">
+        <v>409</v>
+      </c>
+      <c r="L61" s="3">
+        <v>17</v>
+      </c>
+      <c r="M61" t="s">
+        <v>594</v>
+      </c>
+      <c r="N61" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="2:14">
+      <c r="L62" s="3">
+        <v>18</v>
+      </c>
+      <c r="M62" t="s">
+        <v>596</v>
+      </c>
+      <c r="N62" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="2:14">
+      <c r="L63" s="3">
+        <v>19</v>
+      </c>
+      <c r="M63" t="s">
+        <v>598</v>
+      </c>
+      <c r="N63" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="2:14">
+      <c r="L64" s="3">
+        <v>20</v>
+      </c>
+      <c r="M64" t="s">
+        <v>600</v>
+      </c>
+      <c r="N64" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="1:14">
       <c r="B65" s="3" t="s">
-        <v>562</v>
+        <v>602</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="1:9">
+        <v>603</v>
+      </c>
+      <c r="L65" s="3">
+        <v>21</v>
+      </c>
+      <c r="M65" t="s">
+        <v>604</v>
+      </c>
+      <c r="N65" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="1:14">
       <c r="C67" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="1:9">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="1:14">
       <c r="A72" s="7" t="s">
-        <v>565</v>
+        <v>607</v>
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -10692,7 +11064,7 @@
       <c r="H72" s="7"/>
       <c r="I72" s="7"/>
     </row>
-    <row r="73" customHeight="1" spans="1:9">
+    <row r="73" customHeight="1" spans="1:14">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -10703,80 +11075,80 @@
       <c r="H73" s="7"/>
       <c r="I73" s="7"/>
     </row>
-    <row r="76" customHeight="1" spans="1:9">
+    <row r="76" customHeight="1" spans="1:14">
       <c r="C76" s="1" t="s">
-        <v>566</v>
+        <v>608</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="1:9">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="1:14">
       <c r="C77" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="1:9">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="1:14">
       <c r="B78" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="1:9">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="1:14">
       <c r="B79" s="3">
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D79" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G79" s="3">
         <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I79" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="1:9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:14">
       <c r="B80" s="3">
         <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D80" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G80" s="3">
         <v>2</v>
       </c>
       <c r="H80" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I80" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="2:9">
@@ -10784,19 +11156,19 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D81" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G81" s="3">
         <v>3</v>
       </c>
       <c r="H81" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I81" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:9">
@@ -10804,19 +11176,19 @@
         <v>4</v>
       </c>
       <c r="C82" t="s">
-        <v>567</v>
+        <v>609</v>
       </c>
       <c r="D82" t="s">
-        <v>568</v>
+        <v>610</v>
       </c>
       <c r="G82" s="3">
         <v>4</v>
       </c>
       <c r="H82" t="s">
-        <v>567</v>
+        <v>609</v>
       </c>
       <c r="I82" t="s">
-        <v>568</v>
+        <v>610</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:9">
@@ -10824,19 +11196,19 @@
         <v>5</v>
       </c>
       <c r="C83" t="s">
-        <v>569</v>
+        <v>611</v>
       </c>
       <c r="D83" t="s">
-        <v>570</v>
+        <v>612</v>
       </c>
       <c r="G83" s="3">
         <v>5</v>
       </c>
       <c r="H83" t="s">
-        <v>569</v>
+        <v>611</v>
       </c>
       <c r="I83" t="s">
-        <v>570</v>
+        <v>612</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="2:9">
@@ -10844,19 +11216,19 @@
         <v>6</v>
       </c>
       <c r="C84" t="s">
-        <v>571</v>
+        <v>613</v>
       </c>
       <c r="D84" t="s">
-        <v>572</v>
+        <v>614</v>
       </c>
       <c r="G84" s="3">
         <v>6</v>
       </c>
       <c r="H84" t="s">
-        <v>571</v>
+        <v>613</v>
       </c>
       <c r="I84" t="s">
-        <v>572</v>
+        <v>614</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:9">
@@ -10864,19 +11236,19 @@
         <v>7</v>
       </c>
       <c r="C85" t="s">
-        <v>573</v>
+        <v>615</v>
       </c>
       <c r="D85" t="s">
-        <v>574</v>
+        <v>616</v>
       </c>
       <c r="G85" s="3">
         <v>7</v>
       </c>
       <c r="H85" t="s">
-        <v>573</v>
+        <v>615</v>
       </c>
       <c r="I85" t="s">
-        <v>574</v>
+        <v>616</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:9">
@@ -10884,19 +11256,19 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>575</v>
+        <v>617</v>
       </c>
       <c r="D86" t="s">
-        <v>576</v>
+        <v>618</v>
       </c>
       <c r="G86" s="3">
         <v>8</v>
       </c>
       <c r="H86" t="s">
-        <v>575</v>
+        <v>617</v>
       </c>
       <c r="I86" t="s">
-        <v>576</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -10926,29 +11298,29 @@
   <sheetData>
     <row r="5" spans="3:9">
       <c r="C5" s="1" t="s">
-        <v>577</v>
+        <v>619</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>578</v>
+        <v>620</v>
       </c>
     </row>
     <row r="7" spans="3:9">
       <c r="F7" s="1" t="s">
-        <v>579</v>
+        <v>621</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>580</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8" spans="3:9">
       <c r="D8" s="1" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>582</v>
+        <v>624</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>583</v>
+        <v>625</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>14</v>
@@ -10956,89 +11328,89 @@
     </row>
     <row r="9" spans="3:9">
       <c r="I9" t="s">
-        <v>584</v>
+        <v>626</v>
       </c>
     </row>
     <row r="13" spans="3:9">
       <c r="H13" s="1" t="s">
-        <v>585</v>
+        <v>627</v>
       </c>
     </row>
     <row r="14" spans="3:9">
       <c r="H14" s="1" t="s">
-        <v>586</v>
+        <v>628</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>587</v>
+        <v>629</v>
       </c>
     </row>
     <row r="15" spans="3:9">
       <c r="I15" t="s">
-        <v>588</v>
+        <v>630</v>
       </c>
     </row>
     <row r="19" spans="8:9">
       <c r="H19" s="1" t="s">
-        <v>589</v>
+        <v>631</v>
       </c>
     </row>
     <row r="20" spans="8:9">
       <c r="H20" s="1" t="s">
-        <v>590</v>
+        <v>632</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>591</v>
+        <v>633</v>
       </c>
     </row>
     <row r="21" spans="8:9">
       <c r="I21" t="s">
-        <v>592</v>
+        <v>634</v>
       </c>
     </row>
     <row r="25" spans="8:9">
       <c r="H25" s="1" t="s">
-        <v>593</v>
+        <v>635</v>
       </c>
     </row>
     <row r="26" spans="8:9">
       <c r="H26" s="1" t="s">
-        <v>594</v>
+        <v>636</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>595</v>
+        <v>637</v>
       </c>
     </row>
     <row r="27" spans="8:9">
       <c r="I27" t="s">
-        <v>596</v>
+        <v>638</v>
       </c>
     </row>
     <row r="31" spans="8:9">
       <c r="H31" s="1" t="s">
-        <v>597</v>
+        <v>639</v>
       </c>
     </row>
     <row r="32" spans="8:9">
       <c r="H32" s="1" t="s">
-        <v>598</v>
+        <v>640</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>599</v>
+        <v>641</v>
       </c>
     </row>
     <row r="33" spans="8:9">
       <c r="I33" t="s">
-        <v>600</v>
+        <v>642</v>
       </c>
     </row>
     <row r="37" spans="8:9">
       <c r="H37" s="1" t="s">
-        <v>601</v>
+        <v>643</v>
       </c>
     </row>
     <row r="38" spans="8:9">
       <c r="H38" s="1" t="s">
-        <v>602</v>
+        <v>644</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>17</v>
@@ -11046,12 +11418,12 @@
     </row>
     <row r="43" spans="8:9">
       <c r="H43" s="1" t="s">
-        <v>603</v>
+        <v>645</v>
       </c>
     </row>
     <row r="44" spans="8:9">
       <c r="H44" s="1" t="s">
-        <v>604</v>
+        <v>646</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>100</v>
@@ -11059,17 +11431,17 @@
     </row>
     <row r="45" spans="8:9">
       <c r="I45" t="s">
-        <v>605</v>
+        <v>647</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="6:9">
       <c r="H49" s="1" t="s">
-        <v>606</v>
+        <v>648</v>
       </c>
     </row>
     <row r="50" spans="6:9">
       <c r="H50" s="1" t="s">
-        <v>607</v>
+        <v>649</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>102</v>
@@ -11077,41 +11449,41 @@
     </row>
     <row r="51" spans="6:9">
       <c r="I51" t="s">
-        <v>608</v>
+        <v>650</v>
       </c>
     </row>
     <row r="55" spans="6:9">
       <c r="H55" s="1" t="s">
-        <v>609</v>
+        <v>651</v>
       </c>
     </row>
     <row r="56" spans="6:9">
       <c r="H56" s="1" t="s">
-        <v>610</v>
+        <v>652</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>611</v>
+        <v>653</v>
       </c>
     </row>
     <row r="57" spans="6:9">
       <c r="I57" t="s">
-        <v>612</v>
+        <v>654</v>
       </c>
     </row>
     <row r="61" spans="6:9">
       <c r="F61" s="1" t="s">
-        <v>613</v>
+        <v>655</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>614</v>
+        <v>656</v>
       </c>
     </row>
     <row r="62" spans="6:9">
       <c r="F62" s="1" t="s">
-        <v>615</v>
+        <v>657</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>616</v>
+        <v>658</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>47</v>
@@ -11119,17 +11491,17 @@
     </row>
     <row r="63" spans="6:9">
       <c r="I63" t="s">
-        <v>588</v>
+        <v>630</v>
       </c>
     </row>
     <row r="65" spans="8:9">
       <c r="H65" s="1" t="s">
-        <v>617</v>
+        <v>659</v>
       </c>
     </row>
     <row r="66" spans="8:9">
       <c r="H66" s="1" t="s">
-        <v>618</v>
+        <v>660</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>50</v>
@@ -11137,17 +11509,17 @@
     </row>
     <row r="67" spans="8:9">
       <c r="I67" t="s">
-        <v>592</v>
+        <v>634</v>
       </c>
     </row>
     <row r="69" spans="8:9">
       <c r="H69" s="1" t="s">
-        <v>619</v>
+        <v>661</v>
       </c>
     </row>
     <row r="70" spans="8:9">
       <c r="H70" s="1" t="s">
-        <v>620</v>
+        <v>662</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>94</v>
@@ -11155,35 +11527,35 @@
     </row>
     <row r="71" spans="8:9">
       <c r="I71" t="s">
-        <v>596</v>
+        <v>638</v>
       </c>
     </row>
     <row r="73" spans="8:9">
       <c r="H73" s="1" t="s">
-        <v>621</v>
+        <v>663</v>
       </c>
     </row>
     <row r="74" spans="8:9">
       <c r="H74" s="1" t="s">
-        <v>622</v>
+        <v>664</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>623</v>
+        <v>665</v>
       </c>
     </row>
     <row r="75" spans="8:9">
       <c r="I75" t="s">
-        <v>624</v>
+        <v>666</v>
       </c>
     </row>
     <row r="77" spans="8:9">
       <c r="H77" s="1" t="s">
-        <v>625</v>
+        <v>667</v>
       </c>
     </row>
     <row r="78" spans="8:9">
       <c r="H78" s="1" t="s">
-        <v>626</v>
+        <v>668</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>19</v>
@@ -11191,17 +11563,17 @@
     </row>
     <row r="79" spans="8:9">
       <c r="I79" t="s">
-        <v>627</v>
+        <v>669</v>
       </c>
     </row>
     <row r="81" spans="6:9">
       <c r="H81" s="1" t="s">
-        <v>628</v>
+        <v>670</v>
       </c>
     </row>
     <row r="82" spans="6:9">
       <c r="H82" s="1" t="s">
-        <v>629</v>
+        <v>671</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>22</v>
@@ -11209,41 +11581,41 @@
     </row>
     <row r="83" spans="6:9">
       <c r="I83" t="s">
-        <v>630</v>
+        <v>672</v>
       </c>
     </row>
     <row r="87" spans="6:9">
       <c r="F87" s="1" t="s">
-        <v>631</v>
+        <v>673</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>632</v>
+        <v>674</v>
       </c>
     </row>
     <row r="88" spans="6:9">
       <c r="F88" s="1" t="s">
-        <v>633</v>
+        <v>675</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>634</v>
+        <v>676</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>635</v>
+        <v>677</v>
       </c>
     </row>
     <row r="89" spans="6:9">
       <c r="I89" t="s">
-        <v>636</v>
+        <v>678</v>
       </c>
     </row>
     <row r="92" spans="6:9">
       <c r="H92" s="1" t="s">
-        <v>637</v>
+        <v>679</v>
       </c>
     </row>
     <row r="93" spans="6:9">
       <c r="H93" s="1" t="s">
-        <v>638</v>
+        <v>680</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>25</v>
@@ -11251,17 +11623,17 @@
     </row>
     <row r="94" spans="6:9">
       <c r="I94" t="s">
-        <v>639</v>
+        <v>681</v>
       </c>
     </row>
     <row r="97" spans="6:9">
       <c r="H97" s="1" t="s">
-        <v>640</v>
+        <v>682</v>
       </c>
     </row>
     <row r="98" spans="6:9">
       <c r="H98" s="1" t="s">
-        <v>641</v>
+        <v>683</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>132</v>
@@ -11269,17 +11641,17 @@
     </row>
     <row r="99" spans="6:9">
       <c r="I99" t="s">
-        <v>642</v>
+        <v>684</v>
       </c>
     </row>
     <row r="101" spans="6:9">
       <c r="H101" s="1" t="s">
-        <v>643</v>
+        <v>685</v>
       </c>
     </row>
     <row r="102" spans="6:9">
       <c r="H102" s="1" t="s">
-        <v>644</v>
+        <v>686</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>135</v>
@@ -11287,7 +11659,7 @@
     </row>
     <row r="103" spans="6:9">
       <c r="I103" t="s">
-        <v>645</v>
+        <v>687</v>
       </c>
     </row>
     <row r="105" spans="6:9">
@@ -11297,65 +11669,65 @@
     </row>
     <row r="106" spans="6:9">
       <c r="I106" t="s">
-        <v>645</v>
+        <v>687</v>
       </c>
     </row>
     <row r="109" spans="6:9">
       <c r="F109" s="1" t="s">
-        <v>646</v>
+        <v>688</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>647</v>
+        <v>689</v>
       </c>
     </row>
     <row r="110" spans="6:9">
       <c r="F110" s="1" t="s">
-        <v>648</v>
+        <v>690</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>649</v>
+        <v>691</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="111" spans="6:9">
       <c r="I111" t="s">
-        <v>650</v>
+        <v>692</v>
       </c>
     </row>
     <row r="114" spans="6:9">
       <c r="H114" s="1" t="s">
-        <v>651</v>
+        <v>693</v>
       </c>
     </row>
     <row r="115" spans="6:9">
       <c r="H115" s="1" t="s">
-        <v>652</v>
+        <v>694</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="116" spans="6:9">
       <c r="I116" t="s">
-        <v>650</v>
+        <v>692</v>
       </c>
     </row>
     <row r="120" spans="6:9">
       <c r="F120" s="1" t="s">
-        <v>653</v>
+        <v>695</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
     </row>
     <row r="121" spans="6:9">
       <c r="F121" s="1" t="s">
-        <v>655</v>
+        <v>697</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>656</v>
+        <v>698</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>47</v>
@@ -11363,12 +11735,12 @@
     </row>
     <row r="124" spans="6:9">
       <c r="H124" s="1" t="s">
-        <v>657</v>
+        <v>699</v>
       </c>
     </row>
     <row r="125" spans="6:9">
       <c r="H125" s="1" t="s">
-        <v>658</v>
+        <v>700</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>50</v>
@@ -11376,12 +11748,12 @@
     </row>
     <row r="128" spans="6:9">
       <c r="H128" s="1" t="s">
-        <v>659</v>
+        <v>701</v>
       </c>
     </row>
     <row r="129" spans="8:9">
       <c r="H129" s="1" t="s">
-        <v>660</v>
+        <v>702</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>94</v>
@@ -11389,12 +11761,12 @@
     </row>
     <row r="132" spans="8:9">
       <c r="H132" s="1" t="s">
-        <v>661</v>
+        <v>703</v>
       </c>
     </row>
     <row r="133" spans="8:9">
       <c r="H133" s="1" t="s">
-        <v>662</v>
+        <v>704</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>52</v>
@@ -11402,12 +11774,12 @@
     </row>
     <row r="136" spans="8:9">
       <c r="H136" s="1" t="s">
-        <v>663</v>
+        <v>705</v>
       </c>
     </row>
     <row r="137" spans="8:9">
       <c r="H137" s="1" t="s">
-        <v>664</v>
+        <v>706</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>19</v>
@@ -11420,7 +11792,7 @@
     </row>
     <row r="158" spans="6:6">
       <c r="F158" t="s">
-        <v>665</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>

--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10620"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="T00" sheetId="1" r:id="rId1"/>

--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="7"/>
+    <workbookView windowWidth="23040" windowHeight="10620" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="T00" sheetId="1" r:id="rId1"/>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="708">
   <si>
     <t>序号</t>
   </si>
@@ -1871,18 +1871,18 @@
     <t>昨日收盘价</t>
   </si>
   <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>涨幅</t>
+  </si>
+  <si>
     <t>ma5</t>
   </si>
   <si>
     <t>5日均线</t>
   </si>
   <si>
-    <t>rate</t>
-  </si>
-  <si>
-    <t>涨幅</t>
-  </si>
-  <si>
     <t>ma10</t>
   </si>
   <si>
@@ -1967,16 +1967,16 @@
     <t>价格/60日均线-1, 单位%</t>
   </si>
   <si>
+    <t>对</t>
+  </si>
+  <si>
+    <t>打上创业、主板、科创、北证等的标识，才能计算其是否满足涨停，因为其涨跌停限制不一样</t>
+  </si>
+  <si>
     <t>volume_vs_ma5</t>
   </si>
   <si>
     <t>成交量/5日均量-1, 单位%</t>
-  </si>
-  <si>
-    <t>对</t>
-  </si>
-  <si>
-    <t>打上创业、主板、科创、北证等的标识，才能计算其是否满足涨停，因为其涨跌停限制不一样</t>
   </si>
   <si>
     <t>volume_vs_ma20</t>
@@ -10581,10 +10581,10 @@
         <v>3</v>
       </c>
       <c r="M47" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="N47" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="2:14">
@@ -10610,10 +10610,10 @@
         <v>4</v>
       </c>
       <c r="M48" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="N48" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="2:14">
@@ -10639,10 +10639,10 @@
         <v>5</v>
       </c>
       <c r="M49" t="s">
-        <v>568</v>
+        <v>189</v>
       </c>
       <c r="N49" t="s">
-        <v>569</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:14">
@@ -10650,28 +10650,28 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D50" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
       </c>
       <c r="H50" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="I50" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="L50" s="3">
         <v>6</v>
       </c>
       <c r="M50" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="N50" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:14">
@@ -10697,10 +10697,10 @@
         <v>7</v>
       </c>
       <c r="M51" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="N51" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:14">
@@ -10726,10 +10726,10 @@
         <v>8</v>
       </c>
       <c r="M52" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="N52" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:14">
@@ -10755,10 +10755,10 @@
         <v>9</v>
       </c>
       <c r="M53" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N53" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:14">
@@ -10784,10 +10784,10 @@
         <v>10</v>
       </c>
       <c r="M54" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="N54" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:14">
@@ -10813,10 +10813,10 @@
         <v>11</v>
       </c>
       <c r="M55" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="N55" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="2:14">
@@ -10842,10 +10842,10 @@
         <v>12</v>
       </c>
       <c r="M56" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="N56" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:14">
@@ -10871,10 +10871,10 @@
         <v>13</v>
       </c>
       <c r="M57" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="N57" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:14">
@@ -10900,10 +10900,10 @@
         <v>14</v>
       </c>
       <c r="M58" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="N58" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:14">
@@ -10929,10 +10929,10 @@
         <v>15</v>
       </c>
       <c r="M59" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="N59" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:14">
@@ -10958,10 +10958,10 @@
         <v>16</v>
       </c>
       <c r="M60" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="N60" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:14">
@@ -10987,10 +10987,10 @@
         <v>17</v>
       </c>
       <c r="M61" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="N61" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:14">
@@ -10998,10 +10998,10 @@
         <v>18</v>
       </c>
       <c r="M62" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="N62" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:14">
@@ -11009,10 +11009,10 @@
         <v>19</v>
       </c>
       <c r="M63" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N63" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:14">
@@ -11020,29 +11020,40 @@
         <v>20</v>
       </c>
       <c r="M64" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="N64" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:14">
       <c r="B65" s="3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="L65" s="3">
         <v>21</v>
       </c>
       <c r="M65" t="s">
+        <v>602</v>
+      </c>
+      <c r="N65" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="1:14">
+      <c r="L66" s="3">
+        <v>22</v>
+      </c>
+      <c r="M66" t="s">
         <v>604</v>
       </c>
-      <c r="N65" t="s">
+      <c r="N66" t="s">
         <v>605</v>
       </c>
     </row>

--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="742">
   <si>
     <t>序号</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>目前更新至20260202，可更新至T日</t>
+  </si>
+  <si>
+    <t>目前只到5月份？</t>
   </si>
   <si>
     <t>ods_akshare_stock_yjyg_em</t>
@@ -2008,6 +2011,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">DWD </t>
     </r>
     <r>
@@ -3921,6 +3931,9 @@
       <c r="G12" s="22" t="s">
         <v>43</v>
       </c>
+      <c r="H12" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="13" ht="19.95" customHeight="1" spans="1:8">
       <c r="A13" s="20">
@@ -3936,10 +3949,10 @@
         <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>43</v>
@@ -3960,19 +3973,19 @@
         <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" ht="19.95" customHeight="1" spans="1:7">
@@ -3983,16 +3996,16 @@
         <v>8</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" s="16" t="s">
         <v>21</v>
@@ -4006,16 +4019,16 @@
         <v>8</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G19" s="16" t="s">
         <v>21</v>
@@ -4029,19 +4042,19 @@
         <v>8</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" ht="19.95" customHeight="1" spans="1:7">
@@ -4052,19 +4065,19 @@
         <v>8</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="23" t="s">
         <v>58</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="22" ht="19.95" customHeight="1" spans="1:7">
@@ -4075,19 +4088,19 @@
         <v>8</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" ht="19.95" customHeight="1" spans="1:7">
@@ -4098,16 +4111,16 @@
         <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
         <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G23" s="23" t="s">
         <v>40</v>
@@ -4121,16 +4134,16 @@
         <v>8</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
         <v>31</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G24" s="23" t="s">
         <v>40</v>
@@ -4144,16 +4157,16 @@
         <v>8</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
         <v>31</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G25" s="23" t="s">
         <v>40</v>
@@ -4167,16 +4180,16 @@
         <v>8</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
         <v>31</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="23" t="s">
         <v>40</v>
@@ -4190,19 +4203,19 @@
         <v>8</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
         <v>31</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" ht="19.95" customHeight="1" spans="1:7">
@@ -4213,19 +4226,19 @@
         <v>8</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
         <v>31</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="22" t="s">
         <v>74</v>
-      </c>
-      <c r="F28" t="s">
-        <v>75</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="29" ht="19.95" customHeight="1" spans="1:7">
@@ -4236,19 +4249,19 @@
         <v>8</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" ht="19.95" customHeight="1" spans="1:7">
@@ -4259,19 +4272,19 @@
         <v>8</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" ht="19.95" customHeight="1" spans="1:7">
@@ -4282,19 +4295,19 @@
         <v>8</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F31" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" s="25" t="s">
         <v>83</v>
-      </c>
-      <c r="F31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G31" s="25" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="32" ht="19.95" customHeight="1" spans="1:7">
@@ -4305,19 +4318,19 @@
         <v>8</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" ht="19.95" customHeight="1" spans="1:12">
@@ -4328,19 +4341,19 @@
         <v>8</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G33" s="25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" ht="19.95" customHeight="1" spans="1:12">
@@ -4351,19 +4364,19 @@
         <v>8</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" ht="19.95" customHeight="1" spans="1:12">
@@ -4374,19 +4387,19 @@
         <v>8</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" ht="19.95" customHeight="1"/>
@@ -4399,16 +4412,16 @@
         <v>8</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G38" s="22" t="s">
         <v>16</v>
@@ -4422,19 +4435,19 @@
         <v>8</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D39" t="s">
         <v>31</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" ht="19.95" customHeight="1"/>
@@ -4447,16 +4460,16 @@
         <v>8</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G42" s="22" t="s">
         <v>16</v>
@@ -4470,19 +4483,19 @@
         <v>8</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F43" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" ht="19.95" customHeight="1" spans="1:12">
@@ -4493,19 +4506,19 @@
         <v>8</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D44" t="s">
         <v>27</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F44" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" ht="19.95" customHeight="1" spans="1:12">
@@ -4516,25 +4529,25 @@
         <v>8</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D45" t="s">
         <v>27</v>
       </c>
       <c r="E45" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F45" t="s">
+        <v>110</v>
+      </c>
+      <c r="G45" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="F45" t="s">
-        <v>109</v>
-      </c>
-      <c r="G45" s="23" t="s">
-        <v>107</v>
-      </c>
       <c r="K45" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L45" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" ht="19.95" customHeight="1" spans="1:12">
@@ -4545,19 +4558,19 @@
         <v>8</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D46" t="s">
         <v>27</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F46" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" ht="19.95" customHeight="1" spans="1:12">
@@ -4568,19 +4581,19 @@
         <v>8</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D47" t="s">
         <v>27</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F47" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" ht="19.95" customHeight="1" spans="1:12">
@@ -4591,19 +4604,19 @@
         <v>8</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D48" t="s">
         <v>27</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F48" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" ht="19.95" customHeight="1" spans="1:8">
@@ -4614,19 +4627,19 @@
         <v>8</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G49" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" ht="19.95" customHeight="1" spans="1:8">
@@ -4637,26 +4650,26 @@
         <v>8</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D50" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G50" s="25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" ht="19.95" customHeight="1"/>
     <row r="52" ht="19.95" customHeight="1"/>
     <row r="53" ht="19.95" customHeight="1" spans="1:8">
       <c r="A53" s="27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B53" s="27"/>
       <c r="C53" s="27"/>
@@ -4671,39 +4684,39 @@
         <v>26</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F54" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G54" s="28" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H54" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:8">
       <c r="B55" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F55" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G55" s="28" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H55" s="29" t="s">
         <v>19</v>
@@ -4714,22 +4727,22 @@
         <v>27</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F56" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H56" s="29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:8">
@@ -4737,22 +4750,22 @@
         <v>28</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F57" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H57" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1" spans="1:8">
@@ -4760,58 +4773,58 @@
         <v>29</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E58" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F58" t="s">
+        <v>141</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="H58" s="29" t="s">
         <v>139</v>
-      </c>
-      <c r="F58" t="s">
-        <v>140</v>
-      </c>
-      <c r="G58" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="H58" s="29" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="59" ht="26" customHeight="1" spans="1:8">
       <c r="E59" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F59" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H59" s="29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" ht="19.95" customHeight="1" spans="1:8">
       <c r="E60" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F60" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G60" s="30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" ht="19.95" customHeight="1" spans="1:8">
       <c r="E61" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F61" t="s">
+        <v>148</v>
+      </c>
+      <c r="G61" s="30" t="s">
         <v>146</v>
-      </c>
-      <c r="F61" t="s">
-        <v>147</v>
-      </c>
-      <c r="G61" s="30" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="62" ht="19.95" customHeight="1"/>
@@ -4819,7 +4832,7 @@
     <row r="64" ht="19.95" customHeight="1"/>
     <row r="65" ht="19.95" customHeight="1" spans="1:8">
       <c r="A65" s="27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B65" s="27"/>
       <c r="C65" s="27"/>
@@ -4831,39 +4844,39 @@
     </row>
     <row r="66" ht="39" customHeight="1" spans="1:8">
       <c r="B66" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F66" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G66" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H66" s="29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:8">
       <c r="B67" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F67" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G67" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H67" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68" ht="19.95" customHeight="1"/>
@@ -4976,13 +4989,13 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="2" spans="2:6">
@@ -4990,7 +5003,7 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F2" t="str">
         <f>VLOOKUP(E2,B:B,1,FALSE)</f>
@@ -5002,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F3" t="str">
         <f t="shared" ref="F3:F34" si="0">VLOOKUP(E3,B:B,1,FALSE)</f>
@@ -5014,7 +5027,7 @@
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" si="0"/>
@@ -5026,7 +5039,7 @@
         <v>19</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F5" t="e">
         <f t="shared" si="0"/>
@@ -5038,7 +5051,7 @@
         <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F6" t="e">
         <f t="shared" si="0"/>
@@ -5050,7 +5063,7 @@
         <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="0"/>
@@ -5062,7 +5075,7 @@
         <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" si="0"/>
@@ -5074,7 +5087,7 @@
         <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="0"/>
@@ -5086,7 +5099,7 @@
         <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F10" t="str">
         <f t="shared" si="0"/>
@@ -5098,7 +5111,7 @@
         <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="0"/>
@@ -5110,7 +5123,7 @@
         <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F12" t="str">
         <f t="shared" si="0"/>
@@ -5119,10 +5132,10 @@
     </row>
     <row r="13" spans="2:6">
       <c r="B13" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F13" t="e">
         <f t="shared" si="0"/>
@@ -5131,10 +5144,10 @@
     </row>
     <row r="14" spans="2:6">
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="0"/>
@@ -5143,10 +5156,10 @@
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" t="str">
         <f t="shared" si="0"/>
@@ -5155,10 +5168,10 @@
     </row>
     <row r="16" spans="2:6">
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F16" t="str">
         <f t="shared" si="0"/>
@@ -5167,10 +5180,10 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="0"/>
@@ -5179,10 +5192,10 @@
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F18" t="str">
         <f t="shared" si="0"/>
@@ -5191,10 +5204,10 @@
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F19" t="str">
         <f t="shared" si="0"/>
@@ -5203,7 +5216,7 @@
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E20" t="s">
         <v>38</v>
@@ -5215,7 +5228,7 @@
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E21" t="s">
         <v>32</v>
@@ -5227,7 +5240,7 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s">
         <v>41</v>
@@ -5239,10 +5252,10 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F23" t="str">
         <f t="shared" si="0"/>
@@ -5251,7 +5264,7 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
         <v>35</v>
@@ -5263,10 +5276,10 @@
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F25" t="str">
         <f t="shared" si="0"/>
@@ -5275,10 +5288,10 @@
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" t="str">
         <f t="shared" si="0"/>
@@ -5287,10 +5300,10 @@
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F27" t="str">
         <f t="shared" si="0"/>
@@ -5299,10 +5312,10 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F28" t="str">
         <f t="shared" si="0"/>
@@ -5311,10 +5324,10 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F29" t="str">
         <f t="shared" si="0"/>
@@ -5323,10 +5336,10 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F30" t="str">
         <f t="shared" si="0"/>
@@ -5335,10 +5348,10 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F31" t="e">
         <f t="shared" si="0"/>
@@ -5347,10 +5360,10 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F32" t="str">
         <f t="shared" si="0"/>
@@ -5359,10 +5372,10 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F33" t="e">
         <f t="shared" si="0"/>
@@ -5371,7 +5384,7 @@
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E34" t="s">
         <v>22</v>
@@ -5383,10 +5396,10 @@
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F35" t="e">
         <f t="shared" ref="F35:F60" si="1">VLOOKUP(E35,B:B,1,FALSE)</f>
@@ -5395,7 +5408,7 @@
     </row>
     <row r="36" spans="2:6">
       <c r="B36" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
@@ -5407,10 +5420,10 @@
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F37" t="e">
         <f t="shared" si="1"/>
@@ -5419,7 +5432,7 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
         <v>17</v>
@@ -5431,7 +5444,7 @@
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E39" t="s">
         <v>14</v>
@@ -5443,7 +5456,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E40" t="s">
         <v>25</v>
@@ -5455,10 +5468,10 @@
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F41" t="str">
         <f t="shared" si="1"/>
@@ -5467,10 +5480,10 @@
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F42" t="e">
         <f t="shared" si="1"/>
@@ -5479,10 +5492,10 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F43" t="str">
         <f t="shared" si="1"/>
@@ -5491,10 +5504,10 @@
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E44" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F44" t="str">
         <f t="shared" si="1"/>
@@ -5503,10 +5516,10 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F45" t="e">
         <f t="shared" si="1"/>
@@ -5515,10 +5528,10 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E46" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F46" t="str">
         <f t="shared" si="1"/>
@@ -5527,10 +5540,10 @@
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E47" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F47" t="str">
         <f t="shared" si="1"/>
@@ -5539,10 +5552,10 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E48" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F48" t="str">
         <f t="shared" si="1"/>
@@ -5551,10 +5564,10 @@
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E49" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F49" t="str">
         <f t="shared" si="1"/>
@@ -5563,7 +5576,7 @@
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E50" t="s">
         <v>28</v>
@@ -5575,10 +5588,10 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E51" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F51" t="str">
         <f t="shared" si="1"/>
@@ -5587,7 +5600,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="E52" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F52" t="str">
         <f t="shared" si="1"/>
@@ -5605,7 +5618,7 @@
     </row>
     <row r="54" spans="2:6">
       <c r="E54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F54" t="str">
         <f t="shared" si="1"/>
@@ -5614,7 +5627,7 @@
     </row>
     <row r="55" spans="2:6">
       <c r="E55" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F55" t="str">
         <f t="shared" si="1"/>
@@ -5623,7 +5636,7 @@
     </row>
     <row r="56" spans="2:6">
       <c r="E56" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F56" t="str">
         <f t="shared" si="1"/>
@@ -5632,7 +5645,7 @@
     </row>
     <row r="57" spans="2:6">
       <c r="E57" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F57" t="str">
         <f t="shared" si="1"/>
@@ -5641,7 +5654,7 @@
     </row>
     <row r="58" spans="2:6">
       <c r="E58" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F58" t="str">
         <f t="shared" si="1"/>
@@ -5650,7 +5663,7 @@
     </row>
     <row r="59" spans="2:6">
       <c r="E59" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F59" t="str">
         <f t="shared" si="1"/>
@@ -5659,7 +5672,7 @@
     </row>
     <row r="60" spans="2:6">
       <c r="E60" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F60" t="str">
         <f t="shared" si="1"/>
@@ -5767,19 +5780,19 @@
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:13">
@@ -5787,19 +5800,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F7" s="6">
         <v>1</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:13">
@@ -5807,19 +5820,19 @@
         <v>2</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F8" s="6">
         <v>2</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:13">
@@ -5827,10 +5840,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F9" s="6"/>
     </row>
@@ -5839,33 +5852,33 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F10" s="6"/>
     </row>
     <row r="13" customHeight="1" spans="1:13">
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:13">
       <c r="B14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:13">
@@ -5873,28 +5886,28 @@
         <v>0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>0</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:13">
@@ -5902,28 +5915,28 @@
         <v>1</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F16" s="6">
         <v>1</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K16" s="6">
         <v>1</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:18">
@@ -5931,28 +5944,28 @@
         <v>2</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F17" s="6">
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K17" s="6">
         <v>2</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:18">
@@ -5960,28 +5973,28 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F18" s="6">
         <v>3</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K18" s="6">
         <v>3</v>
       </c>
       <c r="L18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:18">
@@ -5989,28 +6002,28 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F19" s="6">
         <v>4</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K19" s="6">
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:18">
@@ -6018,28 +6031,28 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F20" s="6">
         <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K20" s="6">
         <v>5</v>
       </c>
       <c r="L20" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:18">
@@ -6047,28 +6060,28 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F21" s="6">
         <v>6</v>
       </c>
       <c r="G21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K21" s="6">
         <v>6</v>
       </c>
       <c r="L21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:18">
@@ -6076,28 +6089,28 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F22" s="6">
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K22" s="6">
         <v>7</v>
       </c>
       <c r="L22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:18">
@@ -6105,47 +6118,47 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F23" s="6">
         <v>8</v>
       </c>
       <c r="G23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:18">
       <c r="B27" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:18">
       <c r="B28" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>17</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:18">
@@ -6153,37 +6166,37 @@
         <v>0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>0</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:18">
@@ -6191,37 +6204,37 @@
         <v>1</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C30" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F30" s="6">
         <v>1</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H30" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K30" s="6">
         <v>1</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P30" s="6">
         <v>1</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:18">
@@ -6229,37 +6242,37 @@
         <v>2</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F31" s="6">
         <v>2</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H31" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K31" s="6">
         <v>2</v>
       </c>
       <c r="L31" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M31" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P31" s="6">
         <v>2</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="R31" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:18">
@@ -6267,37 +6280,37 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F32" s="6">
         <v>3</v>
       </c>
       <c r="G32" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H32" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K32" s="6">
         <v>3</v>
       </c>
       <c r="L32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P32" s="6">
         <v>3</v>
       </c>
       <c r="Q32" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="R32" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:18">
@@ -6305,37 +6318,37 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F33" s="6">
         <v>4</v>
       </c>
       <c r="G33" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H33" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K33" s="6">
         <v>4</v>
       </c>
       <c r="L33" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M33" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P33" s="6">
         <v>4</v>
       </c>
       <c r="Q33" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="R33" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:18">
@@ -6343,37 +6356,37 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C34" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F34" s="6">
         <v>5</v>
       </c>
       <c r="G34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H34" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K34" s="6">
         <v>5</v>
       </c>
       <c r="L34" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M34" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P34" s="6">
         <v>5</v>
       </c>
       <c r="Q34" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="R34" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:18">
@@ -6381,37 +6394,37 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C35" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F35" s="6">
         <v>6</v>
       </c>
       <c r="G35" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H35" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K35" s="6">
         <v>6</v>
       </c>
       <c r="L35" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M35" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P35" s="6">
         <v>6</v>
       </c>
       <c r="Q35" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="R35" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:18">
@@ -6419,37 +6432,37 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C36" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F36" s="6">
         <v>7</v>
       </c>
       <c r="G36" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H36" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K36" s="6">
         <v>7</v>
       </c>
       <c r="L36" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M36" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P36" s="6">
         <v>7</v>
       </c>
       <c r="Q36" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="R36" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:18">
@@ -6457,37 +6470,37 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C37" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F37" s="6">
         <v>8</v>
       </c>
       <c r="G37" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H37" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K37" s="6">
         <v>8</v>
       </c>
       <c r="L37" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M37" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P37" s="6">
         <v>8</v>
       </c>
       <c r="Q37" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="R37" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:18">
@@ -6495,37 +6508,37 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C38" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F38" s="6">
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H38" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K38" s="6">
         <v>9</v>
       </c>
       <c r="L38" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M38" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P38" s="6">
         <v>9</v>
       </c>
       <c r="Q38" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="R38" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:18">
@@ -6533,28 +6546,28 @@
         <v>10</v>
       </c>
       <c r="G39" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H39" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K39" s="6">
         <v>10</v>
       </c>
       <c r="L39" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M39" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P39" s="6">
         <v>10</v>
       </c>
       <c r="Q39" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="R39" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:18">
@@ -6565,19 +6578,19 @@
         <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H40" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P40" s="6">
         <v>11</v>
       </c>
       <c r="Q40" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R40" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:18">
@@ -6588,10 +6601,10 @@
         <v>12</v>
       </c>
       <c r="G41" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H41" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:18">
@@ -6599,19 +6612,19 @@
         <v>0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F42" s="6">
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H42" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:18">
@@ -6619,19 +6632,19 @@
         <v>1</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C43" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F43" s="6">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H43" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:18">
@@ -6639,19 +6652,19 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C44" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F44" s="6">
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H44" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:18">
@@ -6659,19 +6672,19 @@
         <v>3</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F45" s="6">
         <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:18">
@@ -6679,19 +6692,19 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C46" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F46" s="6">
         <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:18">
@@ -6699,19 +6712,19 @@
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C47" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F47" s="6">
         <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H47" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:18">
@@ -6719,19 +6732,19 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C48" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F48" s="6">
         <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:8">
@@ -6739,19 +6752,19 @@
         <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F49" s="6">
         <v>20</v>
       </c>
       <c r="G49" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H49" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:8">
@@ -6759,10 +6772,10 @@
         <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:8">
@@ -6770,10 +6783,10 @@
         <v>22</v>
       </c>
       <c r="G51" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H51" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:8">
@@ -6781,10 +6794,10 @@
         <v>23</v>
       </c>
       <c r="G52" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H52" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:8">
@@ -6795,10 +6808,10 @@
         <v>24</v>
       </c>
       <c r="G53" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H53" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:8">
@@ -6809,10 +6822,10 @@
         <v>25</v>
       </c>
       <c r="G54" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H54" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:8">
@@ -6820,19 +6833,19 @@
         <v>0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F55" s="6">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H55" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:8">
@@ -6840,19 +6853,19 @@
         <v>1</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F56" s="6">
         <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H56" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:8">
@@ -6860,10 +6873,10 @@
         <v>2</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C57" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F57" s="6"/>
     </row>
@@ -6872,10 +6885,10 @@
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C58" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F58" s="6"/>
     </row>
@@ -6884,10 +6897,10 @@
         <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C59" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F59" s="6"/>
     </row>
@@ -6921,7 +6934,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -6980,28 +6993,28 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:14">
@@ -7009,28 +7022,28 @@
         <v>1</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G9" s="6">
         <v>1</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L9" s="6">
         <v>1</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N9" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:14">
@@ -7038,28 +7051,28 @@
         <v>2</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G10" s="6">
         <v>2</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L10" s="6">
         <v>2</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:14">
@@ -7067,28 +7080,28 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G11" s="6">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L11" s="6">
         <v>3</v>
       </c>
       <c r="M11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:14">
@@ -7096,28 +7109,28 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G12" s="6">
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I12" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L12" s="6">
         <v>4</v>
       </c>
       <c r="M12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:14">
@@ -7125,28 +7138,28 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G13" s="6">
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L13" s="6">
         <v>5</v>
       </c>
       <c r="M13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:14">
@@ -7154,28 +7167,28 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G14" s="6">
         <v>6</v>
       </c>
       <c r="H14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L14" s="6">
         <v>6</v>
       </c>
       <c r="M14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:14">
@@ -7183,28 +7196,28 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D15" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G15" s="6">
         <v>7</v>
       </c>
       <c r="H15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L15" s="6">
         <v>7</v>
       </c>
       <c r="M15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:14">
@@ -7212,28 +7225,28 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G16" s="6">
         <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I16" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L16" s="6">
         <v>8</v>
       </c>
       <c r="M16" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:14">
@@ -7241,28 +7254,28 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D17" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G17" s="6">
         <v>9</v>
       </c>
       <c r="H17" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L17" s="6">
         <v>9</v>
       </c>
       <c r="M17" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N17" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:14">
@@ -7270,28 +7283,28 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D18" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G18" s="6">
         <v>10</v>
       </c>
       <c r="H18" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I18" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L18" s="6">
         <v>10</v>
       </c>
       <c r="M18" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N18" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:14">
@@ -7299,28 +7312,28 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G19" s="6">
         <v>11</v>
       </c>
       <c r="H19" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L19" s="6">
         <v>11</v>
       </c>
       <c r="M19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:14">
@@ -7328,19 +7341,19 @@
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D20" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G20" s="6">
         <v>12</v>
       </c>
       <c r="H20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I20" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:14">
@@ -7348,19 +7361,19 @@
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D21" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G21" s="6">
         <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I21" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:14">
@@ -7368,19 +7381,19 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D22" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G22" s="6">
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I22" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:14">
@@ -7388,10 +7401,10 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I23" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:14">
@@ -7399,10 +7412,10 @@
         <v>42</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:14">
@@ -7410,10 +7423,10 @@
         <v>41</v>
       </c>
       <c r="H27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:14">
@@ -7421,28 +7434,28 @@
         <v>0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L28" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:14">
@@ -7450,28 +7463,28 @@
         <v>1</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G29" s="6">
         <v>1</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L29" s="6">
         <v>1</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N29" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:14">
@@ -7479,7 +7492,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D30" t="s">
         <v>0</v>
@@ -7488,7 +7501,7 @@
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I30" t="s">
         <v>0</v>
@@ -7497,10 +7510,10 @@
         <v>2</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N30" s="16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:14">
@@ -7508,28 +7521,28 @@
         <v>3</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G31" s="6">
         <v>3</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L31" s="6">
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N31" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="2:14">
@@ -7537,28 +7550,28 @@
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D32" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G32" s="6">
         <v>4</v>
       </c>
       <c r="H32" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I32" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L32" s="6">
         <v>4</v>
       </c>
       <c r="M32" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N32" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:14">
@@ -7566,28 +7579,28 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D33" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G33" s="6">
         <v>5</v>
       </c>
       <c r="H33" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I33" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L33" s="6">
         <v>5</v>
       </c>
       <c r="M33" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N33" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:14">
@@ -7595,28 +7608,28 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D34" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G34" s="6">
         <v>6</v>
       </c>
       <c r="H34" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L34" s="6">
         <v>6</v>
       </c>
       <c r="M34" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N34" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -7624,28 +7637,28 @@
         <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D35" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G35" s="6">
         <v>7</v>
       </c>
       <c r="H35" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I35" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L35" s="6">
         <v>7</v>
       </c>
       <c r="M35" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N35" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -7653,28 +7666,28 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D36" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G36" s="6">
         <v>8</v>
       </c>
       <c r="H36" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I36" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L36" s="6">
         <v>8</v>
       </c>
       <c r="M36" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N36" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:14">
@@ -7682,28 +7695,28 @@
         <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D37" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G37" s="6">
         <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I37" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L37" s="6">
         <v>9</v>
       </c>
       <c r="M37" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N37" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:14">
@@ -7711,19 +7724,19 @@
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D38" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G38" s="6">
         <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I38" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:14">
@@ -7731,19 +7744,19 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D39" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G39" s="6">
         <v>11</v>
       </c>
       <c r="H39" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I39" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:14">
@@ -7751,10 +7764,10 @@
         <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D40" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:14">
@@ -7762,10 +7775,10 @@
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D41" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:14">
@@ -7773,10 +7786,10 @@
         <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D42" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:14">
@@ -7784,10 +7797,10 @@
         <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D43" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:14">
@@ -7795,10 +7808,10 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D44" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:14">
@@ -7806,10 +7819,10 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D45" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:14">
@@ -7817,47 +7830,47 @@
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D46" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:20">
       <c r="B51" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:20">
       <c r="C52" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L52" s="6"/>
       <c r="M52" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R52" s="6"/>
       <c r="S52" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:20">
       <c r="C53" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L53" s="6"/>
       <c r="M53" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R53" s="6"/>
       <c r="S53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:20">
@@ -7865,37 +7878,37 @@
         <v>0</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L54" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="R54" s="9" t="s">
         <v>0</v>
       </c>
       <c r="S54" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:20">
@@ -7903,37 +7916,37 @@
         <v>1</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G55" s="6">
         <v>1</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I55" s="16" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L55" s="6">
         <v>1</v>
       </c>
       <c r="M55" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N55" s="16" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="R55" s="6">
         <v>1</v>
       </c>
       <c r="S55" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="T55" s="16" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="2:20">
@@ -7941,7 +7954,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D56" t="s">
         <v>0</v>
@@ -7950,28 +7963,28 @@
         <v>2</v>
       </c>
       <c r="H56" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I56" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L56" s="6">
         <v>2</v>
       </c>
       <c r="M56" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N56" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="R56" s="6">
         <v>2</v>
       </c>
       <c r="S56" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="T56" s="16" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:20">
@@ -7979,37 +7992,37 @@
         <v>3</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G57" s="6">
         <v>3</v>
       </c>
       <c r="H57" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I57" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L57" s="6">
         <v>3</v>
       </c>
       <c r="M57" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N57" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="R57" s="6">
         <v>3</v>
       </c>
       <c r="S57" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="T57" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:20">
@@ -8017,25 +8030,25 @@
         <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D58" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G58" s="6">
         <v>4</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I58" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L58" s="6">
         <v>4</v>
       </c>
       <c r="M58" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N58" t="s">
         <v>0</v>
@@ -8044,10 +8057,10 @@
         <v>4</v>
       </c>
       <c r="S58" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T58" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:20">
@@ -8055,37 +8068,37 @@
         <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G59" s="6">
         <v>5</v>
       </c>
       <c r="H59" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I59" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L59" s="6">
         <v>5</v>
       </c>
       <c r="M59" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N59" s="16" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R59" s="6">
         <v>5</v>
       </c>
       <c r="S59" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="T59" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:20">
@@ -8093,37 +8106,37 @@
         <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D60" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G60" s="6">
         <v>6</v>
       </c>
       <c r="H60" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I60" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L60" s="6">
         <v>6</v>
       </c>
       <c r="M60" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N60" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="R60" s="6">
         <v>6</v>
       </c>
       <c r="S60" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T60" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:20">
@@ -8131,37 +8144,37 @@
         <v>7</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D61" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G61" s="6">
         <v>7</v>
       </c>
       <c r="H61" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I61" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L61" s="6">
         <v>7</v>
       </c>
       <c r="M61" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N61" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="R61" s="6">
         <v>7</v>
       </c>
       <c r="S61" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="T61" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:20">
@@ -8169,37 +8182,37 @@
         <v>8</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D62" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G62" s="6">
         <v>8</v>
       </c>
       <c r="H62" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I62" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L62" s="6">
         <v>8</v>
       </c>
       <c r="M62" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N62" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="R62" s="6">
         <v>8</v>
       </c>
       <c r="S62" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="T62" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:20">
@@ -8207,37 +8220,37 @@
         <v>9</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D63" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G63" s="6">
         <v>9</v>
       </c>
       <c r="H63" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I63" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L63" s="6">
         <v>9</v>
       </c>
       <c r="M63" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N63" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="R63" s="6">
         <v>9</v>
       </c>
       <c r="S63" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="T63" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:20">
@@ -8245,37 +8258,37 @@
         <v>10</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D64" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G64" s="6">
         <v>10</v>
       </c>
       <c r="H64" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="I64" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L64" s="6">
         <v>10</v>
       </c>
       <c r="M64" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N64" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="R64" s="6">
         <v>10</v>
       </c>
       <c r="S64" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="T64" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:20">
@@ -8283,37 +8296,37 @@
         <v>11</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G65" s="6">
         <v>11</v>
       </c>
       <c r="H65" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I65" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L65" s="6">
         <v>11</v>
       </c>
       <c r="M65" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N65" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="R65" s="6">
         <v>11</v>
       </c>
       <c r="S65" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="T65" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:20">
@@ -8321,37 +8334,37 @@
         <v>12</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D66" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G66" s="6">
         <v>12</v>
       </c>
       <c r="H66" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I66" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L66" s="6">
         <v>12</v>
       </c>
       <c r="M66" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N66" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R66" s="6">
         <v>12</v>
       </c>
       <c r="S66" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="T66" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:20">
@@ -8359,28 +8372,28 @@
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D67" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G67" s="6">
         <v>13</v>
       </c>
       <c r="H67" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I67" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L67" s="6">
         <v>13</v>
       </c>
       <c r="M67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N67" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:20">
@@ -8388,19 +8401,19 @@
         <v>14</v>
       </c>
       <c r="C68" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D68" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L68" s="6">
         <v>14</v>
       </c>
       <c r="M68" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N68" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:20">
@@ -8408,19 +8421,19 @@
         <v>15</v>
       </c>
       <c r="C69" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D69" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L69" s="6">
         <v>15</v>
       </c>
       <c r="M69" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N69" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="2:20">
@@ -8428,19 +8441,19 @@
         <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D70" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L70" s="6">
         <v>16</v>
       </c>
       <c r="M70" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N70" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:20">
@@ -8448,19 +8461,19 @@
         <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D71" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L71" s="6">
         <v>17</v>
       </c>
       <c r="M71" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N71" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:20">
@@ -8468,19 +8481,19 @@
         <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L72" s="6">
         <v>18</v>
       </c>
       <c r="M72" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N72" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:20">
@@ -8488,19 +8501,19 @@
         <v>19</v>
       </c>
       <c r="C73" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D73" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L73" s="6">
         <v>19</v>
       </c>
       <c r="M73" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N73" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:20">
@@ -8508,10 +8521,10 @@
         <v>20</v>
       </c>
       <c r="C74" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D74" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:20">
@@ -8519,10 +8532,10 @@
         <v>21</v>
       </c>
       <c r="C75" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D75" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:20">
@@ -8530,10 +8543,10 @@
         <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D76" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:20">
@@ -8541,10 +8554,10 @@
         <v>23</v>
       </c>
       <c r="C77" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D77" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:20">
@@ -8552,31 +8565,31 @@
         <v>24</v>
       </c>
       <c r="C78" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D78" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:9">
       <c r="B82" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:9">
       <c r="C83" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="2:9">
       <c r="C84" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H84" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:9">
@@ -8584,19 +8597,19 @@
         <v>0</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G85" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:9">
@@ -8604,19 +8617,19 @@
         <v>1</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G86" s="6">
         <v>1</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I86" s="16" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:9">
@@ -8624,19 +8637,19 @@
         <v>2</v>
       </c>
       <c r="C87" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D87" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G87" s="6">
         <v>2</v>
       </c>
       <c r="H87" s="17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:9">
@@ -8644,19 +8657,19 @@
         <v>3</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G88" s="6">
         <v>3</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I88" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:9">
@@ -8664,10 +8677,10 @@
         <v>4</v>
       </c>
       <c r="H89" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I89" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:9">
@@ -8675,10 +8688,10 @@
         <v>5</v>
       </c>
       <c r="H90" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I90" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:9">
@@ -8686,10 +8699,10 @@
         <v>6</v>
       </c>
       <c r="H91" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I91" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:9">
@@ -8697,10 +8710,10 @@
         <v>7</v>
       </c>
       <c r="H92" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I92" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:9">
@@ -8708,10 +8721,10 @@
         <v>8</v>
       </c>
       <c r="H93" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I93" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:9">
@@ -8719,10 +8732,10 @@
         <v>9</v>
       </c>
       <c r="H94" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I94" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -8754,7 +8767,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="15" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -8786,26 +8799,26 @@
     </row>
     <row r="6" customHeight="1" spans="1:14">
       <c r="C6" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:14">
       <c r="C7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:14">
@@ -8813,28 +8826,28 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:14">
@@ -8842,10 +8855,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G9" s="6">
         <v>1</v>
@@ -8863,10 +8876,10 @@
         <v>2</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G10" s="6">
         <v>2</v>
@@ -8884,10 +8897,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G11" s="6">
         <v>3</v>
@@ -8901,10 +8914,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G12" s="6">
         <v>4</v>
@@ -8918,10 +8931,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G13" s="6">
         <v>5</v>
@@ -8935,10 +8948,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G14" s="6">
         <v>6</v>
@@ -8952,10 +8965,10 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G15" s="6">
         <v>7</v>
@@ -8969,10 +8982,10 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D16" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G16" s="6">
         <v>8</v>
@@ -8986,10 +8999,10 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D17" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G17" s="6">
         <v>9</v>
@@ -9003,10 +9016,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D18" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G18" s="6">
         <v>10</v>
@@ -9020,10 +9033,10 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D19" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G19" s="6">
         <v>11</v>
@@ -9054,7 +9067,7 @@
     </row>
     <row r="26" customHeight="1" spans="1:14">
       <c r="A26" s="15" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -9086,26 +9099,26 @@
     </row>
     <row r="30" customHeight="1" spans="1:14">
       <c r="C30" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L30" s="6"/>
       <c r="M30" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:14">
       <c r="C31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L31" s="6"/>
       <c r="M31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:14">
@@ -9113,28 +9126,28 @@
         <v>0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G32" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L32" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:14">
@@ -9142,28 +9155,28 @@
         <v>1</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G33" s="6">
         <v>1</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L33" s="6">
         <v>1</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:14">
@@ -9171,28 +9184,28 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D34" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G34" s="6">
         <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I34" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L34" s="6">
         <v>2</v>
       </c>
       <c r="M34" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N34" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -9200,28 +9213,28 @@
         <v>3</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G35" s="6">
         <v>3</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L35" s="6">
         <v>3</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N35" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -9229,28 +9242,28 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D36" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G36" s="6">
         <v>4</v>
       </c>
       <c r="H36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I36" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L36" s="6">
         <v>4</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:14">
@@ -9258,28 +9271,28 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D37" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G37" s="6">
         <v>5</v>
       </c>
       <c r="H37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I37" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L37" s="6">
         <v>5</v>
       </c>
       <c r="M37" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N37" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:14">
@@ -9287,28 +9300,28 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D38" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G38" s="6">
         <v>6</v>
       </c>
       <c r="H38" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I38" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L38" s="6">
         <v>6</v>
       </c>
       <c r="M38" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N38" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:14">
@@ -9316,28 +9329,28 @@
         <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D39" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G39" s="6">
         <v>7</v>
       </c>
       <c r="H39" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I39" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L39" s="6">
         <v>7</v>
       </c>
       <c r="M39" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N39" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:14">
@@ -9345,19 +9358,19 @@
         <v>8</v>
       </c>
       <c r="H40" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I40" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L40" s="6">
         <v>8</v>
       </c>
       <c r="M40" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N40" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:14">
@@ -9365,19 +9378,19 @@
         <v>9</v>
       </c>
       <c r="H41" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I41" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L41" s="6">
         <v>9</v>
       </c>
       <c r="M41" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N41" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:14">
@@ -9385,10 +9398,10 @@
         <v>10</v>
       </c>
       <c r="H42" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I42" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L42" s="6"/>
     </row>
@@ -9397,10 +9410,10 @@
         <v>11</v>
       </c>
       <c r="H43" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I43" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:14">
@@ -9408,10 +9421,10 @@
         <v>12</v>
       </c>
       <c r="H44" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I44" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:14">
@@ -9419,10 +9432,10 @@
         <v>13</v>
       </c>
       <c r="H45" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I45" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:14">
@@ -9430,10 +9443,10 @@
         <v>14</v>
       </c>
       <c r="H46" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I46" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:14">
@@ -9441,34 +9454,34 @@
         <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I47" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:15">
       <c r="C50" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:15">
       <c r="C51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L51" s="6"/>
       <c r="M51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:15">
@@ -9476,28 +9489,28 @@
         <v>0</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L52" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:15">
@@ -9505,28 +9518,28 @@
         <v>1</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G53" s="6">
         <v>1</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I53" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L53" s="6">
         <v>1</v>
       </c>
       <c r="M53" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N53" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O53" s="16"/>
     </row>
@@ -9535,28 +9548,28 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D54" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G54" s="6">
         <v>2</v>
       </c>
       <c r="H54" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I54" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L54" s="6">
         <v>2</v>
       </c>
       <c r="M54" s="16" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N54" s="16" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O54" s="16"/>
     </row>
@@ -9565,28 +9578,28 @@
         <v>3</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G55" s="6">
         <v>3</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I55" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L55" s="6">
         <v>3</v>
       </c>
       <c r="M55" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N55" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O55" s="16"/>
     </row>
@@ -9595,28 +9608,28 @@
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D56" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G56" s="6">
         <v>4</v>
       </c>
       <c r="H56" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I56" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L56" s="6">
         <v>4</v>
       </c>
       <c r="M56" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N56" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:15">
@@ -9624,28 +9637,28 @@
         <v>5</v>
       </c>
       <c r="C57" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D57" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G57" s="6">
         <v>5</v>
       </c>
       <c r="H57" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I57" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L57" s="6">
         <v>5</v>
       </c>
       <c r="M57" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N57" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:15">
@@ -9653,19 +9666,19 @@
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D58" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G58" s="6">
         <v>6</v>
       </c>
       <c r="H58" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I58" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:15">
@@ -9673,19 +9686,19 @@
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D59" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G59" s="6">
         <v>7</v>
       </c>
       <c r="H59" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I59" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:15">
@@ -9693,19 +9706,19 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D60" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G60" s="6">
         <v>8</v>
       </c>
       <c r="H60" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I60" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:15">
@@ -9713,19 +9726,19 @@
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D61" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G61" s="6">
         <v>9</v>
       </c>
       <c r="H61" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I61" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:15">
@@ -9733,19 +9746,19 @@
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D62" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G62" s="6">
         <v>10</v>
       </c>
       <c r="H62" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I62" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:15">
@@ -9753,19 +9766,19 @@
         <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D63" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G63" s="6">
         <v>11</v>
       </c>
       <c r="H63" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I63" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:15">
@@ -9773,10 +9786,10 @@
         <v>12</v>
       </c>
       <c r="H64" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I64" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="7:9">
@@ -9784,10 +9797,10 @@
         <v>13</v>
       </c>
       <c r="H65" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I65" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="7:9">
@@ -9795,10 +9808,10 @@
         <v>14</v>
       </c>
       <c r="H66" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I66" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -9831,7 +9844,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:13">
       <c r="A3" s="15" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -9863,12 +9876,12 @@
     </row>
     <row r="7" customHeight="1" spans="1:13">
       <c r="B7" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:13">
       <c r="C8" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>26</v>
@@ -9876,7 +9889,7 @@
     </row>
     <row r="9" customHeight="1" spans="1:13">
       <c r="C9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H9" t="s">
         <v>25</v>
@@ -9887,19 +9900,19 @@
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:13">
@@ -9907,19 +9920,19 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G11" s="6">
         <v>1</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:13">
@@ -9927,19 +9940,19 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D12" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G12" s="6">
         <v>2</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:13">
@@ -9947,19 +9960,19 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D13" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G13" s="6">
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:13">
@@ -9967,19 +9980,19 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D14" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G14" s="6">
         <v>4</v>
       </c>
       <c r="H14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I14" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:13">
@@ -9987,15 +10000,15 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D15" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:13">
       <c r="A22" s="15" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -10027,17 +10040,17 @@
     </row>
     <row r="25" customHeight="1" spans="1:13">
       <c r="B25" s="9" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:13">
       <c r="C26" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:13">
       <c r="C27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:13">
@@ -10045,10 +10058,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:13">
@@ -10056,10 +10069,10 @@
         <v>1</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:13">
@@ -10067,10 +10080,10 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D30" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:13">
@@ -10078,10 +10091,10 @@
         <v>3</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:13">
@@ -10089,10 +10102,10 @@
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D32" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:4">
@@ -10100,10 +10113,10 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D33" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -10131,12 +10144,12 @@
   <sheetData>
     <row r="4" customHeight="1" spans="2:4">
       <c r="C4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="2:4">
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:4">
@@ -10144,10 +10157,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:4">
@@ -10155,10 +10168,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:4">
@@ -10166,10 +10179,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:4">
@@ -10177,10 +10190,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:4">
@@ -10188,10 +10201,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:4">
@@ -10199,10 +10212,10 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:4">
@@ -10210,10 +10223,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:4">
@@ -10221,28 +10234,28 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:9">
       <c r="C18" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:9">
       <c r="C19" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:9">
@@ -10250,19 +10263,19 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:9">
@@ -10270,19 +10283,19 @@
         <v>1</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D21" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G21" s="6">
         <v>1</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:9">
@@ -10290,19 +10303,19 @@
         <v>2</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G22" s="6">
         <v>2</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I22" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:9">
@@ -10310,10 +10323,10 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G23" s="6"/>
     </row>
@@ -10322,10 +10335,10 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G24" s="6"/>
     </row>
@@ -10334,10 +10347,10 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D25" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G25" s="6"/>
     </row>
@@ -10346,10 +10359,10 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D26" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G26" s="6"/>
     </row>
@@ -10378,7 +10391,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="12" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -10410,26 +10423,26 @@
     </row>
     <row r="6" customHeight="1" spans="1:14">
       <c r="C6" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:14">
       <c r="C7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:14">
@@ -10437,28 +10450,28 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:14">
@@ -10466,28 +10479,28 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G9" s="6">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L9" s="6">
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:14">
@@ -10495,28 +10508,28 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G10" s="6">
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L10" s="6">
         <v>2</v>
       </c>
       <c r="M10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:14">
@@ -10524,28 +10537,28 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G11" s="6">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L11" s="6">
         <v>3</v>
       </c>
       <c r="M11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:14">
@@ -10553,28 +10566,28 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G12" s="6">
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L12" s="6">
         <v>4</v>
       </c>
       <c r="M12" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:14">
@@ -10582,44 +10595,44 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G13" s="6">
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L13" s="6">
         <v>5</v>
       </c>
       <c r="M13" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:14">
       <c r="C16" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:9">
       <c r="C17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:9">
@@ -10627,19 +10640,19 @@
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:9">
@@ -10647,19 +10660,19 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G19" s="6">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:9">
@@ -10667,19 +10680,19 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D20" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G20" s="6">
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I20" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:9">
@@ -10687,19 +10700,19 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D21" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G21" s="6">
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I21" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:9">
@@ -10707,19 +10720,19 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G22" s="6">
         <v>4</v>
       </c>
       <c r="H22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:9">
@@ -10727,19 +10740,19 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G23" s="6">
         <v>5</v>
       </c>
       <c r="H23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:9">
@@ -10757,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:9">
@@ -10768,10 +10781,10 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:9">
@@ -10779,10 +10792,10 @@
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D31" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="2:9">
@@ -10790,10 +10803,10 @@
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D32" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:4">
@@ -10801,10 +10814,10 @@
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D33" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:4">
@@ -10812,10 +10825,10 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D34" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:4">
@@ -10823,10 +10836,10 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D35" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:4">
@@ -10834,10 +10847,10 @@
         <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D36" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:4">
@@ -10845,10 +10858,10 @@
         <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D37" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:4">
@@ -10856,10 +10869,10 @@
         <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D38" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:4">
@@ -10867,10 +10880,10 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D39" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:4">
@@ -10878,10 +10891,10 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D40" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:4">
@@ -10889,10 +10902,10 @@
         <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D41" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -10922,7 +10935,7 @@
   <sheetData>
     <row r="2" customHeight="1" spans="1:14">
       <c r="A2" s="7" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -10957,7 +10970,7 @@
     </row>
     <row r="15" customHeight="1" spans="1:14">
       <c r="A15" s="10" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -10994,26 +11007,26 @@
     </row>
     <row r="18" customHeight="1" spans="2:14">
       <c r="C18" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:14">
       <c r="C19" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:14">
@@ -11021,28 +11034,28 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:14">
@@ -11050,28 +11063,28 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G21" s="6">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L21" s="6">
         <v>1</v>
       </c>
       <c r="M21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:14">
@@ -11079,28 +11092,28 @@
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D22" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G22" s="6">
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L22" s="6">
         <v>2</v>
       </c>
       <c r="M22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N22" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:14">
@@ -11108,28 +11121,28 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D23" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G23" s="6">
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L23" s="6">
         <v>3</v>
       </c>
       <c r="M23" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N23" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:14">
@@ -11137,28 +11150,28 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D24" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="G24" s="6">
         <v>4</v>
       </c>
       <c r="H24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I24" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L24" s="6">
         <v>4</v>
       </c>
       <c r="M24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N24" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:14">
@@ -11166,28 +11179,28 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G25" s="6">
         <v>5</v>
       </c>
       <c r="H25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I25" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L25" s="6">
         <v>5</v>
       </c>
       <c r="M25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N25" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:14">
@@ -11195,28 +11208,28 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G26" s="6">
         <v>6</v>
       </c>
       <c r="H26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L26" s="6">
         <v>6</v>
       </c>
       <c r="M26" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N26" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:14">
@@ -11224,28 +11237,28 @@
         <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D27" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G27" s="6">
         <v>7</v>
       </c>
       <c r="H27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I27" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L27" s="6">
         <v>7</v>
       </c>
       <c r="M27" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N27" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:14">
@@ -11253,10 +11266,10 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D28" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:14">
@@ -11264,10 +11277,10 @@
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D29" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:14">
@@ -11275,10 +11288,10 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D30" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:14">
@@ -11286,10 +11299,10 @@
         <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D31" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H31" s="1"/>
     </row>
@@ -11298,10 +11311,10 @@
         <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D32" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H32" s="1"/>
     </row>
@@ -11310,10 +11323,10 @@
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="1"/>
@@ -11324,10 +11337,10 @@
         <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D34" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -11335,10 +11348,10 @@
         <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D35" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -11346,10 +11359,10 @@
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D36" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:14">
@@ -11357,34 +11370,34 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D37" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:14">
       <c r="C42" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L42" s="6"/>
       <c r="M42" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:14">
       <c r="C43" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:14">
@@ -11392,28 +11405,28 @@
         <v>0</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G44" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L44" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:14">
@@ -11421,28 +11434,28 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G45" s="6">
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L45" s="6">
         <v>1</v>
       </c>
       <c r="M45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:14">
@@ -11450,28 +11463,28 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G46" s="6">
         <v>2</v>
       </c>
       <c r="H46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L46" s="6">
         <v>2</v>
       </c>
       <c r="M46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:14">
@@ -11479,28 +11492,28 @@
         <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D47" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G47" s="6">
         <v>3</v>
       </c>
       <c r="H47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I47" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L47" s="6">
         <v>3</v>
       </c>
       <c r="M47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N47" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="2:14">
@@ -11508,28 +11521,28 @@
         <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D48" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G48" s="6">
         <v>4</v>
       </c>
       <c r="H48" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="I48" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L48" s="6">
         <v>4</v>
       </c>
       <c r="M48" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N48" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="2:14">
@@ -11537,28 +11550,28 @@
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D49" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G49" s="6">
         <v>5</v>
       </c>
       <c r="H49" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I49" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L49" s="6">
         <v>5</v>
       </c>
       <c r="M49" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N49" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:14">
@@ -11566,28 +11579,28 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D50" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G50" s="6">
         <v>6</v>
       </c>
       <c r="H50" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I50" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L50" s="6">
         <v>6</v>
       </c>
       <c r="M50" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N50" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:14">
@@ -11595,28 +11608,28 @@
         <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D51" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G51" s="6">
         <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I51" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L51" s="6">
         <v>7</v>
       </c>
       <c r="M51" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N51" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:14">
@@ -11624,28 +11637,28 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D52" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="G52" s="6">
         <v>8</v>
       </c>
       <c r="H52" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I52" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L52" s="6">
         <v>8</v>
       </c>
       <c r="M52" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N52" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:14">
@@ -11653,28 +11666,28 @@
         <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D53" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G53" s="6">
         <v>9</v>
       </c>
       <c r="H53" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I53" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L53" s="6">
         <v>9</v>
       </c>
       <c r="M53" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N53" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:14">
@@ -11682,28 +11695,28 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D54" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G54" s="6">
         <v>10</v>
       </c>
       <c r="H54" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I54" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L54" s="6">
         <v>10</v>
       </c>
       <c r="M54" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N54" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:14">
@@ -11711,28 +11724,28 @@
         <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D55" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G55" s="6">
         <v>11</v>
       </c>
       <c r="H55" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I55" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L55" s="6">
         <v>11</v>
       </c>
       <c r="M55" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N55" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="2:14">
@@ -11740,28 +11753,28 @@
         <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D56" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G56" s="6">
         <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I56" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L56" s="6">
         <v>12</v>
       </c>
       <c r="M56" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N56" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:14">
@@ -11769,28 +11782,28 @@
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D57" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G57" s="6">
         <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I57" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L57" s="6">
         <v>13</v>
       </c>
       <c r="M57" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N57" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:14">
@@ -11798,28 +11811,28 @@
         <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D58" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G58" s="6">
         <v>14</v>
       </c>
       <c r="H58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I58" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L58" s="6">
         <v>14</v>
       </c>
       <c r="M58" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N58" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:14">
@@ -11827,28 +11840,28 @@
         <v>15</v>
       </c>
       <c r="C59" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D59" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G59" s="6">
         <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I59" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L59" s="6">
         <v>15</v>
       </c>
       <c r="M59" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N59" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:14">
@@ -11856,28 +11869,28 @@
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D60" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G60" s="6">
         <v>16</v>
       </c>
       <c r="H60" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I60" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L60" s="6">
         <v>16</v>
       </c>
       <c r="M60" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N60" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:14">
@@ -11885,28 +11898,28 @@
         <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D61" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G61" s="6">
         <v>17</v>
       </c>
       <c r="H61" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="I61" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L61" s="6">
         <v>17</v>
       </c>
       <c r="M61" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N61" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:14">
@@ -11914,10 +11927,10 @@
         <v>18</v>
       </c>
       <c r="M62" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N62" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:14">
@@ -11925,10 +11938,10 @@
         <v>19</v>
       </c>
       <c r="M63" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N63" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:14">
@@ -11936,30 +11949,30 @@
         <v>20</v>
       </c>
       <c r="M64" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N64" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:14">
       <c r="B65" s="6" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L65" s="6">
         <v>21</v>
       </c>
       <c r="M65" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N65" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:14">
@@ -11967,20 +11980,20 @@
         <v>22</v>
       </c>
       <c r="M66" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N66" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:14">
       <c r="C67" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:14">
       <c r="A70" s="10" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
@@ -12014,18 +12027,18 @@
     </row>
     <row r="73" customHeight="1" spans="1:14">
       <c r="C73" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:14">
       <c r="C74" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:14">
@@ -12033,19 +12046,19 @@
         <v>0</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G75" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:14">
@@ -12053,19 +12066,19 @@
         <v>1</v>
       </c>
       <c r="C76" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D76" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G76" s="6">
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I76" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:14">
@@ -12073,19 +12086,19 @@
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D77" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G77" s="6">
         <v>2</v>
       </c>
       <c r="H77" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I77" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:14">
@@ -12093,19 +12106,19 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D78" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G78" s="6">
         <v>3</v>
       </c>
       <c r="H78" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I78" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:14">
@@ -12113,19 +12126,19 @@
         <v>4</v>
       </c>
       <c r="C79" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D79" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G79" s="6">
         <v>4</v>
       </c>
       <c r="H79" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I79" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:14">
@@ -12133,19 +12146,19 @@
         <v>5</v>
       </c>
       <c r="C80" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D80" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G80" s="6">
         <v>5</v>
       </c>
       <c r="H80" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I80" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:9">
@@ -12153,19 +12166,19 @@
         <v>6</v>
       </c>
       <c r="C81" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D81" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G81" s="6">
         <v>6</v>
       </c>
       <c r="H81" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="I81" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:9">
@@ -12173,19 +12186,19 @@
         <v>7</v>
       </c>
       <c r="C82" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D82" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G82" s="6">
         <v>7</v>
       </c>
       <c r="H82" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I82" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:9">
@@ -12193,19 +12206,19 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D83" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G83" s="6">
         <v>8</v>
       </c>
       <c r="H83" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I83" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:9">
@@ -12213,19 +12226,19 @@
         <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D84" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G84" s="6">
         <v>9</v>
       </c>
       <c r="H84" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="I84" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:9">
@@ -12233,19 +12246,19 @@
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D85" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G85" s="6">
         <v>10</v>
       </c>
       <c r="H85" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="I85" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:9">
@@ -12253,10 +12266,10 @@
         <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D86" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:9">
@@ -12264,10 +12277,10 @@
         <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D87" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:9">
@@ -12275,10 +12288,10 @@
         <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D88" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="1:9">
@@ -12286,10 +12299,10 @@
         <v>14</v>
       </c>
       <c r="C89" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D89" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:9">
@@ -12297,10 +12310,10 @@
         <v>15</v>
       </c>
       <c r="C90" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D90" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:9">
@@ -12308,15 +12321,15 @@
         <v>16</v>
       </c>
       <c r="C91" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D91" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="1:9">
       <c r="A95" s="10" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
@@ -12340,18 +12353,18 @@
     </row>
     <row r="99" customHeight="1" spans="2:9">
       <c r="C99" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="2:9">
       <c r="C100" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="2:9">
@@ -12359,19 +12372,19 @@
         <v>0</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G101" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="2:9">
@@ -12379,19 +12392,19 @@
         <v>1</v>
       </c>
       <c r="C102" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D102" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G102" s="6">
         <v>1</v>
       </c>
       <c r="H102" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I102" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="2:9">
@@ -12399,19 +12412,19 @@
         <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D103" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G103" s="6">
         <v>2</v>
       </c>
       <c r="H103" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I103" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="2:9">
@@ -12419,19 +12432,19 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D104" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G104" s="6">
         <v>3</v>
       </c>
       <c r="H104" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I104" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="2:9">
@@ -12439,19 +12452,19 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D105" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G105" s="6">
         <v>4</v>
       </c>
       <c r="H105" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I105" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="2:9">
@@ -12459,19 +12472,19 @@
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D106" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G106" s="6">
         <v>5</v>
       </c>
       <c r="H106" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I106" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="2:9">
@@ -12479,19 +12492,19 @@
         <v>6</v>
       </c>
       <c r="C107" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D107" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G107" s="6">
         <v>6</v>
       </c>
       <c r="H107" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="I107" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="2:9">
@@ -12499,19 +12512,19 @@
         <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D108" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="G108" s="6">
         <v>7</v>
       </c>
       <c r="H108" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="I108" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="2:9">
@@ -12519,19 +12532,19 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D109" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G109" s="6">
         <v>8</v>
       </c>
       <c r="H109" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I109" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
   </sheetData>
@@ -12562,29 +12575,29 @@
   <sheetData>
     <row r="5" spans="3:9">
       <c r="C5" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="7" spans="3:9">
       <c r="F7" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8" spans="3:9">
       <c r="D8" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>14</v>
@@ -12592,89 +12605,89 @@
     </row>
     <row r="9" spans="3:9">
       <c r="I9" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="13" spans="3:9">
       <c r="H13" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="14" spans="3:9">
       <c r="H14" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="15" spans="3:9">
       <c r="I15" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="19" spans="8:9">
       <c r="H19" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="20" spans="8:9">
       <c r="H20" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="21" spans="8:9">
       <c r="I21" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="25" spans="8:9">
       <c r="H25" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="26" spans="8:9">
       <c r="H26" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="27" spans="8:9">
       <c r="I27" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="31" spans="8:9">
       <c r="H31" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="32" spans="8:9">
       <c r="H32" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="33" spans="8:9">
       <c r="I33" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="37" spans="8:9">
       <c r="H37" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="38" spans="8:9">
       <c r="H38" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>17</v>
@@ -12682,144 +12695,144 @@
     </row>
     <row r="43" spans="8:9">
       <c r="H43" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="44" spans="8:9">
       <c r="H44" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="8:9">
       <c r="I45" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="6:9">
       <c r="H49" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="50" spans="6:9">
       <c r="H50" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="6:9">
       <c r="I51" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="55" spans="6:9">
       <c r="H55" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="56" spans="6:9">
       <c r="H56" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="57" spans="6:9">
       <c r="I57" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="61" spans="6:9">
       <c r="F61" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="62" spans="6:9">
       <c r="F62" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="6:9">
       <c r="I63" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="65" spans="8:9">
       <c r="H65" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="66" spans="8:9">
       <c r="H66" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="8:9">
       <c r="I67" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="69" spans="8:9">
       <c r="H69" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="70" spans="8:9">
       <c r="H70" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71" spans="8:9">
       <c r="I71" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="73" spans="8:9">
       <c r="H73" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="74" spans="8:9">
       <c r="H74" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="75" spans="8:9">
       <c r="I75" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="77" spans="8:9">
       <c r="H77" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="78" spans="8:9">
       <c r="H78" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>19</v>
@@ -12827,17 +12840,17 @@
     </row>
     <row r="79" spans="8:9">
       <c r="I79" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="81" spans="6:9">
       <c r="H81" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="82" spans="6:9">
       <c r="H82" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>22</v>
@@ -12845,41 +12858,41 @@
     </row>
     <row r="83" spans="6:9">
       <c r="I83" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="87" spans="6:9">
       <c r="F87" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="88" spans="6:9">
       <c r="F88" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="89" spans="6:9">
       <c r="I89" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="92" spans="6:9">
       <c r="H92" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="93" spans="6:9">
       <c r="H93" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>25</v>
@@ -12887,163 +12900,163 @@
     </row>
     <row r="94" spans="6:9">
       <c r="I94" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="97" spans="6:9">
       <c r="H97" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="98" spans="6:9">
       <c r="H98" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="99" spans="6:9">
       <c r="I99" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="101" spans="6:9">
       <c r="H101" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="102" spans="6:9">
       <c r="H102" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="103" spans="6:9">
       <c r="I103" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="105" spans="6:9">
       <c r="I105" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="106" spans="6:9">
       <c r="I106" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="109" spans="6:9">
       <c r="F109" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="110" spans="6:9">
       <c r="F110" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="111" spans="6:9">
       <c r="I111" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="114" spans="6:9">
       <c r="H114" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="115" spans="6:9">
       <c r="H115" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="116" spans="6:9">
       <c r="I116" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="120" spans="6:9">
       <c r="F120" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="121" spans="6:9">
       <c r="F121" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="124" spans="6:9">
       <c r="H124" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="125" spans="6:9">
       <c r="H125" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="128" spans="6:9">
       <c r="H128" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="129" spans="8:9">
       <c r="H129" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="132" spans="8:9">
       <c r="H132" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="133" spans="8:9">
       <c r="H133" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="136" spans="8:9">
       <c r="H136" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="137" spans="8:9">
       <c r="H137" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>19</v>
@@ -13056,7 +13069,7 @@
     </row>
     <row r="158" spans="6:6">
       <c r="F158" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
   </sheetData>

--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="743"/>
+    <workbookView windowWidth="23040" windowHeight="10620" tabRatio="743"/>
   </bookViews>
   <sheets>
     <sheet name="T00" sheetId="1" r:id="rId1"/>
@@ -3371,7 +3371,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12257405" y="10421620"/>
+          <a:off x="12667615" y="10421620"/>
           <a:ext cx="1118870" cy="2019300"/>
         </a:xfrm>
         <a:prstGeom prst="rightBrace">
@@ -3666,7 +3666,7 @@
     <col min="5" max="5" width="46.8518518518519" customWidth="1"/>
     <col min="6" max="6" width="35.4444444444444" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="31.8888888888889" customWidth="1"/>
-    <col min="8" max="8" width="31.1018518518519" customWidth="1"/>
+    <col min="8" max="8" width="37.0833333333333" customWidth="1"/>
     <col min="9" max="9" width="18.2592592592593" customWidth="1"/>
     <col min="10" max="10" width="26.5555555555556" customWidth="1"/>
     <col min="11" max="11" width="31.2222222222222" customWidth="1"/>

--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10620" tabRatio="743"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="743" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="T00" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Sheet3" sheetId="14" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">T00!$A$1:$L$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">T00!$A$1:$L$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Sheet1!$B$1:$F$60</definedName>
     <definedName name="ods_akshare_stock_value_em">Takshare!$C$7</definedName>
     <definedName name="ods_akshare_stock_zh_a_gdhs_detail_em">Takshare!$H$7</definedName>
@@ -81,7 +81,7 @@
     <definedName name="ods_akshare_board_concept_name_ths" localSheetId="3">Tushare!#REF!</definedName>
     <definedName name="ods_akshare_stock_board_concept_index_ths" localSheetId="3">Tushare!#REF!</definedName>
     <definedName name="ods_stock_kline_daily_ts">Tushare!$C$7</definedName>
-    <definedName name="ods_akshare_stock_board_concept_maps_ths">Tcal!$C$27</definedName>
+    <definedName name="ods_akshare_stock_board_concept_maps_ths">Tcal!#REF!</definedName>
     <definedName name="ods_tushare_board_concept_name_ths">Tushare!$C$31</definedName>
     <definedName name="ods_tushare_stock_board_concept_hist_ths">Tushare!$H$31</definedName>
     <definedName name="ods_tushare_stock_board_concept_maps_ths">Tushare!$M$31</definedName>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="781">
   <si>
     <t>序号</t>
   </si>
@@ -419,9 +419,6 @@
     <t>行情数据_同花顺板块行情数据</t>
   </si>
   <si>
-    <t>目前更新至20260127  可到T日</t>
-  </si>
-  <si>
     <t>更新到T-1，完美无缺</t>
   </si>
   <si>
@@ -443,6 +440,12 @@
     <t>从20260520之后不全了</t>
   </si>
   <si>
+    <t>板块数据</t>
+  </si>
+  <si>
+    <t>tushare 板块列表</t>
+  </si>
+  <si>
     <t>ods_tushare_board_concept_name_ths</t>
   </si>
   <si>
@@ -452,6 +455,18 @@
     <t>17点日跑</t>
   </si>
   <si>
+    <t>板块行情数据</t>
+  </si>
+  <si>
+    <t>ods_tushare_stock_board_concept_index_ths</t>
+  </si>
+  <si>
+    <t>板块成份</t>
+  </si>
+  <si>
+    <t>ods_tushare_stock_board_concept_maps_ths</t>
+  </si>
+  <si>
     <t>ods_tushare_stock_board_concept_hist_ths</t>
   </si>
   <si>
@@ -461,9 +476,6 @@
     <t>买token 临时跑一次</t>
   </si>
   <si>
-    <t>ods_tushare_stock_board_concept_maps_ths</t>
-  </si>
-  <si>
     <t>同花顺板块内含股票（核心）</t>
   </si>
   <si>
@@ -584,7 +596,7 @@
     <t>行情数据_同花顺板块内含股票</t>
   </si>
   <si>
-    <t>周末手动更新 爬虫</t>
+    <t>废弃</t>
   </si>
   <si>
     <t>只到3月9日</t>
@@ -612,7 +624,7 @@
   </si>
   <si>
     <t>ods_stock_plate_redbook
-ods_akshare_board_concept_name_ths
+ods_tushare_board_concept_name_ths
 ods_tushare_stock_board_concept_maps_ths</t>
   </si>
   <si>
@@ -629,7 +641,9 @@
   </si>
   <si>
     <t>ods_stock_kline_daily_ts
-ods_tdx_stock_pepb_info
+ods_stock_code_daily_insight
+ods_akshare_stock_value_em
+dwd_shareholder_num_latest
 ods_stock_exchange_market
 dwd_stock_a_total_plate</t>
   </si>
@@ -1771,9 +1785,6 @@
   </si>
   <si>
     <t>爬虫数据</t>
-  </si>
-  <si>
-    <t>手动爬虫有望升级为周跑</t>
   </si>
   <si>
     <t xml:space="preserve">name  </t>
@@ -3440,13 +3451,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>572135</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>1691005</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
@@ -3456,7 +3467,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14946630" y="10421620"/>
+          <a:off x="14317345" y="11688445"/>
           <a:ext cx="1118870" cy="2019300"/>
         </a:xfrm>
         <a:prstGeom prst="rightBrace">
@@ -3741,18 +3752,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
     <col min="2" max="2" width="9" style="6"/>
     <col min="3" max="3" width="12.1111111111111" style="6" customWidth="1"/>
     <col min="4" max="4" width="12.1759259259259" customWidth="1"/>
-    <col min="5" max="5" width="33.2314814814815" customWidth="1"/>
+    <col min="5" max="5" width="20.5740740740741" customWidth="1"/>
     <col min="6" max="6" width="46.8518518518519" customWidth="1"/>
     <col min="7" max="7" width="35.4444444444444" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="31.8888888888889" customWidth="1"/>
-    <col min="9" max="9" width="37.0833333333333" customWidth="1"/>
+    <col min="8" max="8" width="26.2777777777778" customWidth="1"/>
+    <col min="9" max="9" width="46.1759259259259" customWidth="1"/>
     <col min="10" max="10" width="18.2592592592593" customWidth="1"/>
     <col min="11" max="11" width="26.5555555555556" customWidth="1"/>
     <col min="12" max="12" width="31.2222222222222" customWidth="1"/>
@@ -4427,17 +4438,17 @@
       <c r="E28" t="s">
         <v>99</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="25" t="s">
         <v>100</v>
       </c>
       <c r="G28" t="s">
         <v>101</v>
       </c>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" t="s">
         <v>102</v>
-      </c>
-      <c r="I28" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="29" ht="19.95" customHeight="1" spans="1:9">
@@ -4451,664 +4462,720 @@
         <v>61</v>
       </c>
       <c r="D29" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" t="s">
         <v>104</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" t="s">
         <v>106</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="H29" s="22" t="s">
+      <c r="I29" t="s">
         <v>108</v>
       </c>
-      <c r="I29" t="s">
-        <v>109</v>
-      </c>
     </row>
     <row r="30" ht="19.95" customHeight="1" spans="1:9">
-      <c r="A30" s="18">
-        <v>14</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D30" t="s">
-        <v>104</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G30" t="s">
-        <v>111</v>
-      </c>
-      <c r="H30" s="22" t="s">
-        <v>112</v>
-      </c>
+      <c r="F30" s="2"/>
+      <c r="H30" s="22"/>
     </row>
     <row r="31" ht="19.95" customHeight="1" spans="1:9">
-      <c r="A31" s="18">
-        <v>15</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" t="s">
-        <v>104</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G31" t="s">
-        <v>114</v>
-      </c>
-      <c r="H31" s="26" t="s">
-        <v>115</v>
-      </c>
+      <c r="F31" s="2"/>
+      <c r="H31" s="22"/>
     </row>
     <row r="32" ht="19.95" customHeight="1" spans="1:9">
-      <c r="A32" s="18">
-        <v>16</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D32" t="s">
-        <v>104</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G32" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="H32" s="26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="33" ht="19.95" customHeight="1" spans="1:13">
+      <c r="F32" s="2"/>
+      <c r="H32" s="22"/>
+    </row>
+    <row r="33" ht="19.95" customHeight="1" spans="1:9">
       <c r="A33" s="18">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
-        <v>104</v>
+        <v>103</v>
+      </c>
+      <c r="E33" t="s">
+        <v>110</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G33" t="s">
-        <v>119</v>
-      </c>
-      <c r="H33" s="26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="34" ht="19.95" customHeight="1" spans="1:13">
+        <v>112</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" ht="19.95" customHeight="1" spans="1:9">
       <c r="A34" s="18">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>104</v>
+        <v>103</v>
+      </c>
+      <c r="E34" t="s">
+        <v>114</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G34" t="s">
-        <v>121</v>
-      </c>
-      <c r="H34" s="26" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="35" ht="19.95" customHeight="1" spans="1:13">
+      <c r="H34" s="22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" ht="19.95" customHeight="1" spans="1:9">
       <c r="A35" s="18">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35" t="s">
+        <v>116</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H35" s="22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" ht="19.95" customHeight="1" spans="1:9">
+      <c r="A36" s="18">
+        <v>4</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D35" t="s">
-        <v>104</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G35" t="s">
-        <v>123</v>
-      </c>
-      <c r="H35" s="26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="36" ht="19.95" customHeight="1"/>
-    <row r="37" ht="19.95" customHeight="1"/>
-    <row r="38" ht="19.95" customHeight="1" spans="1:13">
+      <c r="D36" t="s">
+        <v>103</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G36" t="s">
+        <v>119</v>
+      </c>
+      <c r="H36" s="26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" ht="19.95" customHeight="1" spans="1:9">
+      <c r="A37" s="18">
+        <v>5</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G37" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="H37" s="26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" ht="19.95" customHeight="1" spans="1:9">
       <c r="A38" s="18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G38" t="s">
-        <v>127</v>
-      </c>
-      <c r="H38" s="22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" ht="19.95" customHeight="1" spans="1:13">
+        <v>123</v>
+      </c>
+      <c r="H38" s="26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" ht="19.95" customHeight="1" spans="1:9">
       <c r="A39" s="18">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" t="s">
+        <v>103</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D39" t="s">
-        <v>39</v>
-      </c>
-      <c r="E39" t="s">
-        <v>128</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="G39" t="s">
-        <v>130</v>
-      </c>
-      <c r="H39" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="I39" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="40" ht="19.95" customHeight="1"/>
+        <v>125</v>
+      </c>
+      <c r="H39" s="26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" ht="19.95" customHeight="1" spans="1:9">
+      <c r="A40" s="18">
+        <v>8</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40" t="s">
+        <v>103</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G40" t="s">
+        <v>127</v>
+      </c>
+      <c r="H40" s="26" t="s">
+        <v>120</v>
+      </c>
+    </row>
     <row r="41" ht="19.95" customHeight="1"/>
-    <row r="42" ht="19.95" customHeight="1" spans="1:13">
-      <c r="A42" s="18">
+    <row r="42" ht="19.95" customHeight="1"/>
+    <row r="43" ht="19.95" customHeight="1" spans="1:9">
+      <c r="A43" s="18">
         <v>1</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D42" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" t="s">
-        <v>134</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G42" t="s">
-        <v>136</v>
-      </c>
-      <c r="H42" s="22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" ht="19.95" customHeight="1" spans="1:13">
-      <c r="A43" s="18">
-        <v>2</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G43" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="44" ht="19.95" customHeight="1" spans="1:13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" ht="19.95" customHeight="1" spans="1:9">
       <c r="A44" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44" t="s">
+        <v>39</v>
+      </c>
+      <c r="E44" t="s">
+        <v>132</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D44" t="s">
-        <v>34</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="G44" t="s">
-        <v>142</v>
-      </c>
-      <c r="H44" s="23" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="45" ht="19.95" customHeight="1" spans="1:13">
-      <c r="A45" s="18">
-        <v>4</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D45" t="s">
-        <v>34</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G45" t="s">
-        <v>145</v>
-      </c>
-      <c r="H45" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M45" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="46" ht="19.95" customHeight="1" spans="1:13">
-      <c r="A46" s="18">
-        <v>5</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D46" t="s">
-        <v>34</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G46" t="s">
-        <v>149</v>
-      </c>
-      <c r="H46" s="23" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="47" ht="19.95" customHeight="1" spans="1:13">
+        <v>134</v>
+      </c>
+      <c r="H44" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="I44" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" ht="19.95" customHeight="1"/>
+    <row r="46" ht="19.95" customHeight="1"/>
+    <row r="47" ht="19.95" customHeight="1" spans="1:9">
       <c r="A47" s="18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D47" t="s">
-        <v>34</v>
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>138</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="G47" t="s">
-        <v>151</v>
-      </c>
-      <c r="H47" s="23" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="48" ht="19.95" customHeight="1" spans="1:13">
+        <v>140</v>
+      </c>
+      <c r="H47" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" ht="19.95" customHeight="1" spans="1:9">
       <c r="A48" s="18">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
-        <v>34</v>
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>141</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="G48" t="s">
-        <v>153</v>
-      </c>
-      <c r="H48" s="23" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="49" ht="19.95" customHeight="1" spans="1:9">
+      <c r="H48" s="22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" ht="19.95" customHeight="1" spans="1:13">
       <c r="A49" s="18">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D49" t="s">
-        <v>154</v>
+        <v>34</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G49" t="s">
-        <v>156</v>
-      </c>
-      <c r="H49" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="I49" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="50" ht="19.95" customHeight="1" spans="1:9">
+        <v>146</v>
+      </c>
+      <c r="H49" s="23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="50" ht="19.95" customHeight="1" spans="1:13">
       <c r="A50" s="18">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
+        <v>34</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G50" t="s">
+        <v>149</v>
+      </c>
+      <c r="H50" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="M50" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="51" ht="19.95" customHeight="1" spans="1:13">
+      <c r="A51" s="18">
+        <v>5</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D51" t="s">
+        <v>34</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G51" t="s">
+        <v>153</v>
+      </c>
+      <c r="H51" s="23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="52" ht="19.95" customHeight="1" spans="1:13">
+      <c r="A52" s="18">
+        <v>6</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" t="s">
+        <v>34</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G52" t="s">
+        <v>155</v>
+      </c>
+      <c r="H52" s="23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="53" ht="19.95" customHeight="1" spans="1:13">
+      <c r="A53" s="18">
+        <v>7</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" t="s">
+        <v>34</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G53" t="s">
+        <v>157</v>
+      </c>
+      <c r="H53" s="23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="54" ht="19.95" customHeight="1" spans="1:13">
+      <c r="A54" s="18">
+        <v>8</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D54" t="s">
+        <v>158</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="G54" t="s">
         <v>160</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H54" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="H50" s="26" t="s">
+      <c r="I54" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="51" ht="19.95" customHeight="1"/>
-    <row r="52" ht="19.95" customHeight="1"/>
-    <row r="53" ht="19.95" customHeight="1" spans="1:9">
-      <c r="A53" s="28" t="s">
+    <row r="55" ht="19.95" customHeight="1" spans="1:13">
+      <c r="A55" s="18">
+        <v>9</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" t="s">
         <v>163</v>
       </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="28"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-    </row>
-    <row r="54" ht="124" customHeight="1" spans="1:9">
-      <c r="A54" s="18">
+      <c r="F55" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G55" t="s">
+        <v>165</v>
+      </c>
+      <c r="H55" s="26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="56" ht="19.95" customHeight="1"/>
+    <row r="57" ht="19.95" customHeight="1"/>
+    <row r="58" ht="19.95" customHeight="1" spans="1:13">
+      <c r="A58" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+    </row>
+    <row r="59" ht="124" customHeight="1" spans="1:13">
+      <c r="A59" s="18">
         <v>26</v>
       </c>
-      <c r="B54" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G54" t="s">
-        <v>147</v>
-      </c>
-      <c r="H54" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="I54" s="30" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1" spans="1:9">
-      <c r="B55" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C55" s="6" t="s">
+      <c r="B59" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G59" t="s">
+        <v>151</v>
+      </c>
+      <c r="H59" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="I59" s="30" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1" spans="1:13">
+      <c r="B60" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G55" t="s">
+      <c r="F60" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G60" t="s">
+        <v>172</v>
+      </c>
+      <c r="H60" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="I60" s="30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" ht="98" customHeight="1" spans="1:13">
+      <c r="A61" s="18">
+        <v>27</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="H55" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="I55" s="30" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="56" ht="67" customHeight="1" spans="1:9">
-      <c r="A56" s="18">
-        <v>27</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C56" s="6" t="s">
+      <c r="C61" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F61" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G61" t="s">
+        <v>174</v>
+      </c>
+      <c r="H61" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="G56" t="s">
-        <v>170</v>
-      </c>
-      <c r="H56" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="I56" s="30" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="57" ht="40" customHeight="1" spans="1:9">
-      <c r="A57" s="18">
+      <c r="I61" s="30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1" spans="1:13">
+      <c r="A62" s="18">
         <v>28</v>
       </c>
-      <c r="B57" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C57" s="6" t="s">
+      <c r="B62" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G57" t="s">
-        <v>173</v>
-      </c>
-      <c r="H57" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="I57" s="30" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="58" ht="36" customHeight="1" spans="1:9">
-      <c r="A58" s="18">
+      <c r="F62" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G62" t="s">
+        <v>177</v>
+      </c>
+      <c r="H62" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="I62" s="30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1" spans="1:13">
+      <c r="A63" s="18">
         <v>29</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C58" s="6" t="s">
+      <c r="B63" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G58" t="s">
-        <v>177</v>
-      </c>
-      <c r="H58" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="I58" s="30" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="59" ht="26" customHeight="1" spans="1:9">
-      <c r="F59" s="2" t="s">
+      <c r="F63" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G63" t="s">
+        <v>181</v>
+      </c>
+      <c r="H63" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="G59" t="s">
+      <c r="I63" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="H59" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="I59" s="30" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="60" ht="19.95" customHeight="1" spans="1:9">
-      <c r="F60" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="G60" t="s">
-        <v>181</v>
-      </c>
-      <c r="H60" s="31" t="s">
+    </row>
+    <row r="64" ht="26" customHeight="1" spans="1:13">
+      <c r="F64" s="2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="61" ht="19.95" customHeight="1" spans="1:9">
-      <c r="F61" s="2" t="s">
+      <c r="G64" t="s">
         <v>183</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H64" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="I64" s="30" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="65" ht="19.95" customHeight="1" spans="1:9">
+      <c r="F65" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="H61" s="31" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="62" ht="19.95" customHeight="1"/>
-    <row r="63" ht="19.95" customHeight="1"/>
-    <row r="64" ht="19.95" customHeight="1"/>
-    <row r="65" ht="19.95" customHeight="1" spans="1:9">
-      <c r="A65" s="28" t="s">
+      <c r="G65" t="s">
         <v>185</v>
       </c>
-      <c r="B65" s="28"/>
-      <c r="C65" s="28"/>
-      <c r="D65" s="28"/>
-      <c r="E65" s="28"/>
-      <c r="F65" s="28"/>
-      <c r="G65" s="28"/>
-      <c r="H65" s="28"/>
-      <c r="I65" s="28"/>
-    </row>
-    <row r="66" ht="39" customHeight="1" spans="1:9">
-      <c r="B66" s="6" t="s">
+      <c r="H65" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>61</v>
-      </c>
+    </row>
+    <row r="66" ht="19.95" customHeight="1" spans="1:9">
       <c r="F66" s="2" t="s">
         <v>187</v>
       </c>
       <c r="G66" t="s">
         <v>188</v>
       </c>
-      <c r="H66" t="s">
-        <v>189</v>
-      </c>
-      <c r="I66" s="30" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="67" ht="24" customHeight="1" spans="1:9">
-      <c r="B67" s="6" t="s">
+      <c r="H66" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="F67" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G67" t="s">
-        <v>192</v>
-      </c>
-      <c r="H67" t="s">
-        <v>193</v>
-      </c>
-      <c r="I67" t="s">
-        <v>187</v>
-      </c>
-    </row>
+    </row>
+    <row r="67" ht="19.95" customHeight="1"/>
     <row r="68" ht="19.95" customHeight="1"/>
     <row r="69" ht="19.95" customHeight="1"/>
-    <row r="70" ht="19.95" customHeight="1"/>
-    <row r="71" ht="19.95" customHeight="1"/>
-    <row r="72" ht="19.95" customHeight="1"/>
+    <row r="70" ht="19.95" customHeight="1" spans="1:9">
+      <c r="A70" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+    </row>
+    <row r="71" ht="39" customHeight="1" spans="1:9">
+      <c r="B71" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G71" t="s">
+        <v>192</v>
+      </c>
+      <c r="H71" t="s">
+        <v>193</v>
+      </c>
+      <c r="I71" s="30" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="72" ht="24" customHeight="1" spans="1:9">
+      <c r="B72" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G72" t="s">
+        <v>196</v>
+      </c>
+      <c r="H72" t="s">
+        <v>197</v>
+      </c>
+      <c r="I72" t="s">
+        <v>191</v>
+      </c>
+    </row>
     <row r="73" ht="19.95" customHeight="1"/>
     <row r="74" ht="19.95" customHeight="1"/>
     <row r="75" ht="19.95" customHeight="1"/>
@@ -5130,13 +5197,18 @@
     <row r="91" ht="19.95" customHeight="1"/>
     <row r="92" ht="19.95" customHeight="1"/>
     <row r="93" ht="19.95" customHeight="1"/>
+    <row r="94" ht="19.95" customHeight="1"/>
+    <row r="95" ht="19.95" customHeight="1"/>
+    <row r="96" ht="19.95" customHeight="1"/>
+    <row r="97" ht="19.95" customHeight="1"/>
+    <row r="98" ht="19.95" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L67" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L72" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="2">
-    <mergeCell ref="A53:I53"/>
-    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A70:I70"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F9" location="ods_akshare_stock_value_em" display="ods_akshare_stock_value_em"/>
@@ -5144,7 +5216,7 @@
     <hyperlink ref="F11" location="ods_akshare_stock_cyq_em" display="ods_akshare_stock_cyq_em"/>
     <hyperlink ref="F12" location="ods_akshare_stock_yjkb_em" display="ods_akshare_stock_yjkb_em"/>
     <hyperlink ref="F13" location="ods_akshare_stock_yjyg_em" display="ods_akshare_stock_yjyg_em"/>
-    <hyperlink ref="F39" location="ods_akshare_stock_a_high_low_statistics" display="ods_akshare_stock_a_high_low_statistics"/>
+    <hyperlink ref="F44" location="ods_akshare_stock_a_high_low_statistics" display="ods_akshare_stock_a_high_low_statistics"/>
     <hyperlink ref="F2" location="ods_trading_days_insight" display="ods_trading_days_insight"/>
     <hyperlink ref="F3" location="ods_stock_code_daily_insight" display="ods_stock_code_daily_insight"/>
     <hyperlink ref="F4" location="ods_stock_chouma_insight" display="ods_stock_chouma_insight"/>
@@ -5159,40 +5231,40 @@
     <hyperlink ref="F21" location="ods_exchange_rate_vantage_detail" display="ods_exchange_rate_vantage_detail"/>
     <hyperlink ref="F22" location="ods_exchange_dxy_vantage" display="ods_exchange_dxy_vantage"/>
     <hyperlink ref="F23" location="ods_akshare_stock_zh_a_spot_em" display="ods_akshare_stock_zh_a_spot_em"/>
-    <hyperlink ref="F38" location="ods_stock_limit_summary_insight" display="ods_stock_limit_summary_insight"/>
-    <hyperlink ref="F42" location="ods_astock_industry_overview" display="ods_astock_industry_overview"/>
-    <hyperlink ref="F43" location="ods_astock_industry_detail" display="ods_astock_industry_detail"/>
-    <hyperlink ref="F44" location="ods_tdx_stock_concept_plate" display="ods_tdx_stock_concept_plate"/>
-    <hyperlink ref="F45" location="ods_tdx_stock_region_plate" display="ods_tdx_stock_region_plate"/>
-    <hyperlink ref="F46" location="ods_tdx_stock_industry_plate" display="ods_tdx_stock_industry_plate"/>
-    <hyperlink ref="F47" location="ods_tdx_stock_style_plate" display="ods_tdx_stock_style_plate"/>
-    <hyperlink ref="F48" location="ods_tdx_stock_index_plate" display="ods_tdx_stock_index_plate"/>
-    <hyperlink ref="F50" location="ods_stock_plate_redbook" display="ods_stock_plate_redbook"/>
-    <hyperlink ref="F54" location="dwd_stock_a_total_plate" display="dwd_stock_a_total_plate"/>
-    <hyperlink ref="F56" location="dwd_ashare_stock_base_info" display="dwd_ashare_stock_base_info"/>
-    <hyperlink ref="F57" location="dwd_stock_ZT_list" display="dwd_stock_zt_list"/>
-    <hyperlink ref="F58" location="dwd_stock_DT_list" display="dwd_stock_dt_list"/>
-    <hyperlink ref="F66" location="dmart_stock_zt_details" display="dmart_stock_zt_details"/>
-    <hyperlink ref="F67" location="dmart_stock_zt_details_expanded" display="dmart_stock_zt_details_expanded"/>
+    <hyperlink ref="F43" location="ods_stock_limit_summary_insight" display="ods_stock_limit_summary_insight"/>
+    <hyperlink ref="F47" location="ods_astock_industry_overview" display="ods_astock_industry_overview"/>
+    <hyperlink ref="F48" location="ods_astock_industry_detail" display="ods_astock_industry_detail"/>
+    <hyperlink ref="F49" location="ods_tdx_stock_concept_plate" display="ods_tdx_stock_concept_plate"/>
+    <hyperlink ref="F50" location="ods_tdx_stock_region_plate" display="ods_tdx_stock_region_plate"/>
+    <hyperlink ref="F51" location="ods_tdx_stock_industry_plate" display="ods_tdx_stock_industry_plate"/>
+    <hyperlink ref="F52" location="ods_tdx_stock_style_plate" display="ods_tdx_stock_style_plate"/>
+    <hyperlink ref="F53" location="ods_tdx_stock_index_plate" display="ods_tdx_stock_index_plate"/>
+    <hyperlink ref="F55" location="ods_stock_plate_redbook" display="ods_stock_plate_redbook"/>
+    <hyperlink ref="F59" location="dwd_stock_a_total_plate" display="dwd_stock_a_total_plate"/>
+    <hyperlink ref="F61" location="dwd_ashare_stock_base_info" display="dwd_ashare_stock_base_info"/>
+    <hyperlink ref="F62" location="dwd_stock_ZT_list" display="dwd_stock_zt_list"/>
+    <hyperlink ref="F63" location="dwd_stock_DT_list" display="dwd_stock_dt_list"/>
+    <hyperlink ref="F71" location="dmart_stock_zt_details" display="dmart_stock_zt_details"/>
+    <hyperlink ref="F72" location="dmart_stock_zt_details_expanded" display="dmart_stock_zt_details_expanded"/>
     <hyperlink ref="I7" location="ods_stock_code_daily_insight" display="ods_stock_code_daily_insight"/>
-    <hyperlink ref="L45" location="dwd_stock_a_total_plate" display="dwd_stock_a_total_plate"/>
+    <hyperlink ref="L50" location="dwd_stock_a_total_plate" display="dwd_stock_a_total_plate"/>
     <hyperlink ref="F24" location="ods_akshare_stock_board_concept_name_em" display="ods_akshare_stock_board_concept_name_em"/>
     <hyperlink ref="F25" location="ods_akshare_stock_board_concept_cons_em" display="ods_akshare_stock_board_concept_cons_em"/>
     <hyperlink ref="F26" location="ods_akshare_stock_board_concept_hist_em" display="ods_akshare_stock_board_concept_hist_em"/>
     <hyperlink ref="F27" location="ods_akshare_board_concept_name_ths" display="ods_akshare_board_concept_name_ths"/>
     <hyperlink ref="F28" location="ods_akshare_stock_board_concept_index_ths" display="ods_akshare_stock_board_concept_index_ths"/>
     <hyperlink ref="F29" location="ods_stock_kline_daily_ts" display="ods_stock_kline_daily_ts"/>
-    <hyperlink ref="F49" location="ods_akshare_stock_board_concept_maps_ths" display="ods_akshare_stock_board_concept_maps_ths"/>
-    <hyperlink ref="F30" location="ods_tushare_board_concept_name_ths" display="ods_tushare_board_concept_name_ths"/>
-    <hyperlink ref="F31" location="ods_tushare_stock_board_concept_hist_ths" display="ods_tushare_stock_board_concept_hist_ths"/>
-    <hyperlink ref="F32" location="ods_tushare_stock_board_concept_maps_ths" display="ods_tushare_stock_board_concept_maps_ths"/>
-    <hyperlink ref="F33" location="ods_tushare_stock_board_concept_name_em" display="ods_tushare_stock_board_concept_name_em"/>
-    <hyperlink ref="F34" location="ods_tushare_stock_board_concept_hist_em" display="ods_tushare_stock_board_concept_hist_em"/>
-    <hyperlink ref="F35" location="ods_tushare_stock_board_concept_maps_em" display="ods_tushare_stock_board_concept_maps_em"/>
-    <hyperlink ref="F55" location="dwd_shareholder_num_latest" display="dwd_shareholder_num_latest"/>
-    <hyperlink ref="F59" location="dwd_stock_technical_indicators" display="dwd_stock_technical_indicators"/>
-    <hyperlink ref="F60" location="dwd_factor_volume_shrinkage" display="dwd_factor_volume_shrinkage"/>
-    <hyperlink ref="F61" location="dwd_factor_summary" display="dwd_factor_summary"/>
+    <hyperlink ref="F54" location="ods_akshare_stock_board_concept_maps_ths" display="ods_akshare_stock_board_concept_maps_ths"/>
+    <hyperlink ref="F33" location="ods_tushare_board_concept_name_ths" display="ods_tushare_board_concept_name_ths"/>
+    <hyperlink ref="F36" location="ods_tushare_stock_board_concept_hist_ths" display="ods_tushare_stock_board_concept_hist_ths"/>
+    <hyperlink ref="F37" location="ods_tushare_stock_board_concept_maps_ths" display="ods_tushare_stock_board_concept_maps_ths"/>
+    <hyperlink ref="F38" location="ods_tushare_stock_board_concept_name_em" display="ods_tushare_stock_board_concept_name_em"/>
+    <hyperlink ref="F39" location="ods_tushare_stock_board_concept_hist_em" display="ods_tushare_stock_board_concept_hist_em"/>
+    <hyperlink ref="F40" location="ods_tushare_stock_board_concept_maps_em" display="ods_tushare_stock_board_concept_maps_em"/>
+    <hyperlink ref="F60" location="dwd_shareholder_num_latest" display="dwd_shareholder_num_latest"/>
+    <hyperlink ref="F64" location="dwd_stock_technical_indicators" display="dwd_stock_technical_indicators"/>
+    <hyperlink ref="F65" location="dwd_factor_volume_shrinkage" display="dwd_factor_volume_shrinkage"/>
+    <hyperlink ref="F66" location="dwd_factor_summary" display="dwd_factor_summary"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -5214,13 +5286,13 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="1" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="2" spans="2:6">
@@ -5228,7 +5300,7 @@
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F2" t="str">
         <f>VLOOKUP(E2,B:B,1,FALSE)</f>
@@ -5240,7 +5312,7 @@
         <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F3" t="str">
         <f t="shared" ref="F3:F34" si="0">VLOOKUP(E3,B:B,1,FALSE)</f>
@@ -5252,7 +5324,7 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" si="0"/>
@@ -5264,7 +5336,7 @@
         <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F5" t="e">
         <f t="shared" si="0"/>
@@ -5276,7 +5348,7 @@
         <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F6" t="e">
         <f t="shared" si="0"/>
@@ -5288,7 +5360,7 @@
         <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="0"/>
@@ -5300,7 +5372,7 @@
         <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" si="0"/>
@@ -5312,7 +5384,7 @@
         <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="0"/>
@@ -5324,7 +5396,7 @@
         <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F10" t="str">
         <f t="shared" si="0"/>
@@ -5336,7 +5408,7 @@
         <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="0"/>
@@ -5360,7 +5432,7 @@
         <v>59</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="F13" t="e">
         <f t="shared" si="0"/>
@@ -5372,7 +5444,7 @@
         <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="0"/>
@@ -5420,7 +5492,7 @@
         <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F18" t="str">
         <f t="shared" si="0"/>
@@ -5513,10 +5585,10 @@
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F26" t="str">
         <f t="shared" si="0"/>
@@ -5525,10 +5597,10 @@
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E27" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F27" t="str">
         <f t="shared" si="0"/>
@@ -5537,7 +5609,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
         <v>81</v>
@@ -5549,7 +5621,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E29" t="s">
         <v>78</v>
@@ -5561,7 +5633,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E30" t="s">
         <v>70</v>
@@ -5573,10 +5645,10 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="F31" t="e">
         <f t="shared" si="0"/>
@@ -5585,7 +5657,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s">
         <v>67</v>
@@ -5597,10 +5669,10 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F33" t="e">
         <f t="shared" si="0"/>
@@ -5609,7 +5681,7 @@
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E34" t="s">
         <v>28</v>
@@ -5621,10 +5693,10 @@
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="F35" t="e">
         <f t="shared" ref="F35:F60" si="1">VLOOKUP(E35,B:B,1,FALSE)</f>
@@ -5633,7 +5705,7 @@
     </row>
     <row r="36" spans="2:6">
       <c r="B36" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E36" t="s">
         <v>24</v>
@@ -5645,10 +5717,10 @@
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F37" t="e">
         <f t="shared" si="1"/>
@@ -5657,7 +5729,7 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E38" t="s">
         <v>21</v>
@@ -5669,7 +5741,7 @@
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
@@ -5681,7 +5753,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E40" t="s">
         <v>32</v>
@@ -5693,7 +5765,7 @@
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E41" t="s">
         <v>63</v>
@@ -5705,10 +5777,10 @@
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="F42" t="e">
         <f t="shared" si="1"/>
@@ -5717,10 +5789,10 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F43" t="str">
         <f t="shared" si="1"/>
@@ -5729,10 +5801,10 @@
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E44" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F44" t="str">
         <f t="shared" si="1"/>
@@ -5741,10 +5813,10 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="F45" t="e">
         <f t="shared" si="1"/>
@@ -5753,10 +5825,10 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E46" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F46" t="str">
         <f t="shared" si="1"/>
@@ -5765,10 +5837,10 @@
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E47" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F47" t="str">
         <f t="shared" si="1"/>
@@ -5777,10 +5849,10 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E48" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F48" t="str">
         <f t="shared" si="1"/>
@@ -5789,10 +5861,10 @@
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E49" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F49" t="str">
         <f t="shared" si="1"/>
@@ -5801,7 +5873,7 @@
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E50" t="s">
         <v>36</v>
@@ -5813,10 +5885,10 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E51" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F51" t="str">
         <f t="shared" si="1"/>
@@ -5825,7 +5897,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="E52" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F52" t="str">
         <f t="shared" si="1"/>
@@ -5843,7 +5915,7 @@
     </row>
     <row r="54" spans="2:6">
       <c r="E54" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F54" t="str">
         <f t="shared" si="1"/>
@@ -5852,7 +5924,7 @@
     </row>
     <row r="55" spans="2:6">
       <c r="E55" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F55" t="str">
         <f t="shared" si="1"/>
@@ -5861,7 +5933,7 @@
     </row>
     <row r="56" spans="2:6">
       <c r="E56" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F56" t="str">
         <f t="shared" si="1"/>
@@ -5870,7 +5942,7 @@
     </row>
     <row r="57" spans="2:6">
       <c r="E57" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F57" t="str">
         <f t="shared" si="1"/>
@@ -5879,7 +5951,7 @@
     </row>
     <row r="58" spans="2:6">
       <c r="E58" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F58" t="str">
         <f t="shared" si="1"/>
@@ -5888,7 +5960,7 @@
     </row>
     <row r="59" spans="2:6">
       <c r="E59" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F59" t="str">
         <f t="shared" si="1"/>
@@ -5976,7 +6048,7 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
   </sheetData>
@@ -6025,19 +6097,19 @@
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:13">
@@ -6045,19 +6117,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F7" s="6">
         <v>1</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:13">
@@ -6065,19 +6137,19 @@
         <v>2</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C8" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F8" s="6">
         <v>2</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H8" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:13">
@@ -6085,10 +6157,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C9" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F9" s="6"/>
     </row>
@@ -6097,10 +6169,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C10" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F10" s="6"/>
     </row>
@@ -6112,7 +6184,7 @@
         <v>68</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:13">
@@ -6123,7 +6195,7 @@
         <v>67</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:13">
@@ -6131,28 +6203,28 @@
         <v>0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>0</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:13">
@@ -6160,28 +6232,28 @@
         <v>1</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C16" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F16" s="6">
         <v>1</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H16" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="K16" s="6">
         <v>1</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:18">
@@ -6189,28 +6261,28 @@
         <v>2</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F17" s="6">
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H17" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K17" s="6">
         <v>2</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M17" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:18">
@@ -6218,28 +6290,28 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C18" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F18" s="6">
         <v>3</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H18" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="K18" s="6">
         <v>3</v>
       </c>
       <c r="L18" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M18" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:18">
@@ -6247,28 +6319,28 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C19" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F19" s="6">
         <v>4</v>
       </c>
       <c r="G19" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H19" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K19" s="6">
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:18">
@@ -6276,28 +6348,28 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C20" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F20" s="6">
         <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="H20" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K20" s="6">
         <v>5</v>
       </c>
       <c r="L20" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:18">
@@ -6305,28 +6377,28 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C21" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F21" s="6">
         <v>6</v>
       </c>
       <c r="G21" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H21" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K21" s="6">
         <v>6</v>
       </c>
       <c r="L21" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M21" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:18">
@@ -6334,28 +6406,28 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C22" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F22" s="6">
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H22" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K22" s="6">
         <v>7</v>
       </c>
       <c r="L22" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:18">
@@ -6363,19 +6435,19 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C23" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F23" s="6">
         <v>8</v>
       </c>
       <c r="G23" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="H23" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:18">
@@ -6386,10 +6458,10 @@
         <v>22</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:18">
@@ -6400,10 +6472,10 @@
         <v>21</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:18">
@@ -6411,37 +6483,37 @@
         <v>0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>0</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:18">
@@ -6449,37 +6521,37 @@
         <v>1</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C30" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F30" s="6">
         <v>1</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H30" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K30" s="6">
         <v>1</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="M30" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="P30" s="6">
         <v>1</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="R30" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:18">
@@ -6487,37 +6559,37 @@
         <v>2</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C31" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F31" s="6">
         <v>2</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H31" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="K31" s="6">
         <v>2</v>
       </c>
       <c r="L31" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="M31" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="P31" s="6">
         <v>2</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="R31" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:18">
@@ -6525,37 +6597,37 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C32" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F32" s="6">
         <v>3</v>
       </c>
       <c r="G32" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H32" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K32" s="6">
         <v>3</v>
       </c>
       <c r="L32" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="M32" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="P32" s="6">
         <v>3</v>
       </c>
       <c r="Q32" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="R32" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:18">
@@ -6563,37 +6635,37 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C33" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F33" s="6">
         <v>4</v>
       </c>
       <c r="G33" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H33" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K33" s="6">
         <v>4</v>
       </c>
       <c r="L33" s="14" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="M33" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="P33" s="6">
         <v>4</v>
       </c>
       <c r="Q33" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="R33" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:18">
@@ -6601,37 +6673,37 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C34" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F34" s="6">
         <v>5</v>
       </c>
       <c r="G34" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="H34" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K34" s="6">
         <v>5</v>
       </c>
       <c r="L34" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="M34" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="P34" s="6">
         <v>5</v>
       </c>
       <c r="Q34" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="R34" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:18">
@@ -6639,37 +6711,37 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F35" s="6">
         <v>6</v>
       </c>
       <c r="G35" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H35" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="K35" s="6">
         <v>6</v>
       </c>
       <c r="L35" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="M35" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="P35" s="6">
         <v>6</v>
       </c>
       <c r="Q35" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="R35" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:18">
@@ -6677,37 +6749,37 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C36" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F36" s="6">
         <v>7</v>
       </c>
       <c r="G36" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H36" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K36" s="6">
         <v>7</v>
       </c>
       <c r="L36" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="M36" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="P36" s="6">
         <v>7</v>
       </c>
       <c r="Q36" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="R36" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:18">
@@ -6715,37 +6787,37 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F37" s="6">
         <v>8</v>
       </c>
       <c r="G37" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H37" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K37" s="6">
         <v>8</v>
       </c>
       <c r="L37" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="M37" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="P37" s="6">
         <v>8</v>
       </c>
       <c r="Q37" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="R37" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:18">
@@ -6753,37 +6825,37 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C38" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F38" s="6">
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H38" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K38" s="6">
         <v>9</v>
       </c>
       <c r="L38" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="M38" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="P38" s="6">
         <v>9</v>
       </c>
       <c r="Q38" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="R38" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:18">
@@ -6791,28 +6863,28 @@
         <v>10</v>
       </c>
       <c r="G39" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H39" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K39" s="6">
         <v>10</v>
       </c>
       <c r="L39" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="M39" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="P39" s="6">
         <v>10</v>
       </c>
       <c r="Q39" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="R39" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:18">
@@ -6823,19 +6895,19 @@
         <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H40" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="P40" s="6">
         <v>11</v>
       </c>
       <c r="Q40" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="R40" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:18">
@@ -6846,10 +6918,10 @@
         <v>12</v>
       </c>
       <c r="G41" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H41" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:18">
@@ -6857,19 +6929,19 @@
         <v>0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F42" s="6">
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="H42" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:18">
@@ -6877,19 +6949,19 @@
         <v>1</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C43" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F43" s="6">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H43" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:18">
@@ -6897,19 +6969,19 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C44" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F44" s="6">
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="H44" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:18">
@@ -6917,19 +6989,19 @@
         <v>3</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C45" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F45" s="6">
         <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H45" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:18">
@@ -6937,19 +7009,19 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C46" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F46" s="6">
         <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H46" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:18">
@@ -6957,19 +7029,19 @@
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C47" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F47" s="6">
         <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="H47" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:18">
@@ -6977,19 +7049,19 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C48" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F48" s="6">
         <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H48" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:8">
@@ -6997,19 +7069,19 @@
         <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C49" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F49" s="6">
         <v>20</v>
       </c>
       <c r="G49" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="H49" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:8">
@@ -7017,10 +7089,10 @@
         <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="H50" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:8">
@@ -7028,10 +7100,10 @@
         <v>22</v>
       </c>
       <c r="G51" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="H51" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:8">
@@ -7039,10 +7111,10 @@
         <v>23</v>
       </c>
       <c r="G52" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="H52" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:8">
@@ -7053,10 +7125,10 @@
         <v>24</v>
       </c>
       <c r="G53" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="H53" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:8">
@@ -7067,10 +7139,10 @@
         <v>25</v>
       </c>
       <c r="G54" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H54" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:8">
@@ -7078,19 +7150,19 @@
         <v>0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F55" s="6">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="H55" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:8">
@@ -7098,19 +7170,19 @@
         <v>1</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C56" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F56" s="6">
         <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="H56" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:8">
@@ -7118,10 +7190,10 @@
         <v>2</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C57" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F57" s="6"/>
     </row>
@@ -7130,10 +7202,10 @@
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C58" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F58" s="6"/>
     </row>
@@ -7142,10 +7214,10 @@
         <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C59" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F59" s="6"/>
     </row>
@@ -7179,7 +7251,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="15" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -7238,28 +7310,28 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:14">
@@ -7267,28 +7339,28 @@
         <v>1</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G9" s="6">
         <v>1</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="L9" s="6">
         <v>1</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N9" s="16" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:14">
@@ -7296,28 +7368,28 @@
         <v>2</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G10" s="6">
         <v>2</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="L10" s="6">
         <v>2</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:14">
@@ -7325,28 +7397,28 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G11" s="6">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I11" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L11" s="6">
         <v>3</v>
       </c>
       <c r="M11" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N11" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:14">
@@ -7354,28 +7426,28 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D12" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G12" s="6">
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I12" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="L12" s="6">
         <v>4</v>
       </c>
       <c r="M12" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="N12" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:14">
@@ -7383,28 +7455,28 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D13" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G13" s="6">
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I13" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="L13" s="6">
         <v>5</v>
       </c>
       <c r="M13" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="N13" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:14">
@@ -7412,28 +7484,28 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G14" s="6">
         <v>6</v>
       </c>
       <c r="H14" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="I14" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L14" s="6">
         <v>6</v>
       </c>
       <c r="M14" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="N14" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:14">
@@ -7441,28 +7513,28 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D15" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G15" s="6">
         <v>7</v>
       </c>
       <c r="H15" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="I15" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="L15" s="6">
         <v>7</v>
       </c>
       <c r="M15" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N15" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:14">
@@ -7470,28 +7542,28 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D16" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="G16" s="6">
         <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="I16" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L16" s="6">
         <v>8</v>
       </c>
       <c r="M16" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="N16" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:14">
@@ -7499,28 +7571,28 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D17" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="G17" s="6">
         <v>9</v>
       </c>
       <c r="H17" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I17" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="L17" s="6">
         <v>9</v>
       </c>
       <c r="M17" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="N17" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:14">
@@ -7528,28 +7600,28 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D18" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G18" s="6">
         <v>10</v>
       </c>
       <c r="H18" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="I18" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="L18" s="6">
         <v>10</v>
       </c>
       <c r="M18" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N18" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:14">
@@ -7557,28 +7629,28 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D19" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G19" s="6">
         <v>11</v>
       </c>
       <c r="H19" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="I19" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L19" s="6">
         <v>11</v>
       </c>
       <c r="M19" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="N19" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:14">
@@ -7586,19 +7658,19 @@
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D20" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G20" s="6">
         <v>12</v>
       </c>
       <c r="H20" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I20" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:14">
@@ -7606,19 +7678,19 @@
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D21" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G21" s="6">
         <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="I21" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:14">
@@ -7626,19 +7698,19 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D22" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="G22" s="6">
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="I22" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:14">
@@ -7646,10 +7718,10 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="I23" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:14">
@@ -7660,7 +7732,7 @@
         <v>60</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:14">
@@ -7671,7 +7743,7 @@
         <v>59</v>
       </c>
       <c r="M27" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:14">
@@ -7679,28 +7751,28 @@
         <v>0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L28" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:14">
@@ -7708,28 +7780,28 @@
         <v>1</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="G29" s="6">
         <v>1</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="L29" s="6">
         <v>1</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N29" s="16" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:14">
@@ -7737,7 +7809,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D30" t="s">
         <v>0</v>
@@ -7746,7 +7818,7 @@
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="I30" t="s">
         <v>0</v>
@@ -7755,10 +7827,10 @@
         <v>2</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="N30" s="16" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:14">
@@ -7766,28 +7838,28 @@
         <v>3</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G31" s="6">
         <v>3</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="L31" s="6">
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="N31" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="2:14">
@@ -7795,28 +7867,28 @@
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D32" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="G32" s="6">
         <v>4</v>
       </c>
       <c r="H32" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I32" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L32" s="6">
         <v>4</v>
       </c>
       <c r="M32" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="N32" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:14">
@@ -7824,28 +7896,28 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D33" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G33" s="6">
         <v>5</v>
       </c>
       <c r="H33" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="I33" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="L33" s="6">
         <v>5</v>
       </c>
       <c r="M33" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="N33" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:14">
@@ -7853,28 +7925,28 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D34" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="G34" s="6">
         <v>6</v>
       </c>
       <c r="H34" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="I34" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="L34" s="6">
         <v>6</v>
       </c>
       <c r="M34" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="N34" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -7882,28 +7954,28 @@
         <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D35" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G35" s="6">
         <v>7</v>
       </c>
       <c r="H35" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="I35" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="L35" s="6">
         <v>7</v>
       </c>
       <c r="M35" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="N35" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -7911,28 +7983,28 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D36" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="G36" s="6">
         <v>8</v>
       </c>
       <c r="H36" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I36" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="L36" s="6">
         <v>8</v>
       </c>
       <c r="M36" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N36" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:14">
@@ -7940,28 +8012,28 @@
         <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D37" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="G37" s="6">
         <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="I37" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L37" s="6">
         <v>9</v>
       </c>
       <c r="M37" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="N37" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:14">
@@ -7969,19 +8041,19 @@
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D38" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="G38" s="6">
         <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="I38" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:14">
@@ -7989,19 +8061,19 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D39" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="G39" s="6">
         <v>11</v>
       </c>
       <c r="H39" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="I39" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:14">
@@ -8009,10 +8081,10 @@
         <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D40" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:14">
@@ -8020,10 +8092,10 @@
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D41" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:14">
@@ -8031,10 +8103,10 @@
         <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D42" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:14">
@@ -8042,10 +8114,10 @@
         <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D43" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:14">
@@ -8053,10 +8125,10 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D44" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:14">
@@ -8064,10 +8136,10 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D45" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:14">
@@ -8075,15 +8147,15 @@
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D46" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:20">
       <c r="B51" s="9" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:20">
@@ -8123,37 +8195,37 @@
         <v>0</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L54" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R54" s="9" t="s">
         <v>0</v>
       </c>
       <c r="S54" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:20">
@@ -8161,37 +8233,37 @@
         <v>1</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="G55" s="6">
         <v>1</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I55" s="16" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="L55" s="6">
         <v>1</v>
       </c>
       <c r="M55" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N55" s="16" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="R55" s="6">
         <v>1</v>
       </c>
       <c r="S55" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="T55" s="16" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="2:20">
@@ -8199,7 +8271,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D56" t="s">
         <v>0</v>
@@ -8208,28 +8280,28 @@
         <v>2</v>
       </c>
       <c r="H56" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="I56" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="L56" s="6">
         <v>2</v>
       </c>
       <c r="M56" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="N56" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="R56" s="6">
         <v>2</v>
       </c>
       <c r="S56" s="16" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="T56" s="16" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:20">
@@ -8237,37 +8309,37 @@
         <v>3</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G57" s="6">
         <v>3</v>
       </c>
       <c r="H57" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="I57" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L57" s="6">
         <v>3</v>
       </c>
       <c r="M57" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="N57" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="R57" s="6">
         <v>3</v>
       </c>
       <c r="S57" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="T57" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:20">
@@ -8275,25 +8347,25 @@
         <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D58" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G58" s="6">
         <v>4</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="I58" s="16" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="L58" s="6">
         <v>4</v>
       </c>
       <c r="M58" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="N58" t="s">
         <v>0</v>
@@ -8302,10 +8374,10 @@
         <v>4</v>
       </c>
       <c r="S58" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="T58" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:20">
@@ -8313,37 +8385,37 @@
         <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D59" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G59" s="6">
         <v>5</v>
       </c>
       <c r="H59" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I59" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="L59" s="6">
         <v>5</v>
       </c>
       <c r="M59" s="16" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N59" s="16" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="R59" s="6">
         <v>5</v>
       </c>
       <c r="S59" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T59" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:20">
@@ -8351,37 +8423,37 @@
         <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D60" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="G60" s="6">
         <v>6</v>
       </c>
       <c r="H60" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="I60" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="L60" s="6">
         <v>6</v>
       </c>
       <c r="M60" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N60" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="R60" s="6">
         <v>6</v>
       </c>
       <c r="S60" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="T60" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:20">
@@ -8389,37 +8461,37 @@
         <v>7</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D61" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G61" s="6">
         <v>7</v>
       </c>
       <c r="H61" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I61" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="L61" s="6">
         <v>7</v>
       </c>
       <c r="M61" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="N61" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="R61" s="6">
         <v>7</v>
       </c>
       <c r="S61" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="T61" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:20">
@@ -8427,37 +8499,37 @@
         <v>8</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D62" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="G62" s="6">
         <v>8</v>
       </c>
       <c r="H62" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="I62" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L62" s="6">
         <v>8</v>
       </c>
       <c r="M62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="N62" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="R62" s="6">
         <v>8</v>
       </c>
       <c r="S62" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="T62" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:20">
@@ -8465,37 +8537,37 @@
         <v>9</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D63" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="G63" s="6">
         <v>9</v>
       </c>
       <c r="H63" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="I63" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="L63" s="6">
         <v>9</v>
       </c>
       <c r="M63" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="N63" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="R63" s="6">
         <v>9</v>
       </c>
       <c r="S63" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="T63" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:20">
@@ -8503,37 +8575,37 @@
         <v>10</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D64" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="G64" s="6">
         <v>10</v>
       </c>
       <c r="H64" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="I64" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="L64" s="6">
         <v>10</v>
       </c>
       <c r="M64" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="N64" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="R64" s="6">
         <v>10</v>
       </c>
       <c r="S64" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="T64" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:20">
@@ -8541,37 +8613,37 @@
         <v>11</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="G65" s="6">
         <v>11</v>
       </c>
       <c r="H65" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I65" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="L65" s="6">
         <v>11</v>
       </c>
       <c r="M65" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="N65" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="R65" s="6">
         <v>11</v>
       </c>
       <c r="S65" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="T65" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:20">
@@ -8579,37 +8651,37 @@
         <v>12</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D66" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="G66" s="6">
         <v>12</v>
       </c>
       <c r="H66" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="I66" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="L66" s="6">
         <v>12</v>
       </c>
       <c r="M66" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="N66" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="R66" s="6">
         <v>12</v>
       </c>
       <c r="S66" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="T66" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:20">
@@ -8617,28 +8689,28 @@
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D67" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="G67" s="6">
         <v>13</v>
       </c>
       <c r="H67" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="I67" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="L67" s="6">
         <v>13</v>
       </c>
       <c r="M67" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N67" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:20">
@@ -8646,19 +8718,19 @@
         <v>14</v>
       </c>
       <c r="C68" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D68" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="L68" s="6">
         <v>14</v>
       </c>
       <c r="M68" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N68" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:20">
@@ -8666,19 +8738,19 @@
         <v>15</v>
       </c>
       <c r="C69" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D69" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="L69" s="6">
         <v>15</v>
       </c>
       <c r="M69" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="N69" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="2:20">
@@ -8686,19 +8758,19 @@
         <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D70" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="L70" s="6">
         <v>16</v>
       </c>
       <c r="M70" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="N70" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:20">
@@ -8706,19 +8778,19 @@
         <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D71" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L71" s="6">
         <v>17</v>
       </c>
       <c r="M71" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="N71" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:20">
@@ -8726,19 +8798,19 @@
         <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D72" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="L72" s="6">
         <v>18</v>
       </c>
       <c r="M72" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="N72" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:20">
@@ -8746,19 +8818,19 @@
         <v>19</v>
       </c>
       <c r="C73" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="L73" s="6">
         <v>19</v>
       </c>
       <c r="M73" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="N73" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:20">
@@ -8766,10 +8838,10 @@
         <v>20</v>
       </c>
       <c r="C74" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:20">
@@ -8777,10 +8849,10 @@
         <v>21</v>
       </c>
       <c r="C75" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D75" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:20">
@@ -8788,10 +8860,10 @@
         <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D76" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:20">
@@ -8799,10 +8871,10 @@
         <v>23</v>
       </c>
       <c r="C77" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D77" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:20">
@@ -8810,15 +8882,15 @@
         <v>24</v>
       </c>
       <c r="C78" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="D78" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:9">
       <c r="B82" s="9" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:9">
@@ -8842,19 +8914,19 @@
         <v>0</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G85" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:9">
@@ -8862,19 +8934,19 @@
         <v>1</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G86" s="6">
         <v>1</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I86" s="16" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:9">
@@ -8882,19 +8954,19 @@
         <v>2</v>
       </c>
       <c r="C87" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D87" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G87" s="6">
         <v>2</v>
       </c>
       <c r="H87" s="17" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:9">
@@ -8902,19 +8974,19 @@
         <v>3</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G88" s="6">
         <v>3</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="I88" s="16" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:9">
@@ -8922,10 +8994,10 @@
         <v>4</v>
       </c>
       <c r="H89" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I89" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:9">
@@ -8933,10 +9005,10 @@
         <v>5</v>
       </c>
       <c r="H90" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I90" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:9">
@@ -8944,10 +9016,10 @@
         <v>6</v>
       </c>
       <c r="H91" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I91" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:9">
@@ -8955,10 +9027,10 @@
         <v>7</v>
       </c>
       <c r="H92" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I92" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:9">
@@ -8966,10 +9038,10 @@
         <v>8</v>
       </c>
       <c r="H93" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="I93" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:9">
@@ -8977,10 +9049,10 @@
         <v>9</v>
       </c>
       <c r="H94" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="I94" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -9012,7 +9084,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="15" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -9044,26 +9116,26 @@
     </row>
     <row r="6" customHeight="1" spans="1:14">
       <c r="C6" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="1" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:14">
       <c r="C7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H7" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:14">
@@ -9071,28 +9143,28 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:14">
@@ -9100,10 +9172,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G9" s="6">
         <v>1</v>
@@ -9121,10 +9193,10 @@
         <v>2</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G10" s="6">
         <v>2</v>
@@ -9142,10 +9214,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D11" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G11" s="6">
         <v>3</v>
@@ -9159,10 +9231,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D12" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G12" s="6">
         <v>4</v>
@@ -9176,10 +9248,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D13" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G13" s="6">
         <v>5</v>
@@ -9193,10 +9265,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D14" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G14" s="6">
         <v>6</v>
@@ -9210,10 +9282,10 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D15" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G15" s="6">
         <v>7</v>
@@ -9227,10 +9299,10 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D16" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="G16" s="6">
         <v>8</v>
@@ -9244,10 +9316,10 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D17" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="G17" s="6">
         <v>9</v>
@@ -9261,10 +9333,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D18" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="G18" s="6">
         <v>10</v>
@@ -9278,10 +9350,10 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D19" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="G19" s="6">
         <v>11</v>
@@ -9312,7 +9384,7 @@
     </row>
     <row r="26" customHeight="1" spans="1:14">
       <c r="A26" s="15" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -9344,26 +9416,26 @@
     </row>
     <row r="30" customHeight="1" spans="1:14">
       <c r="C30" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L30" s="6"/>
       <c r="M30" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:14">
       <c r="C31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H31" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="L31" s="6"/>
       <c r="M31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:14">
@@ -9371,28 +9443,28 @@
         <v>0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G32" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L32" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:14">
@@ -9400,28 +9472,28 @@
         <v>1</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G33" s="6">
         <v>1</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="L33" s="6">
         <v>1</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:14">
@@ -9429,28 +9501,28 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D34" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G34" s="6">
         <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="I34" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L34" s="6">
         <v>2</v>
       </c>
       <c r="M34" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="N34" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -9458,28 +9530,28 @@
         <v>3</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G35" s="6">
         <v>3</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="L35" s="6">
         <v>3</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="N35" s="16" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -9487,28 +9559,28 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="D36" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="G36" s="6">
         <v>4</v>
       </c>
       <c r="H36" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I36" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L36" s="6">
         <v>4</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:14">
@@ -9516,28 +9588,28 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D37" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G37" s="6">
         <v>5</v>
       </c>
       <c r="H37" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I37" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="L37" s="6">
         <v>5</v>
       </c>
       <c r="M37" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N37" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:14">
@@ -9545,28 +9617,28 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D38" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="G38" s="6">
         <v>6</v>
       </c>
       <c r="H38" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I38" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="L38" s="6">
         <v>6</v>
       </c>
       <c r="M38" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="N38" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:14">
@@ -9574,28 +9646,28 @@
         <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D39" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G39" s="6">
         <v>7</v>
       </c>
       <c r="H39" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I39" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L39" s="6">
         <v>7</v>
       </c>
       <c r="M39" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="N39" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:14">
@@ -9603,19 +9675,19 @@
         <v>8</v>
       </c>
       <c r="H40" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I40" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="L40" s="6">
         <v>8</v>
       </c>
       <c r="M40" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="N40" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:14">
@@ -9623,19 +9695,19 @@
         <v>9</v>
       </c>
       <c r="H41" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="I41" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="L41" s="6">
         <v>9</v>
       </c>
       <c r="M41" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="N41" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:14">
@@ -9643,10 +9715,10 @@
         <v>10</v>
       </c>
       <c r="H42" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="I42" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="L42" s="6"/>
     </row>
@@ -9655,10 +9727,10 @@
         <v>11</v>
       </c>
       <c r="H43" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I43" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:14">
@@ -9666,10 +9738,10 @@
         <v>12</v>
       </c>
       <c r="H44" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="I44" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:14">
@@ -9677,10 +9749,10 @@
         <v>13</v>
       </c>
       <c r="H45" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="I45" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:14">
@@ -9688,10 +9760,10 @@
         <v>14</v>
       </c>
       <c r="H46" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="I46" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:14">
@@ -9699,34 +9771,34 @@
         <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="I47" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:15">
       <c r="C50" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:15">
       <c r="C51" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H51" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="L51" s="6"/>
       <c r="M51" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:15">
@@ -9734,28 +9806,28 @@
         <v>0</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L52" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:15">
@@ -9763,28 +9835,28 @@
         <v>1</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G53" s="6">
         <v>1</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I53" s="16" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="L53" s="6">
         <v>1</v>
       </c>
       <c r="M53" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N53" s="16" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="O53" s="16"/>
     </row>
@@ -9793,28 +9865,28 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D54" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G54" s="6">
         <v>2</v>
       </c>
       <c r="H54" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="I54" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L54" s="6">
         <v>2</v>
       </c>
       <c r="M54" s="16" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="N54" s="16" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="O54" s="16"/>
     </row>
@@ -9823,28 +9895,28 @@
         <v>3</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G55" s="6">
         <v>3</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="I55" s="16" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="L55" s="6">
         <v>3</v>
       </c>
       <c r="M55" s="16" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="N55" s="16" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="O55" s="16"/>
     </row>
@@ -9853,28 +9925,28 @@
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D56" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G56" s="6">
         <v>4</v>
       </c>
       <c r="H56" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I56" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L56" s="6">
         <v>4</v>
       </c>
       <c r="M56" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N56" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:15">
@@ -9882,28 +9954,28 @@
         <v>5</v>
       </c>
       <c r="C57" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D57" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="G57" s="6">
         <v>5</v>
       </c>
       <c r="H57" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I57" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="L57" s="6">
         <v>5</v>
       </c>
       <c r="M57" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N57" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:15">
@@ -9911,19 +9983,19 @@
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D58" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="G58" s="6">
         <v>6</v>
       </c>
       <c r="H58" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I58" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:15">
@@ -9931,19 +10003,19 @@
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D59" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="G59" s="6">
         <v>7</v>
       </c>
       <c r="H59" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I59" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:15">
@@ -9951,19 +10023,19 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D60" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="G60" s="6">
         <v>8</v>
       </c>
       <c r="H60" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="I60" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:15">
@@ -9971,19 +10043,19 @@
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D61" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="G61" s="6">
         <v>9</v>
       </c>
       <c r="H61" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I61" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:15">
@@ -9991,19 +10063,19 @@
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D62" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="G62" s="6">
         <v>10</v>
       </c>
       <c r="H62" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="I62" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:15">
@@ -10011,19 +10083,19 @@
         <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D63" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="G63" s="6">
         <v>11</v>
       </c>
       <c r="H63" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="I63" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:15">
@@ -10031,10 +10103,10 @@
         <v>12</v>
       </c>
       <c r="H64" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="I64" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="7:9">
@@ -10042,10 +10114,10 @@
         <v>13</v>
       </c>
       <c r="H65" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="I65" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="7:9">
@@ -10053,10 +10125,10 @@
         <v>14</v>
       </c>
       <c r="H66" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="I66" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -10072,7 +10144,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:M33"/>
+  <dimension ref="A3:M23"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="8.88888888888889" style="6"/>
@@ -10089,7 +10161,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:13">
       <c r="A3" s="15" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -10121,12 +10193,12 @@
     </row>
     <row r="7" customHeight="1" spans="1:13">
       <c r="B7" s="9" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:13">
       <c r="C8" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>33</v>
@@ -10134,7 +10206,7 @@
     </row>
     <row r="9" customHeight="1" spans="1:13">
       <c r="C9" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H9" t="s">
         <v>32</v>
@@ -10145,19 +10217,19 @@
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:13">
@@ -10165,19 +10237,19 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D11" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G11" s="6">
         <v>1</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:13">
@@ -10185,19 +10257,19 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D12" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G12" s="6">
         <v>2</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:13">
@@ -10205,19 +10277,19 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D13" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G13" s="6">
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I13" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:13">
@@ -10225,19 +10297,19 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D14" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="G14" s="6">
         <v>4</v>
       </c>
       <c r="H14" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="I14" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:13">
@@ -10245,15 +10317,15 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D15" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:13">
       <c r="A22" s="15" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -10282,87 +10354,6 @@
       <c r="K23" s="12"/>
       <c r="L23" s="12"/>
       <c r="M23" s="12"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:13">
-      <c r="B25" s="9" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:13">
-      <c r="C26" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:13">
-      <c r="C27" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:13">
-      <c r="B28" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:13">
-      <c r="B29" s="6">
-        <v>1</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:13">
-      <c r="B30" s="6">
-        <v>2</v>
-      </c>
-      <c r="C30" t="s">
-        <v>450</v>
-      </c>
-      <c r="D30" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:13">
-      <c r="B31" s="6">
-        <v>3</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>452</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:13">
-      <c r="B32" s="6">
-        <v>4</v>
-      </c>
-      <c r="C32" t="s">
-        <v>198</v>
-      </c>
-      <c r="D32" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="2:4">
-      <c r="B33" s="6">
-        <v>5</v>
-      </c>
-      <c r="C33" t="s">
-        <v>202</v>
-      </c>
-      <c r="D33" t="s">
-        <v>457</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10402,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:4">
@@ -10413,10 +10404,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D7" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:4">
@@ -10424,10 +10415,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D8" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:4">
@@ -10435,10 +10426,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D9" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:4">
@@ -10446,10 +10437,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D10" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:4">
@@ -10457,10 +10448,10 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D11" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:4">
@@ -10468,10 +10459,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D12" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:4">
@@ -10479,10 +10470,10 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D13" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:9">
@@ -10508,19 +10499,19 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:9">
@@ -10528,19 +10519,19 @@
         <v>1</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D21" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G21" s="6">
         <v>1</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I21" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:9">
@@ -10548,19 +10539,19 @@
         <v>2</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D22" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G22" s="6">
         <v>2</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I22" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:9">
@@ -10568,10 +10559,10 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D23" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G23" s="6"/>
     </row>
@@ -10580,10 +10571,10 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D24" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G24" s="6"/>
     </row>
@@ -10592,10 +10583,10 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D25" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G25" s="6"/>
     </row>
@@ -10604,10 +10595,10 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D26" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G26" s="6"/>
     </row>
@@ -10636,7 +10627,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="12" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -10668,26 +10659,26 @@
     </row>
     <row r="6" customHeight="1" spans="1:14">
       <c r="C6" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:14">
       <c r="C7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:14">
@@ -10695,28 +10686,28 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:14">
@@ -10724,28 +10715,28 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D9" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G9" s="6">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="I9" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="L9" s="6">
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="N9" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:14">
@@ -10753,28 +10744,28 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D10" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="G10" s="6">
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="I10" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="L10" s="6">
         <v>2</v>
       </c>
       <c r="M10" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="N10" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:14">
@@ -10782,28 +10773,28 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D11" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="G11" s="6">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="I11" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="L11" s="6">
         <v>3</v>
       </c>
       <c r="M11" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="N11" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:14">
@@ -10811,28 +10802,28 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D12" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G12" s="6">
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="I12" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="L12" s="6">
         <v>4</v>
       </c>
       <c r="M12" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="N12" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:14">
@@ -10840,44 +10831,44 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D13" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G13" s="6">
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="I13" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L13" s="6">
         <v>5</v>
       </c>
       <c r="M13" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="N13" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:14">
       <c r="C16" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:9">
       <c r="C17" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H17" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:9">
@@ -10885,19 +10876,19 @@
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:9">
@@ -10905,19 +10896,19 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D19" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G19" s="6">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="I19" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:9">
@@ -10925,19 +10916,19 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D20" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="G20" s="6">
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="I20" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:9">
@@ -10945,19 +10936,19 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D21" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="G21" s="6">
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="I21" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:9">
@@ -10965,19 +10956,19 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D22" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G22" s="6">
         <v>4</v>
       </c>
       <c r="H22" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I22" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:9">
@@ -10985,19 +10976,19 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D23" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G23" s="6">
         <v>5</v>
       </c>
       <c r="H23" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I23" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:9">
@@ -11015,10 +11006,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:9">
@@ -11026,10 +11017,10 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D30" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:9">
@@ -11037,10 +11028,10 @@
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D31" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="2:9">
@@ -11048,10 +11039,10 @@
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D32" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:4">
@@ -11059,10 +11050,10 @@
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D33" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:4">
@@ -11070,10 +11061,10 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D34" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:4">
@@ -11081,10 +11072,10 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D35" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:4">
@@ -11092,10 +11083,10 @@
         <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D36" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:4">
@@ -11103,10 +11094,10 @@
         <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D37" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:4">
@@ -11114,10 +11105,10 @@
         <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D38" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:4">
@@ -11125,10 +11116,10 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D39" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:4">
@@ -11136,10 +11127,10 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D40" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:4">
@@ -11147,10 +11138,10 @@
         <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D41" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -11180,7 +11171,7 @@
   <sheetData>
     <row r="2" customHeight="1" spans="1:14">
       <c r="A2" s="7" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -11215,7 +11206,7 @@
     </row>
     <row r="15" customHeight="1" spans="1:14">
       <c r="A15" s="10" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -11252,26 +11243,26 @@
     </row>
     <row r="18" customHeight="1" spans="2:14">
       <c r="C18" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:14">
       <c r="C19" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:14">
@@ -11279,28 +11270,28 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:14">
@@ -11308,28 +11299,28 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D21" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G21" s="6">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I21" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L21" s="6">
         <v>1</v>
       </c>
       <c r="M21" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N21" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:14">
@@ -11337,28 +11328,28 @@
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D22" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G22" s="6">
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I22" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="L22" s="6">
         <v>2</v>
       </c>
       <c r="M22" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="N22" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:14">
@@ -11366,28 +11357,28 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D23" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G23" s="6">
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I23" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L23" s="6">
         <v>3</v>
       </c>
       <c r="M23" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="N23" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:14">
@@ -11395,28 +11386,28 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D24" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="G24" s="6">
         <v>4</v>
       </c>
       <c r="H24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="I24" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="L24" s="6">
         <v>4</v>
       </c>
       <c r="M24" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N24" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:14">
@@ -11424,28 +11415,28 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D25" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G25" s="6">
         <v>5</v>
       </c>
       <c r="H25" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="I25" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="L25" s="6">
         <v>5</v>
       </c>
       <c r="M25" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N25" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:14">
@@ -11453,28 +11444,28 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D26" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G26" s="6">
         <v>6</v>
       </c>
       <c r="H26" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="I26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="L26" s="6">
         <v>6</v>
       </c>
       <c r="M26" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="N26" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:14">
@@ -11482,28 +11473,28 @@
         <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D27" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="G27" s="6">
         <v>7</v>
       </c>
       <c r="H27" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I27" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="L27" s="6">
         <v>7</v>
       </c>
       <c r="M27" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="N27" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:14">
@@ -11511,10 +11502,10 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D28" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:14">
@@ -11522,10 +11513,10 @@
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D29" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:14">
@@ -11533,10 +11524,10 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D30" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:14">
@@ -11544,10 +11535,10 @@
         <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D31" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="H31" s="1"/>
     </row>
@@ -11556,10 +11547,10 @@
         <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D32" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="H32" s="1"/>
     </row>
@@ -11568,10 +11559,10 @@
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="1"/>
@@ -11582,10 +11573,10 @@
         <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D34" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -11593,10 +11584,10 @@
         <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D35" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -11604,10 +11595,10 @@
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D36" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:14">
@@ -11615,34 +11606,34 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D37" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:14">
       <c r="C42" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="L42" s="6"/>
       <c r="M42" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:14">
       <c r="C43" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:14">
@@ -11650,28 +11641,28 @@
         <v>0</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G44" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L44" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:14">
@@ -11679,28 +11670,28 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D45" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G45" s="6">
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I45" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L45" s="6">
         <v>1</v>
       </c>
       <c r="M45" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N45" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:14">
@@ -11708,28 +11699,28 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D46" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G46" s="6">
         <v>2</v>
       </c>
       <c r="H46" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I46" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="L46" s="6">
         <v>2</v>
       </c>
       <c r="M46" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N46" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:14">
@@ -11737,28 +11728,28 @@
         <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D47" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G47" s="6">
         <v>3</v>
       </c>
       <c r="H47" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I47" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L47" s="6">
         <v>3</v>
       </c>
       <c r="M47" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N47" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="2:14">
@@ -11766,28 +11757,28 @@
         <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D48" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="G48" s="6">
         <v>4</v>
       </c>
       <c r="H48" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="I48" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L48" s="6">
         <v>4</v>
       </c>
       <c r="M48" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="N48" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="2:14">
@@ -11795,28 +11786,28 @@
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D49" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G49" s="6">
         <v>5</v>
       </c>
       <c r="H49" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I49" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="L49" s="6">
         <v>5</v>
       </c>
       <c r="M49" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="N49" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:14">
@@ -11824,28 +11815,28 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D50" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="G50" s="6">
         <v>6</v>
       </c>
       <c r="H50" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="I50" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L50" s="6">
         <v>6</v>
       </c>
       <c r="M50" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="N50" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:14">
@@ -11853,28 +11844,28 @@
         <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D51" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="G51" s="6">
         <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="I51" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="L51" s="6">
         <v>7</v>
       </c>
       <c r="M51" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="N51" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:14">
@@ -11882,28 +11873,28 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D52" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G52" s="6">
         <v>8</v>
       </c>
       <c r="H52" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="I52" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="L52" s="6">
         <v>8</v>
       </c>
       <c r="M52" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="N52" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:14">
@@ -11911,28 +11902,28 @@
         <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D53" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="G53" s="6">
         <v>9</v>
       </c>
       <c r="H53" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="I53" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="L53" s="6">
         <v>9</v>
       </c>
       <c r="M53" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="N53" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:14">
@@ -11940,28 +11931,28 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D54" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="G54" s="6">
         <v>10</v>
       </c>
       <c r="H54" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="I54" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="L54" s="6">
         <v>10</v>
       </c>
       <c r="M54" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="N54" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:14">
@@ -11969,28 +11960,28 @@
         <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D55" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="G55" s="6">
         <v>11</v>
       </c>
       <c r="H55" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="I55" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="L55" s="6">
         <v>11</v>
       </c>
       <c r="M55" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="N55" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="2:14">
@@ -11998,28 +11989,28 @@
         <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D56" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="G56" s="6">
         <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="I56" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="L56" s="6">
         <v>12</v>
       </c>
       <c r="M56" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="N56" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:14">
@@ -12027,28 +12018,28 @@
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D57" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="G57" s="6">
         <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="I57" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="L57" s="6">
         <v>13</v>
       </c>
       <c r="M57" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="N57" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:14">
@@ -12056,28 +12047,28 @@
         <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D58" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G58" s="6">
         <v>14</v>
       </c>
       <c r="H58" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="I58" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="L58" s="6">
         <v>14</v>
       </c>
       <c r="M58" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="N58" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:14">
@@ -12085,28 +12076,28 @@
         <v>15</v>
       </c>
       <c r="C59" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D59" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="G59" s="6">
         <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="I59" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L59" s="6">
         <v>15</v>
       </c>
       <c r="M59" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="N59" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:14">
@@ -12114,28 +12105,28 @@
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D60" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="G60" s="6">
         <v>16</v>
       </c>
       <c r="H60" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="I60" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="L60" s="6">
         <v>16</v>
       </c>
       <c r="M60" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="N60" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:14">
@@ -12143,28 +12134,28 @@
         <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D61" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G61" s="6">
         <v>17</v>
       </c>
       <c r="H61" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="I61" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L61" s="6">
         <v>17</v>
       </c>
       <c r="M61" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="N61" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:14">
@@ -12172,10 +12163,10 @@
         <v>18</v>
       </c>
       <c r="M62" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="N62" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:14">
@@ -12183,10 +12174,10 @@
         <v>19</v>
       </c>
       <c r="M63" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="N63" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:14">
@@ -12194,30 +12185,30 @@
         <v>20</v>
       </c>
       <c r="M64" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="N64" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:14">
       <c r="B65" s="6" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L65" s="6">
         <v>21</v>
       </c>
       <c r="M65" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="N65" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:14">
@@ -12225,20 +12216,20 @@
         <v>22</v>
       </c>
       <c r="M66" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="N66" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:14">
       <c r="C67" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:14">
       <c r="A70" s="10" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
@@ -12272,18 +12263,18 @@
     </row>
     <row r="73" customHeight="1" spans="1:14">
       <c r="C73" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:14">
       <c r="C74" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:14">
@@ -12291,19 +12282,19 @@
         <v>0</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G75" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:14">
@@ -12311,19 +12302,19 @@
         <v>1</v>
       </c>
       <c r="C76" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D76" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G76" s="6">
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I76" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:14">
@@ -12331,19 +12322,19 @@
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D77" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G77" s="6">
         <v>2</v>
       </c>
       <c r="H77" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I77" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:14">
@@ -12351,19 +12342,19 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D78" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G78" s="6">
         <v>3</v>
       </c>
       <c r="H78" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I78" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:14">
@@ -12371,19 +12362,19 @@
         <v>4</v>
       </c>
       <c r="C79" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D79" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G79" s="6">
         <v>4</v>
       </c>
       <c r="H79" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="I79" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:14">
@@ -12391,19 +12382,19 @@
         <v>5</v>
       </c>
       <c r="C80" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D80" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G80" s="6">
         <v>5</v>
       </c>
       <c r="H80" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="I80" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:9">
@@ -12411,19 +12402,19 @@
         <v>6</v>
       </c>
       <c r="C81" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D81" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="G81" s="6">
         <v>6</v>
       </c>
       <c r="H81" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="I81" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:9">
@@ -12431,19 +12422,19 @@
         <v>7</v>
       </c>
       <c r="C82" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D82" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="G82" s="6">
         <v>7</v>
       </c>
       <c r="H82" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="I82" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:9">
@@ -12451,19 +12442,19 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D83" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="G83" s="6">
         <v>8</v>
       </c>
       <c r="H83" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="I83" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:9">
@@ -12471,19 +12462,19 @@
         <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D84" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="G84" s="6">
         <v>9</v>
       </c>
       <c r="H84" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="I84" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:9">
@@ -12491,19 +12482,19 @@
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D85" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="G85" s="6">
         <v>10</v>
       </c>
       <c r="H85" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="I85" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:9">
@@ -12511,10 +12502,10 @@
         <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D86" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:9">
@@ -12522,10 +12513,10 @@
         <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D87" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:9">
@@ -12533,10 +12524,10 @@
         <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="D88" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="1:9">
@@ -12544,10 +12535,10 @@
         <v>14</v>
       </c>
       <c r="C89" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D89" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:9">
@@ -12555,10 +12546,10 @@
         <v>15</v>
       </c>
       <c r="C90" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D90" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:9">
@@ -12566,15 +12557,15 @@
         <v>16</v>
       </c>
       <c r="C91" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D91" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="1:9">
       <c r="A95" s="10" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
@@ -12598,18 +12589,18 @@
     </row>
     <row r="99" customHeight="1" spans="2:9">
       <c r="C99" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="2:9">
       <c r="C100" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="2:9">
@@ -12617,19 +12608,19 @@
         <v>0</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G101" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="2:9">
@@ -12637,19 +12628,19 @@
         <v>1</v>
       </c>
       <c r="C102" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D102" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G102" s="6">
         <v>1</v>
       </c>
       <c r="H102" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I102" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="2:9">
@@ -12657,19 +12648,19 @@
         <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D103" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G103" s="6">
         <v>2</v>
       </c>
       <c r="H103" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I103" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="2:9">
@@ -12677,19 +12668,19 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D104" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G104" s="6">
         <v>3</v>
       </c>
       <c r="H104" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I104" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="2:9">
@@ -12697,19 +12688,19 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D105" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="G105" s="6">
         <v>4</v>
       </c>
       <c r="H105" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="I105" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="2:9">
@@ -12717,19 +12708,19 @@
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="D106" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="G106" s="6">
         <v>5</v>
       </c>
       <c r="H106" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="I106" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="2:9">
@@ -12737,19 +12728,19 @@
         <v>6</v>
       </c>
       <c r="C107" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="D107" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G107" s="6">
         <v>6</v>
       </c>
       <c r="H107" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="I107" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="2:9">
@@ -12757,19 +12748,19 @@
         <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="D108" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="G108" s="6">
         <v>7</v>
       </c>
       <c r="H108" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="I108" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="2:9">
@@ -12777,19 +12768,19 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D109" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="G109" s="6">
         <v>8</v>
       </c>
       <c r="H109" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="I109" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
   </sheetData>
@@ -12820,29 +12811,29 @@
   <sheetData>
     <row r="5" spans="3:9">
       <c r="C5" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="7" spans="3:9">
       <c r="F7" s="1" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8" spans="3:9">
       <c r="D8" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>17</v>
@@ -12850,89 +12841,89 @@
     </row>
     <row r="9" spans="3:9">
       <c r="I9" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="13" spans="3:9">
       <c r="H13" s="1" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="14" spans="3:9">
       <c r="H14" s="1" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="15" spans="3:9">
       <c r="I15" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="19" spans="8:9">
       <c r="H19" s="1" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="20" spans="8:9">
       <c r="H20" s="1" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="21" spans="8:9">
       <c r="I21" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="25" spans="8:9">
       <c r="H25" s="1" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="26" spans="8:9">
       <c r="H26" s="1" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="27" spans="8:9">
       <c r="I27" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="31" spans="8:9">
       <c r="H31" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="32" spans="8:9">
       <c r="H32" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="33" spans="8:9">
       <c r="I33" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="37" spans="8:9">
       <c r="H37" s="1" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
     <row r="38" spans="8:9">
       <c r="H38" s="1" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>21</v>
@@ -12940,72 +12931,72 @@
     </row>
     <row r="43" spans="8:9">
       <c r="H43" s="1" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="44" spans="8:9">
       <c r="H44" s="1" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="8:9">
       <c r="I45" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="6:9">
       <c r="H49" s="1" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="50" spans="6:9">
       <c r="H50" s="1" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51" spans="6:9">
       <c r="I51" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="55" spans="6:9">
       <c r="H55" s="1" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="56" spans="6:9">
       <c r="H56" s="1" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="57" spans="6:9">
       <c r="I57" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="61" spans="6:9">
       <c r="F61" s="1" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="62" spans="6:9">
       <c r="F62" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>63</v>
@@ -13013,17 +13004,17 @@
     </row>
     <row r="63" spans="6:9">
       <c r="I63" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="65" spans="8:9">
       <c r="H65" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="66" spans="8:9">
       <c r="H66" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>67</v>
@@ -13031,53 +13022,53 @@
     </row>
     <row r="67" spans="8:9">
       <c r="I67" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="69" spans="8:9">
       <c r="H69" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
     <row r="70" spans="8:9">
       <c r="H70" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="71" spans="8:9">
       <c r="I71" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="73" spans="8:9">
       <c r="H73" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="74" spans="8:9">
       <c r="H74" s="1" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="75" spans="8:9">
       <c r="I75" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="77" spans="8:9">
       <c r="H77" s="1" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="78" spans="8:9">
       <c r="H78" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>24</v>
@@ -13085,17 +13076,17 @@
     </row>
     <row r="79" spans="8:9">
       <c r="I79" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
     <row r="81" spans="6:9">
       <c r="H81" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="82" spans="6:9">
       <c r="H82" s="1" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>28</v>
@@ -13103,41 +13094,41 @@
     </row>
     <row r="83" spans="6:9">
       <c r="I83" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
     </row>
     <row r="87" spans="6:9">
       <c r="F87" s="1" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="88" spans="6:9">
       <c r="F88" s="1" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="89" spans="6:9">
       <c r="I89" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="92" spans="6:9">
       <c r="H92" s="1" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="93" spans="6:9">
       <c r="H93" s="1" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>32</v>
@@ -13145,111 +13136,111 @@
     </row>
     <row r="94" spans="6:9">
       <c r="I94" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
     </row>
     <row r="97" spans="6:9">
       <c r="H97" s="1" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="98" spans="6:9">
       <c r="H98" s="1" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="99" spans="6:9">
       <c r="I99" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="101" spans="6:9">
       <c r="H101" s="1" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="102" spans="6:9">
       <c r="H102" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="103" spans="6:9">
       <c r="I103" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
     <row r="105" spans="6:9">
       <c r="I105" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="106" spans="6:9">
       <c r="I106" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
     <row r="109" spans="6:9">
       <c r="F109" s="1" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
     </row>
     <row r="110" spans="6:9">
       <c r="F110" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="111" spans="6:9">
       <c r="I111" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="114" spans="6:9">
       <c r="H114" s="1" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="115" spans="6:9">
       <c r="H115" s="1" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="116" spans="6:9">
       <c r="I116" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="120" spans="6:9">
       <c r="F120" s="1" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
     </row>
     <row r="121" spans="6:9">
       <c r="F121" s="1" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>63</v>
@@ -13257,12 +13248,12 @@
     </row>
     <row r="124" spans="6:9">
       <c r="H124" s="1" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="125" spans="6:9">
       <c r="H125" s="1" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>67</v>
@@ -13270,25 +13261,25 @@
     </row>
     <row r="128" spans="6:9">
       <c r="H128" s="1" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
     </row>
     <row r="129" spans="8:9">
       <c r="H129" s="1" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="132" spans="8:9">
       <c r="H132" s="1" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
     </row>
     <row r="133" spans="8:9">
       <c r="H133" s="1" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>70</v>
@@ -13296,12 +13287,12 @@
     </row>
     <row r="136" spans="8:9">
       <c r="H136" s="1" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
     </row>
     <row r="137" spans="8:9">
       <c r="H137" s="1" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>24</v>
@@ -13314,7 +13305,7 @@
     </row>
     <row r="158" spans="6:6">
       <c r="F158" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
   </sheetData>
